--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Caplan\OneDrive\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD1F2E7-C9F6-4C8F-9454-B15C5A5F608A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3391C4B-A9D0-4986-A2D3-6E26BE7E5ECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="660" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2650" uniqueCount="2650">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2694" uniqueCount="2694">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -8001,6 +8001,138 @@
   </si>
   <si>
     <t>72.503251</t>
+  </si>
+  <si>
+    <t>Zarkent sh., Qo'shrabot tumani, Zarkent ko'chasi, 246 uy: г. Заркент, Кошрабадский район, улица Заркент, дом 246</t>
+  </si>
+  <si>
+    <t>FrЗРТ-1</t>
+  </si>
+  <si>
+    <t>40.312979</t>
+  </si>
+  <si>
+    <t>66.733867</t>
+  </si>
+  <si>
+    <t>Farg'ona sh., Said Axmad ko'chasi, 53 uy: г. Фергана, улица Саид Ахмад, дом 53</t>
+  </si>
+  <si>
+    <t>FrФЕР-36</t>
+  </si>
+  <si>
+    <t>40.379913</t>
+  </si>
+  <si>
+    <t>71.809586</t>
+  </si>
+  <si>
+    <t>To'rtko'l sh., Toshkent ko'chasi, 427 a uy: г. Турткуль, улица Ташкент, дом 427 а</t>
+  </si>
+  <si>
+    <t>FrТРТ-4</t>
+  </si>
+  <si>
+    <t>41.541697</t>
+  </si>
+  <si>
+    <t>61.024024</t>
+  </si>
+  <si>
+    <t>Buxoro sh., Amir Temur ko'chasi, 39 uy: г. Бухара, улица Амир Темур, дом 39</t>
+  </si>
+  <si>
+    <t>FrБХР-36</t>
+  </si>
+  <si>
+    <t>39.739232</t>
+  </si>
+  <si>
+    <t>64.402773</t>
+  </si>
+  <si>
+    <t>Galaоsiya sh., Fayzullo Xoʻjayev ko'chasi, 386 uy: г. Галаасия, улица Файзулла Ходжаева, 386 дом</t>
+  </si>
+  <si>
+    <t>FrГЛС-3</t>
+  </si>
+  <si>
+    <t>39.851524</t>
+  </si>
+  <si>
+    <t>64.442893</t>
+  </si>
+  <si>
+    <t>Pop sh., Oybek ko'chasi, 131 uy: г. Пап, улица Ойбек, дом 131</t>
+  </si>
+  <si>
+    <t>FrПАП-6</t>
+  </si>
+  <si>
+    <t>40.874289</t>
+  </si>
+  <si>
+    <t>71.105374</t>
+  </si>
+  <si>
+    <t>Sharg'un sh., Bog'i shamol ko'chasi, 3 uy: г. Шаргунь, улица Боги шамол, дом 3</t>
+  </si>
+  <si>
+    <t>FrШРГ-2</t>
+  </si>
+  <si>
+    <t>38.455263</t>
+  </si>
+  <si>
+    <t>67.977437</t>
+  </si>
+  <si>
+    <t>G'uzor sh., Mustakillik ko'chasi, 85 uy: г. Гузар, улица Мустакиллик, дом 85</t>
+  </si>
+  <si>
+    <t>FrГУЗ-5</t>
+  </si>
+  <si>
+    <t>38.635054</t>
+  </si>
+  <si>
+    <t>66.211378</t>
+  </si>
+  <si>
+    <t>Jomboy sh., Galakapa ko'chasi, 72 uy: г. Джамбай, улица Галакапа, дом 72</t>
+  </si>
+  <si>
+    <t>FrДЖБ-5</t>
+  </si>
+  <si>
+    <t>39.694270</t>
+  </si>
+  <si>
+    <t>67.099952</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Mirobod tumani, Yangizamon ko'chasi, 11 uy: г. Ташкент, Мирабадский район, улица Янгизамон, дом 11</t>
+  </si>
+  <si>
+    <t>FrТАШ-349</t>
+  </si>
+  <si>
+    <t>41.278930</t>
+  </si>
+  <si>
+    <t>69.299820</t>
+  </si>
+  <si>
+    <t>Yangiyer sh., Amir Temur ko'chasi, 3 uy: г. Янгиер, улица Амир Тему, дом 3</t>
+  </si>
+  <si>
+    <t>FrЯНР-4</t>
+  </si>
+  <si>
+    <t>40.273954</t>
+  </si>
+  <si>
+    <t>68.828436</t>
   </si>
 </sst>
 </file>
@@ -8162,7 +8294,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -8211,6 +8343,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8492,11 +8630,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1287"/>
+  <dimension ref="A1:D1298"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="10"/>
+    <col min="2" max="2" width="12.85546875" style="10" customWidth="1"/>
     <col min="3" max="3" width="12" style="10" customWidth="1"/>
     <col min="4" max="4" width="13.85546875" style="10" customWidth="1"/>
     <col min="6" max="6" width="9.140625" customWidth="1"/>
@@ -8796,7 +8934,7 @@
         <v>71.809231999999994</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>42</v>
       </c>
@@ -10798,7 +10936,7 @@
         <v>69.343695999999994</v>
       </c>
     </row>
-    <row r="165" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="5" t="s">
         <v>328</v>
       </c>
@@ -11694,7 +11832,7 @@
         <v>72.999573999999996</v>
       </c>
     </row>
-    <row r="229" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="5" t="s">
         <v>456</v>
       </c>
@@ -11862,7 +12000,7 @@
         <v>64.434209999999993</v>
       </c>
     </row>
-    <row r="241" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="5" t="s">
         <v>480</v>
       </c>
@@ -12590,7 +12728,7 @@
         <v>70.059414000000004</v>
       </c>
     </row>
-    <row r="293" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="5" t="s">
         <v>584</v>
       </c>
@@ -15194,7 +15332,7 @@
         <v>69.23648</v>
       </c>
     </row>
-    <row r="479" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A479" s="5" t="s">
         <v>956</v>
       </c>
@@ -17560,7 +17698,7 @@
         <v>59.462802000000003</v>
       </c>
     </row>
-    <row r="648" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A648" s="5" t="s">
         <v>1294</v>
       </c>
@@ -17882,7 +18020,7 @@
         <v>69.202941999999993</v>
       </c>
     </row>
-    <row r="671" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A671" s="5" t="s">
         <v>1340</v>
       </c>
@@ -18274,7 +18412,7 @@
         <v>72.069658000000004</v>
       </c>
     </row>
-    <row r="699" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A699" s="5" t="s">
         <v>1396</v>
       </c>
@@ -18610,7 +18748,7 @@
         <v>72.754859999999994</v>
       </c>
     </row>
-    <row r="723" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A723" s="5" t="s">
         <v>1444</v>
       </c>
@@ -19296,7 +19434,7 @@
         <v>69.341136000000006</v>
       </c>
     </row>
-    <row r="772" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A772" s="5" t="s">
         <v>1542</v>
       </c>
@@ -19618,7 +19756,7 @@
         <v>72.094283000000004</v>
       </c>
     </row>
-    <row r="795" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A795" s="5" t="s">
         <v>1588</v>
       </c>
@@ -20094,7 +20232,7 @@
         <v>60.602592999999999</v>
       </c>
     </row>
-    <row r="829" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A829" s="5" t="s">
         <v>1656</v>
       </c>
@@ -21550,7 +21688,7 @@
         <v>69.221705</v>
       </c>
     </row>
-    <row r="933" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="933" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A933" s="5" t="s">
         <v>1864</v>
       </c>
@@ -21998,7 +22136,7 @@
         <v>69.371487000000002</v>
       </c>
     </row>
-    <row r="965" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="965" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A965" s="5" t="s">
         <v>1928</v>
       </c>
@@ -22460,7 +22598,7 @@
         <v>72.833483000000001</v>
       </c>
     </row>
-    <row r="998" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="998" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A998" s="5" t="s">
         <v>1994</v>
       </c>
@@ -26518,6 +26656,160 @@
       </c>
       <c r="D1287" s="10" t="s">
         <v>2649</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1288" s="1" t="s">
+        <v>2650</v>
+      </c>
+      <c r="B1288" s="17" t="s">
+        <v>2651</v>
+      </c>
+      <c r="C1288" s="17" t="s">
+        <v>2652</v>
+      </c>
+      <c r="D1288" s="10" t="s">
+        <v>2653</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1289" s="1" t="s">
+        <v>2654</v>
+      </c>
+      <c r="B1289" s="17" t="s">
+        <v>2655</v>
+      </c>
+      <c r="C1289" s="17" t="s">
+        <v>2656</v>
+      </c>
+      <c r="D1289" s="10" t="s">
+        <v>2657</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1290" s="1" t="s">
+        <v>2658</v>
+      </c>
+      <c r="B1290" s="17" t="s">
+        <v>2659</v>
+      </c>
+      <c r="C1290" s="17" t="s">
+        <v>2660</v>
+      </c>
+      <c r="D1290" s="10" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1291" s="1" t="s">
+        <v>2662</v>
+      </c>
+      <c r="B1291" s="17" t="s">
+        <v>2663</v>
+      </c>
+      <c r="C1291" s="17" t="s">
+        <v>2664</v>
+      </c>
+      <c r="D1291" s="10" t="s">
+        <v>2665</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1292" s="1" t="s">
+        <v>2666</v>
+      </c>
+      <c r="B1292" s="17" t="s">
+        <v>2667</v>
+      </c>
+      <c r="C1292" s="17" t="s">
+        <v>2668</v>
+      </c>
+      <c r="D1292" s="10" t="s">
+        <v>2669</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1293" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="B1293" s="17" t="s">
+        <v>2671</v>
+      </c>
+      <c r="C1293" s="17" t="s">
+        <v>2672</v>
+      </c>
+      <c r="D1293" s="10" t="s">
+        <v>2673</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1294" s="1" t="s">
+        <v>2674</v>
+      </c>
+      <c r="B1294" s="17" t="s">
+        <v>2675</v>
+      </c>
+      <c r="C1294" s="17" t="s">
+        <v>2676</v>
+      </c>
+      <c r="D1294" s="10" t="s">
+        <v>2677</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1295" s="1" t="s">
+        <v>2678</v>
+      </c>
+      <c r="B1295" s="17" t="s">
+        <v>2679</v>
+      </c>
+      <c r="C1295" s="17" t="s">
+        <v>2680</v>
+      </c>
+      <c r="D1295" s="10" t="s">
+        <v>2681</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1296" s="1" t="s">
+        <v>2682</v>
+      </c>
+      <c r="B1296" s="17" t="s">
+        <v>2683</v>
+      </c>
+      <c r="C1296" s="17" t="s">
+        <v>2684</v>
+      </c>
+      <c r="D1296" s="10" t="s">
+        <v>2685</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1297" s="1" t="s">
+        <v>2686</v>
+      </c>
+      <c r="B1297" s="17" t="s">
+        <v>2687</v>
+      </c>
+      <c r="C1297" s="17" t="s">
+        <v>2688</v>
+      </c>
+      <c r="D1297" s="10" t="s">
+        <v>2689</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1298" s="8" t="s">
+        <v>2690</v>
+      </c>
+      <c r="B1298" s="18" t="s">
+        <v>2691</v>
+      </c>
+      <c r="C1298" s="18" t="s">
+        <v>2692</v>
+      </c>
+      <c r="D1298" s="10" t="s">
+        <v>2693</v>
       </c>
     </row>
   </sheetData>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Caplan\OneDrive\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3391C4B-A9D0-4986-A2D3-6E26BE7E5ECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF35F64-7048-4DFC-A42A-1B03ED49BCA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="660" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2694" uniqueCount="2694">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2726" uniqueCount="2726">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -8133,6 +8133,102 @@
   </si>
   <si>
     <t>68.828436</t>
+  </si>
+  <si>
+    <t>Qorashiq sh., Gulzor ko‘chasi, 33 uy: г. Карашик, улица Гулзор, дом 33</t>
+  </si>
+  <si>
+    <t>FrКРА-2</t>
+  </si>
+  <si>
+    <t>38.398783</t>
+  </si>
+  <si>
+    <t>68.028000</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Mirobod tumani, Gospital mavzesi, 37 uy: г. Ташкент, Мирабадский район, массив Госпитальный, дом 37</t>
+  </si>
+  <si>
+    <t>FrТАШ-346</t>
+  </si>
+  <si>
+    <t>41.292492</t>
+  </si>
+  <si>
+    <t>69.273993</t>
+  </si>
+  <si>
+    <t>G'o's sh., Soy guzar ko‘chasi, 34 uy: г. Гус, улица Сой гузар, дом 34</t>
+  </si>
+  <si>
+    <t>FrГУС-1</t>
+  </si>
+  <si>
+    <t>39.395701</t>
+  </si>
+  <si>
+    <t>67.305706</t>
+  </si>
+  <si>
+    <t>Jondor sh., Tinchlik ko'chasi, 11a uy: г. Жондор, улица Тинчлик, дом 11а</t>
+  </si>
+  <si>
+    <t>FrЖНД-2</t>
+  </si>
+  <si>
+    <t>39.738943</t>
+  </si>
+  <si>
+    <t>64.173463</t>
+  </si>
+  <si>
+    <t>Qorovulbozor sh., Bobur ko'chasi, 732 uy: г. Караулбазар, улица Бобур, дом 732</t>
+  </si>
+  <si>
+    <t>FrКРБ-2</t>
+  </si>
+  <si>
+    <t>39.497783</t>
+  </si>
+  <si>
+    <t>64.785196</t>
+  </si>
+  <si>
+    <t>Jarqoʻrgʻon sh., M.Oʼtanov ko'chasi, 64 b uy: г. Джаркурган, улица М. Утанов, дом 64 б</t>
+  </si>
+  <si>
+    <t>FrДЖР-3</t>
+  </si>
+  <si>
+    <t>37.503131</t>
+  </si>
+  <si>
+    <t>67.407110</t>
+  </si>
+  <si>
+    <t>Termiz sh., Istiqlol ko'chasi, 11 v uy: г. Термез, улица Истиклол, дом 11 в</t>
+  </si>
+  <si>
+    <t>FrТЕР-21</t>
+  </si>
+  <si>
+    <t>37.249238</t>
+  </si>
+  <si>
+    <t>67.259770</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Uchtepa tumani, Jurdjani ko’chasi, 42A uy: г. Ташкент, Учтепинский район, улица Джурджани, дом 42А</t>
+  </si>
+  <si>
+    <t>FrТАШ-352</t>
+  </si>
+  <si>
+    <t>41.298587</t>
+  </si>
+  <si>
+    <t>69.173592</t>
   </si>
 </sst>
 </file>
@@ -8294,7 +8390,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -8348,6 +8444,9 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8630,7 +8729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1298"/>
+  <dimension ref="A1:D1306"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -9732,7 +9831,7 @@
         <v>66.966831999999997</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>156</v>
       </c>
@@ -10012,7 +10111,7 @@
         <v>69.220478999999997</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>196</v>
       </c>
@@ -10180,7 +10279,7 @@
         <v>67.845365999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>220</v>
       </c>
@@ -10782,7 +10881,7 @@
         <v>64.449057999999994</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="5" t="s">
         <v>306</v>
       </c>
@@ -11580,7 +11679,7 @@
         <v>69.213064000000003</v>
       </c>
     </row>
-    <row r="211" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="5" t="s">
         <v>420</v>
       </c>
@@ -11608,7 +11707,7 @@
         <v>69.262288999999996</v>
       </c>
     </row>
-    <row r="213" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="5" t="s">
         <v>424</v>
       </c>
@@ -12112,7 +12211,7 @@
         <v>66.914541</v>
       </c>
     </row>
-    <row r="249" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="5" t="s">
         <v>496</v>
       </c>
@@ -12462,7 +12561,7 @@
         <v>69.345461999999998</v>
       </c>
     </row>
-    <row r="274" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="5" t="s">
         <v>546</v>
       </c>
@@ -12756,7 +12855,7 @@
         <v>69.199830000000006</v>
       </c>
     </row>
-    <row r="295" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A295" s="5" t="s">
         <v>588</v>
       </c>
@@ -14912,7 +15011,7 @@
         <v>66.811442</v>
       </c>
     </row>
-    <row r="449" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A449" s="5" t="s">
         <v>896</v>
       </c>
@@ -15626,7 +15725,7 @@
         <v>65.967026000000004</v>
       </c>
     </row>
-    <row r="500" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A500" s="5" t="s">
         <v>998</v>
       </c>
@@ -15640,7 +15739,7 @@
         <v>67.955681999999996</v>
       </c>
     </row>
-    <row r="501" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A501" s="5" t="s">
         <v>1000</v>
       </c>
@@ -15710,7 +15809,7 @@
         <v>68.698858000000001</v>
       </c>
     </row>
-    <row r="506" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A506" s="5" t="s">
         <v>1010</v>
       </c>
@@ -16312,7 +16411,7 @@
         <v>68.778199000000001</v>
       </c>
     </row>
-    <row r="549" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A549" s="5" t="s">
         <v>1096</v>
       </c>
@@ -17712,7 +17811,7 @@
         <v>59.636077999999998</v>
       </c>
     </row>
-    <row r="649" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A649" s="5" t="s">
         <v>1296</v>
       </c>
@@ -17782,7 +17881,7 @@
         <v>69.666891000000007</v>
       </c>
     </row>
-    <row r="654" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A654" s="5" t="s">
         <v>1306</v>
       </c>
@@ -18874,7 +18973,7 @@
         <v>60.775509999999997</v>
       </c>
     </row>
-    <row r="732" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A732" s="5" t="s">
         <v>1462</v>
       </c>
@@ -20064,7 +20163,7 @@
         <v>66.580971000000005</v>
       </c>
     </row>
-    <row r="817" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A817" s="5" t="s">
         <v>1632</v>
       </c>
@@ -20092,7 +20191,7 @@
         <v>72.248024000000001</v>
       </c>
     </row>
-    <row r="819" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A819" s="5" t="s">
         <v>1636</v>
       </c>
@@ -21282,7 +21381,7 @@
         <v>66.664512999999999</v>
       </c>
     </row>
-    <row r="904" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="904" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A904" s="5" t="s">
         <v>1806</v>
       </c>
@@ -22626,7 +22725,7 @@
         <v>72.605045000000004</v>
       </c>
     </row>
-    <row r="1000" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1000" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1000" s="5" t="s">
         <v>1998</v>
       </c>
@@ -22948,7 +23047,7 @@
         <v>68.044437000000002</v>
       </c>
     </row>
-    <row r="1023" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1023" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1023" s="5" t="s">
         <v>2044</v>
       </c>
@@ -24208,7 +24307,7 @@
         <v>69.506917999999999</v>
       </c>
     </row>
-    <row r="1113" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1113" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1113" s="5" t="s">
         <v>2224</v>
       </c>
@@ -24796,7 +24895,7 @@
         <v>69.234982000000002</v>
       </c>
     </row>
-    <row r="1155" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1155" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1155" s="5" t="s">
         <v>2308</v>
       </c>
@@ -26350,7 +26449,7 @@
         <v>2561</v>
       </c>
     </row>
-    <row r="1266" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1266" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1266" s="1" t="s">
         <v>2562</v>
       </c>
@@ -26810,6 +26909,118 @@
       </c>
       <c r="D1298" s="10" t="s">
         <v>2693</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1299" s="7" t="s">
+        <v>2694</v>
+      </c>
+      <c r="B1299" s="17" t="s">
+        <v>2695</v>
+      </c>
+      <c r="C1299" s="19" t="s">
+        <v>2696</v>
+      </c>
+      <c r="D1299" s="10" t="s">
+        <v>2697</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1300" s="1" t="s">
+        <v>2698</v>
+      </c>
+      <c r="B1300" s="17" t="s">
+        <v>2699</v>
+      </c>
+      <c r="C1300" s="17" t="s">
+        <v>2700</v>
+      </c>
+      <c r="D1300" s="10" t="s">
+        <v>2701</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1301" s="1" t="s">
+        <v>2702</v>
+      </c>
+      <c r="B1301" s="17" t="s">
+        <v>2703</v>
+      </c>
+      <c r="C1301" s="17" t="s">
+        <v>2704</v>
+      </c>
+      <c r="D1301" s="10" t="s">
+        <v>2705</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1302" s="1" t="s">
+        <v>2706</v>
+      </c>
+      <c r="B1302" s="17" t="s">
+        <v>2707</v>
+      </c>
+      <c r="C1302" s="17" t="s">
+        <v>2708</v>
+      </c>
+      <c r="D1302" s="10" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1303" s="1" t="s">
+        <v>2710</v>
+      </c>
+      <c r="B1303" s="17" t="s">
+        <v>2711</v>
+      </c>
+      <c r="C1303" s="17" t="s">
+        <v>2712</v>
+      </c>
+      <c r="D1303" s="10" t="s">
+        <v>2713</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1304" s="1" t="s">
+        <v>2714</v>
+      </c>
+      <c r="B1304" s="17" t="s">
+        <v>2715</v>
+      </c>
+      <c r="C1304" s="17" t="s">
+        <v>2716</v>
+      </c>
+      <c r="D1304" s="10" t="s">
+        <v>2717</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1305" s="1" t="s">
+        <v>2718</v>
+      </c>
+      <c r="B1305" s="17" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1305" s="17" t="s">
+        <v>2720</v>
+      </c>
+      <c r="D1305" s="10" t="s">
+        <v>2721</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1306" s="1" t="s">
+        <v>2722</v>
+      </c>
+      <c r="B1306" s="17" t="s">
+        <v>2723</v>
+      </c>
+      <c r="C1306" s="17" t="s">
+        <v>2724</v>
+      </c>
+      <c r="D1306" s="10" t="s">
+        <v>2725</v>
       </c>
     </row>
   </sheetData>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Caplan\OneDrive\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF35F64-7048-4DFC-A42A-1B03ED49BCA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274E1294-E2E5-40A0-A6DE-9F7818A59E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-1230" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2726" uniqueCount="2726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2742" uniqueCount="2742">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -8229,6 +8229,54 @@
   </si>
   <si>
     <t>69.173592</t>
+  </si>
+  <si>
+    <t>Yangiqoʻrgʻon sh., Yangiqo'rg'on tumani, Chortoq ko'chasi, 77 uy: г. Янгикурган, Янгикурганский район, улица Чорток, дом 77</t>
+  </si>
+  <si>
+    <t>FrЯНК-2</t>
+  </si>
+  <si>
+    <t>41.187051</t>
+  </si>
+  <si>
+    <t>71.727449</t>
+  </si>
+  <si>
+    <t>Qumqo'rg'on sh., Qumqo‘rg‘on tumani, Maxmut Turaboy ko'chasi, 42 a uy: г. Кумкурган, Кумкурганский район, улица Махмут Турабой, дом 42 а</t>
+  </si>
+  <si>
+    <t>FrКУМ-3</t>
+  </si>
+  <si>
+    <t>37.825286</t>
+  </si>
+  <si>
+    <t>67.598500</t>
+  </si>
+  <si>
+    <t>Yangiobod sh., Sardoba tumani, Barkamol ko'chasi, 14 uy: г. Янгиабад, район Сардоба, улица Баркамол, дом 14</t>
+  </si>
+  <si>
+    <t>FrЯБД-1</t>
+  </si>
+  <si>
+    <t>40.270450</t>
+  </si>
+  <si>
+    <t>68.271593</t>
+  </si>
+  <si>
+    <t>Farg'ona sh., Ahmad Yassaviy ko'chasi, 39 а uy: г. Фергана, улица Ахмада Яссави, дом 39 а</t>
+  </si>
+  <si>
+    <t>FrФЕР-33</t>
+  </si>
+  <si>
+    <t>40.381401</t>
+  </si>
+  <si>
+    <t>71.802847</t>
   </si>
 </sst>
 </file>
@@ -8729,7 +8777,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1306"/>
+  <dimension ref="A1:D1310"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -27023,6 +27071,62 @@
         <v>2725</v>
       </c>
     </row>
+    <row r="1307" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1307" s="1" t="s">
+        <v>2726</v>
+      </c>
+      <c r="B1307" s="17" t="s">
+        <v>2727</v>
+      </c>
+      <c r="C1307" s="17" t="s">
+        <v>2728</v>
+      </c>
+      <c r="D1307" s="10" t="s">
+        <v>2729</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1308" s="1" t="s">
+        <v>2730</v>
+      </c>
+      <c r="B1308" s="17" t="s">
+        <v>2731</v>
+      </c>
+      <c r="C1308" s="17" t="s">
+        <v>2732</v>
+      </c>
+      <c r="D1308" s="10" t="s">
+        <v>2733</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1309" s="1" t="s">
+        <v>2734</v>
+      </c>
+      <c r="B1309" s="17" t="s">
+        <v>2735</v>
+      </c>
+      <c r="C1309" s="17" t="s">
+        <v>2736</v>
+      </c>
+      <c r="D1309" s="10" t="s">
+        <v>2737</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1310" s="1" t="s">
+        <v>2738</v>
+      </c>
+      <c r="B1310" s="17" t="s">
+        <v>2739</v>
+      </c>
+      <c r="C1310" s="17" t="s">
+        <v>2740</v>
+      </c>
+      <c r="D1310" s="10" t="s">
+        <v>2741</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Caplan\OneDrive\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274E1294-E2E5-40A0-A6DE-9F7818A59E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91613CB0-E373-485E-8FF3-07EBE3DE0C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1230" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2742" uniqueCount="2742">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2798" uniqueCount="2798">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -8277,6 +8277,174 @@
   </si>
   <si>
     <t>71.802847</t>
+  </si>
+  <si>
+    <t>Farg'ona sh., Tinchlik ko'chasi, 15 а uy: г. Фергана, улица Тинчлик, дом 15 а</t>
+  </si>
+  <si>
+    <t>FrФЕР-39</t>
+  </si>
+  <si>
+    <t>40.445262</t>
+  </si>
+  <si>
+    <t>71.758996</t>
+  </si>
+  <si>
+    <t>Farg'ona sh., Tarona ko'chasi, 17 uy: г. Фергана, улица Тарона, дом 17</t>
+  </si>
+  <si>
+    <t>FrФЕР-40</t>
+  </si>
+  <si>
+    <t>40.367736</t>
+  </si>
+  <si>
+    <t>71.807733</t>
+  </si>
+  <si>
+    <t>Farg'ona sh., Abdulla Qodiriy ko'chasi, 142/1 uy: г. Фергана, улица Абдуллы Кадыри, дом 142/1</t>
+  </si>
+  <si>
+    <t>FrФЕР-41</t>
+  </si>
+  <si>
+    <t>40.365137</t>
+  </si>
+  <si>
+    <t>71.846589</t>
+  </si>
+  <si>
+    <t>Yangiyer sh., Zahiridin Bobur ko'chasi, 68 uy: г. Янгиер, улица Захириддин Бобур, дом 68</t>
+  </si>
+  <si>
+    <t>FrЯНР-5</t>
+  </si>
+  <si>
+    <t>40.269663</t>
+  </si>
+  <si>
+    <t>68.792805</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Mirzo-Ulug'bek tumani, Temur Malik ko'chasi, 2g uy: г. Ташкент, Мирзо Улугбекский район, улица Тимура Малика, дом 2г</t>
+  </si>
+  <si>
+    <t>FrТАШ-358</t>
+  </si>
+  <si>
+    <t>41.348721</t>
+  </si>
+  <si>
+    <t>69.354990</t>
+  </si>
+  <si>
+    <t>Navoiy sh., Ibn Sino ko'chasi, 568 uy: г. Навои, улица Ибн Сино, дом 568</t>
+  </si>
+  <si>
+    <t>FrНАВ-23</t>
+  </si>
+  <si>
+    <t>40.091043</t>
+  </si>
+  <si>
+    <t>65.371796</t>
+  </si>
+  <si>
+    <t>Qarshi sh., Xonobod yo‘li ko'chasi, 19A uy: г. Карши, улица Хонобод йули, дом 19А</t>
+  </si>
+  <si>
+    <t>FrКРШ-27</t>
+  </si>
+  <si>
+    <t>38.830072</t>
+  </si>
+  <si>
+    <t>65.803053</t>
+  </si>
+  <si>
+    <t>Bekobod sh., Istiklol ko'chasi, 11 uy: г. Бекабад, улица Истиклол, дом 11</t>
+  </si>
+  <si>
+    <t>FrБЕК-8</t>
+  </si>
+  <si>
+    <t>40.217814</t>
+  </si>
+  <si>
+    <t>69.230751</t>
+  </si>
+  <si>
+    <t>Xalkobod sh., Xalqabod shoh ko'chasi, 43 uy: г. Халкабад, проспект Халкобод, дом 43</t>
+  </si>
+  <si>
+    <t>FrХЛБ-1</t>
+  </si>
+  <si>
+    <t>42.686428</t>
+  </si>
+  <si>
+    <t>59.727527</t>
+  </si>
+  <si>
+    <t>Vodiy sh., Denov tumani, Shifokorlar ko‘chasi, 56А uy : г. Водий, Денауский район, улица Шифокорлар, дом 56 А</t>
+  </si>
+  <si>
+    <t>FrВОД-1</t>
+  </si>
+  <si>
+    <t>38.321427</t>
+  </si>
+  <si>
+    <t>67.904949</t>
+  </si>
+  <si>
+    <t>Kangli sh., Jomboy tumani, Kangli qishlog ko‘chasi, 96 uy: г. Кангли, Джамбайский район, улица Кишлак Кангли, дом 96</t>
+  </si>
+  <si>
+    <t>FrКАН-1</t>
+  </si>
+  <si>
+    <t>39.780236</t>
+  </si>
+  <si>
+    <t>67.056848</t>
+  </si>
+  <si>
+    <t>Keles sh., Keles yo‘li ko'chasi, 180 uy: г. Келес, улица улица Келес йули, дом 180</t>
+  </si>
+  <si>
+    <t>FrКЕЛ-4</t>
+  </si>
+  <si>
+    <t>41.392315</t>
+  </si>
+  <si>
+    <t>69.206985</t>
+  </si>
+  <si>
+    <t>Chirchiq sh., 8 mikrorayon, 52/56 uy: г. Чирчик, 8 микрорайон, дом 52/56</t>
+  </si>
+  <si>
+    <t>FrЧИР-19</t>
+  </si>
+  <si>
+    <t>41.464525</t>
+  </si>
+  <si>
+    <t>69.552221</t>
+  </si>
+  <si>
+    <t>Samarqand sh.,Tong Yogdusi ko'chasi, 104 uy: г. Самарканд, улица Тонг Ёгдуси, дом 104</t>
+  </si>
+  <si>
+    <t>FrСМК-62</t>
+  </si>
+  <si>
+    <t>39.618029</t>
+  </si>
+  <si>
+    <t>66.997565</t>
   </si>
 </sst>
 </file>
@@ -8777,7 +8945,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1310"/>
+  <dimension ref="A1:D1324"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -27127,6 +27295,202 @@
         <v>2741</v>
       </c>
     </row>
+    <row r="1311" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1311" s="1" t="s">
+        <v>2742</v>
+      </c>
+      <c r="B1311" s="17" t="s">
+        <v>2743</v>
+      </c>
+      <c r="C1311" s="17" t="s">
+        <v>2744</v>
+      </c>
+      <c r="D1311" s="10" t="s">
+        <v>2745</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1312" s="1" t="s">
+        <v>2746</v>
+      </c>
+      <c r="B1312" s="17" t="s">
+        <v>2747</v>
+      </c>
+      <c r="C1312" s="17" t="s">
+        <v>2748</v>
+      </c>
+      <c r="D1312" s="10" t="s">
+        <v>2749</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1313" s="1" t="s">
+        <v>2750</v>
+      </c>
+      <c r="B1313" s="17" t="s">
+        <v>2751</v>
+      </c>
+      <c r="C1313" s="17" t="s">
+        <v>2752</v>
+      </c>
+      <c r="D1313" s="10" t="s">
+        <v>2753</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1314" s="7" t="s">
+        <v>2754</v>
+      </c>
+      <c r="B1314" s="17" t="s">
+        <v>2755</v>
+      </c>
+      <c r="C1314" s="19" t="s">
+        <v>2756</v>
+      </c>
+      <c r="D1314" s="10" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1315" s="7" t="s">
+        <v>2758</v>
+      </c>
+      <c r="B1315" s="17" t="s">
+        <v>2759</v>
+      </c>
+      <c r="C1315" s="19" t="s">
+        <v>2760</v>
+      </c>
+      <c r="D1315" s="10" t="s">
+        <v>2761</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1316" s="7" t="s">
+        <v>2762</v>
+      </c>
+      <c r="B1316" s="17" t="s">
+        <v>2763</v>
+      </c>
+      <c r="C1316" s="19" t="s">
+        <v>2764</v>
+      </c>
+      <c r="D1316" s="10" t="s">
+        <v>2765</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1317" s="7" t="s">
+        <v>2766</v>
+      </c>
+      <c r="B1317" s="17" t="s">
+        <v>2767</v>
+      </c>
+      <c r="C1317" s="19" t="s">
+        <v>2768</v>
+      </c>
+      <c r="D1317" s="10" t="s">
+        <v>2769</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1318" s="1" t="s">
+        <v>2770</v>
+      </c>
+      <c r="B1318" s="17" t="s">
+        <v>2771</v>
+      </c>
+      <c r="C1318" s="17" t="s">
+        <v>2772</v>
+      </c>
+      <c r="D1318" s="10" t="s">
+        <v>2773</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1319" s="7" t="s">
+        <v>2774</v>
+      </c>
+      <c r="B1319" s="17" t="s">
+        <v>2775</v>
+      </c>
+      <c r="C1319" s="19" t="s">
+        <v>2776</v>
+      </c>
+      <c r="D1319" s="10" t="s">
+        <v>2777</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1320" s="7" t="s">
+        <v>2778</v>
+      </c>
+      <c r="B1320" s="17" t="s">
+        <v>2779</v>
+      </c>
+      <c r="C1320" s="19" t="s">
+        <v>2780</v>
+      </c>
+      <c r="D1320" s="10" t="s">
+        <v>2781</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1321" s="7" t="s">
+        <v>2782</v>
+      </c>
+      <c r="B1321" s="17" t="s">
+        <v>2783</v>
+      </c>
+      <c r="C1321" s="19" t="s">
+        <v>2784</v>
+      </c>
+      <c r="D1321" s="10" t="s">
+        <v>2785</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1322" s="7" t="s">
+        <v>2786</v>
+      </c>
+      <c r="B1322" s="17" t="s">
+        <v>2787</v>
+      </c>
+      <c r="C1322" s="19" t="s">
+        <v>2788</v>
+      </c>
+      <c r="D1322" s="10" t="s">
+        <v>2789</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1323" s="8" t="s">
+        <v>2790</v>
+      </c>
+      <c r="B1323" s="18" t="s">
+        <v>2791</v>
+      </c>
+      <c r="C1323" s="18" t="s">
+        <v>2792</v>
+      </c>
+      <c r="D1323" s="10" t="s">
+        <v>2793</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1324" s="8" t="s">
+        <v>2794</v>
+      </c>
+      <c r="B1324" s="18" t="s">
+        <v>2795</v>
+      </c>
+      <c r="C1324" s="18" t="s">
+        <v>2796</v>
+      </c>
+      <c r="D1324" s="10" t="s">
+        <v>2797</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Caplan\OneDrive\Desktop\PVZ_BOT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7b1c8268b11fc464/Desktop/PVZ_BOT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91613CB0-E373-485E-8FF3-07EBE3DE0C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{91613CB0-E373-485E-8FF3-07EBE3DE0C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C2DEE7A-8799-4A6E-A151-C11C18941A76}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2798" uniqueCount="2798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2830" uniqueCount="2830">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -8445,6 +8445,102 @@
   </si>
   <si>
     <t>66.997565</t>
+  </si>
+  <si>
+    <t>Nukus sh., Allayar Dosnazarov ko‘chasi, 85A uy: г. Нукус, улица Аллаяра Досназарова, дом 85а</t>
+  </si>
+  <si>
+    <t>FrНУК-17</t>
+  </si>
+  <si>
+    <t>42.460473</t>
+  </si>
+  <si>
+    <t>59.620900</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Yashnobod tumani, Qorasu ko'chasi, 27 uy: г. Ташкент, Яшнабадский район, улица Карасу, дом 27</t>
+  </si>
+  <si>
+    <t>FrТАШ-357</t>
+  </si>
+  <si>
+    <t>41.295155</t>
+  </si>
+  <si>
+    <t>69.340587</t>
+  </si>
+  <si>
+    <t>Termiz sh., Denov ko'chasi, 57 a uy: г. Термез, улица Денов, дом 57 а</t>
+  </si>
+  <si>
+    <t>FrТЕР-23</t>
+  </si>
+  <si>
+    <t>37.232714</t>
+  </si>
+  <si>
+    <t>67.284426</t>
+  </si>
+  <si>
+    <t>Chirchiq sh., Amir Temur shoh ko'chasi, 106 uy: г. Чирчик, проспект Амира Темура, дом 106</t>
+  </si>
+  <si>
+    <t>FrЧИР-20</t>
+  </si>
+  <si>
+    <t>41.472964</t>
+  </si>
+  <si>
+    <t>69.573818</t>
+  </si>
+  <si>
+    <t>G‘ijduvon sh., Fayzullo Xoʻjayev ko'chasi, 46 uy: г. Гиждуван, улица Файзулло Ходжаева, дом 46</t>
+  </si>
+  <si>
+    <t>FrГЖД-6</t>
+  </si>
+  <si>
+    <t>40.111945</t>
+  </si>
+  <si>
+    <t>64.678487</t>
+  </si>
+  <si>
+    <t>Olmaliq sh., Mustagilik ko'chasi, 66 uy: г. Алмалык, улица Мустакиллик, дом 66</t>
+  </si>
+  <si>
+    <t>FrАЛМ-13</t>
+  </si>
+  <si>
+    <t>40.874836</t>
+  </si>
+  <si>
+    <t>69.597307</t>
+  </si>
+  <si>
+    <t>Samarqand sh., Movorounnaxr ko'chasi, 24 uy: г. Самарканд, улица Моворуннахр, дом 24</t>
+  </si>
+  <si>
+    <t>FrСМК-44</t>
+  </si>
+  <si>
+    <t>39.687384</t>
+  </si>
+  <si>
+    <t>66.880084</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Yakkasaroy tumani, Bobur ko'chasi, 67/10 uy: г. Ташкент, Яккасарайский район, улица Бабура, дом 67/10</t>
+  </si>
+  <si>
+    <t>FrТАШ-361</t>
+  </si>
+  <si>
+    <t>41.277957</t>
+  </si>
+  <si>
+    <t>69.258308</t>
   </si>
 </sst>
 </file>
@@ -8945,7 +9041,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1324"/>
+  <dimension ref="A1:D1332"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -27491,6 +27587,118 @@
         <v>2797</v>
       </c>
     </row>
+    <row r="1325" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1325" s="1" t="s">
+        <v>2798</v>
+      </c>
+      <c r="B1325" s="17" t="s">
+        <v>2799</v>
+      </c>
+      <c r="C1325" s="17" t="s">
+        <v>2800</v>
+      </c>
+      <c r="D1325" s="10" t="s">
+        <v>2801</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1326" s="7" t="s">
+        <v>2802</v>
+      </c>
+      <c r="B1326" s="17" t="s">
+        <v>2803</v>
+      </c>
+      <c r="C1326" s="19" t="s">
+        <v>2804</v>
+      </c>
+      <c r="D1326" s="10" t="s">
+        <v>2805</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1327" s="7" t="s">
+        <v>2806</v>
+      </c>
+      <c r="B1327" s="17" t="s">
+        <v>2807</v>
+      </c>
+      <c r="C1327" s="19" t="s">
+        <v>2808</v>
+      </c>
+      <c r="D1327" s="10" t="s">
+        <v>2809</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1328" s="7" t="s">
+        <v>2810</v>
+      </c>
+      <c r="B1328" s="17" t="s">
+        <v>2811</v>
+      </c>
+      <c r="C1328" s="19" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1328" s="10" t="s">
+        <v>2813</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1329" s="1" t="s">
+        <v>2814</v>
+      </c>
+      <c r="B1329" s="17" t="s">
+        <v>2815</v>
+      </c>
+      <c r="C1329" s="17" t="s">
+        <v>2816</v>
+      </c>
+      <c r="D1329" s="10" t="s">
+        <v>2817</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1330" s="1" t="s">
+        <v>2818</v>
+      </c>
+      <c r="B1330" s="17" t="s">
+        <v>2819</v>
+      </c>
+      <c r="C1330" s="17" t="s">
+        <v>2820</v>
+      </c>
+      <c r="D1330" s="10" t="s">
+        <v>2821</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1331" s="1" t="s">
+        <v>2822</v>
+      </c>
+      <c r="B1331" s="17" t="s">
+        <v>2823</v>
+      </c>
+      <c r="C1331" s="17" t="s">
+        <v>2824</v>
+      </c>
+      <c r="D1331" s="10" t="s">
+        <v>2825</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1332" s="1" t="s">
+        <v>2826</v>
+      </c>
+      <c r="B1332" s="17" t="s">
+        <v>2827</v>
+      </c>
+      <c r="C1332" s="17" t="s">
+        <v>2828</v>
+      </c>
+      <c r="D1332" s="10" t="s">
+        <v>2829</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7b1c8268b11fc464/Desktop/PVZ_BOT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{91613CB0-E373-485E-8FF3-07EBE3DE0C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C2DEE7A-8799-4A6E-A151-C11C18941A76}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{91613CB0-E373-485E-8FF3-07EBE3DE0C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{799F0575-7CA3-4CDD-8025-27E0DD312FEE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2830" uniqueCount="2830">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2850" uniqueCount="2850">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -8541,6 +8541,66 @@
   </si>
   <si>
     <t>69.258308</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Shayxontohur tumani, Qurilish ko'chasi, 9 uy: г. Ташкент, Шайхантахурский район, улица Курилиш, дом 9</t>
+  </si>
+  <si>
+    <t>FrТАШ-354</t>
+  </si>
+  <si>
+    <t>41.303866</t>
+  </si>
+  <si>
+    <t>69.214803</t>
+  </si>
+  <si>
+    <t>Toshloq sh., Xotinqumi MFY, Alisher Navoiy ko'chasi, 23 uy: г. Ташлак, МСГ Хотинкуми, улица Алишера Навои, дом 23</t>
+  </si>
+  <si>
+    <t>FrТЛК-3</t>
+  </si>
+  <si>
+    <t>40.492847</t>
+  </si>
+  <si>
+    <t>71.785760</t>
+  </si>
+  <si>
+    <t>Quva sh., Qayqubbod ko'chasi, 33 uy: г. Кува, улица Кайкуббод, дом 33</t>
+  </si>
+  <si>
+    <t>FrКВА-3</t>
+  </si>
+  <si>
+    <t>40.540944</t>
+  </si>
+  <si>
+    <t>72.067546</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Mirzo Ulug'bek tumani, Xumoyun mavzesi, 10 uy: г. Ташкент, Мирзо Улугбекский район, массив Хумаюн, дом 10</t>
+  </si>
+  <si>
+    <t>FrТАШ-364</t>
+  </si>
+  <si>
+    <t>41.342575</t>
+  </si>
+  <si>
+    <t>69.386001</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Chilonzor tumani, Arnasoy ko‘chasi, 9a uy: г. Ташкент, Чиланзарский район, улица Арнасай , 9а дом</t>
+  </si>
+  <si>
+    <t>FrТАШ-337</t>
+  </si>
+  <si>
+    <t>41.271183</t>
+  </si>
+  <si>
+    <t>69.221482</t>
   </si>
 </sst>
 </file>
@@ -9041,7 +9101,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1332"/>
+  <dimension ref="A1:D1337"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -27699,6 +27759,76 @@
         <v>2829</v>
       </c>
     </row>
+    <row r="1333" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1333" s="1" t="s">
+        <v>2830</v>
+      </c>
+      <c r="B1333" s="18" t="s">
+        <v>2831</v>
+      </c>
+      <c r="C1333" s="17" t="s">
+        <v>2832</v>
+      </c>
+      <c r="D1333" s="10" t="s">
+        <v>2833</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1334" s="1" t="s">
+        <v>2834</v>
+      </c>
+      <c r="B1334" s="18" t="s">
+        <v>2835</v>
+      </c>
+      <c r="C1334" s="17" t="s">
+        <v>2836</v>
+      </c>
+      <c r="D1334" s="10" t="s">
+        <v>2837</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1335" s="1" t="s">
+        <v>2838</v>
+      </c>
+      <c r="B1335" s="18" t="s">
+        <v>2839</v>
+      </c>
+      <c r="C1335" s="17" t="s">
+        <v>2840</v>
+      </c>
+      <c r="D1335" s="10" t="s">
+        <v>2841</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1336" s="1" t="s">
+        <v>2842</v>
+      </c>
+      <c r="B1336" s="18" t="s">
+        <v>2843</v>
+      </c>
+      <c r="C1336" s="17" t="s">
+        <v>2844</v>
+      </c>
+      <c r="D1336" s="10" t="s">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1337" s="1" t="s">
+        <v>2846</v>
+      </c>
+      <c r="B1337" s="18" t="s">
+        <v>2847</v>
+      </c>
+      <c r="C1337" s="17" t="s">
+        <v>2848</v>
+      </c>
+      <c r="D1337" s="10" t="s">
+        <v>2849</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7b1c8268b11fc464/Desktop/PVZ_BOT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{91613CB0-E373-485E-8FF3-07EBE3DE0C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{799F0575-7CA3-4CDD-8025-27E0DD312FEE}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{91613CB0-E373-485E-8FF3-07EBE3DE0C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E53FAA9-7575-427B-943F-5CD8C476DFE6}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2850" uniqueCount="2850">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2862" uniqueCount="2862">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -8601,6 +8601,42 @@
   </si>
   <si>
     <t>69.221482</t>
+  </si>
+  <si>
+    <t>To'rtko'l sh., Turtko'l tumani, Qozog'iston ko‘chasi, 5/5 uy: г. Турткуль, Турткульский район, улица Козогистон, дом 5/5</t>
+  </si>
+  <si>
+    <t>FrТРТ-5</t>
+  </si>
+  <si>
+    <t>41.548432</t>
+  </si>
+  <si>
+    <t>61.026050</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Mirobod tumani, Nukus ko'chasi, 3 uy: г. Ташкент, Мирабадский район, улица Нукус, дом 3</t>
+  </si>
+  <si>
+    <t>FrТАШ-363</t>
+  </si>
+  <si>
+    <t>41.299190</t>
+  </si>
+  <si>
+    <t>69.290758</t>
+  </si>
+  <si>
+    <t>Shamaton sh., Shamaton qishlog'i, 809 uy: г. Шаматан, кишлак Шаматан, дом 809</t>
+  </si>
+  <si>
+    <t>FrШМТ-1</t>
+  </si>
+  <si>
+    <t>39.058651</t>
+  </si>
+  <si>
+    <t>66.773051</t>
   </si>
 </sst>
 </file>
@@ -9101,7 +9137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1337"/>
+  <dimension ref="A1:D1340"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -27829,6 +27865,48 @@
         <v>2849</v>
       </c>
     </row>
+    <row r="1338" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1338" s="7" t="s">
+        <v>2850</v>
+      </c>
+      <c r="B1338" s="17" t="s">
+        <v>2851</v>
+      </c>
+      <c r="C1338" s="19" t="s">
+        <v>2852</v>
+      </c>
+      <c r="D1338" s="10" t="s">
+        <v>2853</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1339" s="7" t="s">
+        <v>2854</v>
+      </c>
+      <c r="B1339" s="17" t="s">
+        <v>2855</v>
+      </c>
+      <c r="C1339" s="19" t="s">
+        <v>2856</v>
+      </c>
+      <c r="D1339" s="10" t="s">
+        <v>2857</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1340" s="7" t="s">
+        <v>2858</v>
+      </c>
+      <c r="B1340" s="17" t="s">
+        <v>2859</v>
+      </c>
+      <c r="C1340" s="19" t="s">
+        <v>2860</v>
+      </c>
+      <c r="D1340" s="10" t="s">
+        <v>2861</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7b1c8268b11fc464/Desktop/PVZ_BOT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{91613CB0-E373-485E-8FF3-07EBE3DE0C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E53FAA9-7575-427B-943F-5CD8C476DFE6}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{91613CB0-E373-485E-8FF3-07EBE3DE0C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB663A0D-91FF-4A03-A113-CF596BDE2A60}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2862" uniqueCount="2862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2886" uniqueCount="2886">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -8637,6 +8637,78 @@
   </si>
   <si>
     <t>66.773051</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Mirzo Ulug'bek tumani, Buyuk Ipak Yo'li mavzesi, 8 uy: г. Ташкент, Мирзо Улугбекский район, массив Буюк Ипак Йули, 8 дом</t>
+  </si>
+  <si>
+    <t>FrТАШ-359</t>
+  </si>
+  <si>
+    <t>41.314706</t>
+  </si>
+  <si>
+    <t>69.289476</t>
+  </si>
+  <si>
+    <t>Yangiyo'l sh., Samarqand ko'chasi, 34 v uy: г. Янгиюль, Самаркандская улица, дом 34 в</t>
+  </si>
+  <si>
+    <t>FrЯНГ-14</t>
+  </si>
+  <si>
+    <t>41.133037</t>
+  </si>
+  <si>
+    <t>69.073877</t>
+  </si>
+  <si>
+    <t>Yangibozor sh., Peshku tumani, O‘g‘lon MFY, Gulxalon ko'chasi, 32 a uy: г. Янгибазар, Пешкунский район, МСГ Оглон, улица Гулхалон, дом 32 а</t>
+  </si>
+  <si>
+    <t>FrЯНЗ-3</t>
+  </si>
+  <si>
+    <t>40.046566</t>
+  </si>
+  <si>
+    <t>64.328450</t>
+  </si>
+  <si>
+    <t>Uzun sh., Uzun tumani, Beklar ko'chasi, 51 uy: г. Узун, Узунский район, улица Беклар, дом 51</t>
+  </si>
+  <si>
+    <t>FrУЗУ-2</t>
+  </si>
+  <si>
+    <t>38.358268</t>
+  </si>
+  <si>
+    <t>68.007537</t>
+  </si>
+  <si>
+    <t>Samarqand sh., Abu Bakr Roziy ko'chasi, 7 a uy: г. Самарканд , улица Абу Бакр Рози, дом 7 а</t>
+  </si>
+  <si>
+    <t>FrСМК-65</t>
+  </si>
+  <si>
+    <t>39.661105</t>
+  </si>
+  <si>
+    <t>66.913865</t>
+  </si>
+  <si>
+    <t>Yakkabog' sh., Nishon ko'chasi, 24 uy: г. Яккабаг, улица Нишон, дом 24</t>
+  </si>
+  <si>
+    <t>FrЯКК-6</t>
+  </si>
+  <si>
+    <t>38.935819</t>
+  </si>
+  <si>
+    <t>66.833201</t>
   </si>
 </sst>
 </file>
@@ -9137,7 +9209,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1340"/>
+  <dimension ref="A1:D1346"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -27907,6 +27979,90 @@
         <v>2861</v>
       </c>
     </row>
+    <row r="1341" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1341" s="1" t="s">
+        <v>2862</v>
+      </c>
+      <c r="B1341" s="17" t="s">
+        <v>2863</v>
+      </c>
+      <c r="C1341" s="17" t="s">
+        <v>2864</v>
+      </c>
+      <c r="D1341" s="10" t="s">
+        <v>2865</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1342" s="7" t="s">
+        <v>2866</v>
+      </c>
+      <c r="B1342" s="17" t="s">
+        <v>2867</v>
+      </c>
+      <c r="C1342" s="19" t="s">
+        <v>2868</v>
+      </c>
+      <c r="D1342" s="10" t="s">
+        <v>2869</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1343" s="7" t="s">
+        <v>2870</v>
+      </c>
+      <c r="B1343" s="17" t="s">
+        <v>2871</v>
+      </c>
+      <c r="C1343" s="19" t="s">
+        <v>2872</v>
+      </c>
+      <c r="D1343" s="10" t="s">
+        <v>2873</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1344" s="7" t="s">
+        <v>2874</v>
+      </c>
+      <c r="B1344" s="17" t="s">
+        <v>2875</v>
+      </c>
+      <c r="C1344" s="19" t="s">
+        <v>2876</v>
+      </c>
+      <c r="D1344" s="10" t="s">
+        <v>2877</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1345" s="7" t="s">
+        <v>2878</v>
+      </c>
+      <c r="B1345" s="17" t="s">
+        <v>2879</v>
+      </c>
+      <c r="C1345" s="19" t="s">
+        <v>2880</v>
+      </c>
+      <c r="D1345" s="10" t="s">
+        <v>2881</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1346" s="7" t="s">
+        <v>2882</v>
+      </c>
+      <c r="B1346" s="18" t="s">
+        <v>2883</v>
+      </c>
+      <c r="C1346" s="19" t="s">
+        <v>2884</v>
+      </c>
+      <c r="D1346" s="10" t="s">
+        <v>2885</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7b1c8268b11fc464/Desktop/PVZ_BOT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{91613CB0-E373-485E-8FF3-07EBE3DE0C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB663A0D-91FF-4A03-A113-CF596BDE2A60}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{91613CB0-E373-485E-8FF3-07EBE3DE0C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A09CD3DD-F3E6-4C85-BC08-8F09890761A2}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2886" uniqueCount="2886">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2906" uniqueCount="2906">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -8709,6 +8709,66 @@
   </si>
   <si>
     <t>66.833201</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Yashnobod tumani, 3 mavze, 7 uy: г. Ташкент, Яшнабадский район, 3 квартал, дом 7</t>
+  </si>
+  <si>
+    <t>FrТАШ-366</t>
+  </si>
+  <si>
+    <t>41.287226</t>
+  </si>
+  <si>
+    <t>69.338099</t>
+  </si>
+  <si>
+    <t>Xanka sh., Andalib ko'chasi, 34 a uy: г. Ханка, улица Андалиб, дом 34 а</t>
+  </si>
+  <si>
+    <t>FrХНК-4</t>
+  </si>
+  <si>
+    <t>41.478376</t>
+  </si>
+  <si>
+    <t>60.773137</t>
+  </si>
+  <si>
+    <t>Qorashin sh., Oydin yoʻl ko'chasi, 271 uy: г. Карашина, улица Ойдин Йули, дом 271</t>
+  </si>
+  <si>
+    <t>FrКШН-3</t>
+  </si>
+  <si>
+    <t>38.337800</t>
+  </si>
+  <si>
+    <t>66.576119</t>
+  </si>
+  <si>
+    <t>Toshloq sh., Furkat MFY, Mehnat ko'chasi, 31 uy: г. Ташлак, МСГ Фуркат, улица Мехнат, дом 31</t>
+  </si>
+  <si>
+    <t>FrТЛК-2</t>
+  </si>
+  <si>
+    <t>40.485561</t>
+  </si>
+  <si>
+    <t>71.755090</t>
+  </si>
+  <si>
+    <t>G‘ijduvon sh., Fayzullo Xoʻjayev ko'chasi, 328 uy: г. Гиждуван, улица Файзулла Ходжаев, дом 328</t>
+  </si>
+  <si>
+    <t>FrГЖД-5</t>
+  </si>
+  <si>
+    <t>40.107276</t>
+  </si>
+  <si>
+    <t>64.673415</t>
   </si>
 </sst>
 </file>
@@ -9209,7 +9269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1346"/>
+  <dimension ref="A1:D1351"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -28063,6 +28123,76 @@
         <v>2885</v>
       </c>
     </row>
+    <row r="1347" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1347" s="7" t="s">
+        <v>2886</v>
+      </c>
+      <c r="B1347" s="19" t="s">
+        <v>2887</v>
+      </c>
+      <c r="C1347" s="19" t="s">
+        <v>2888</v>
+      </c>
+      <c r="D1347" s="10" t="s">
+        <v>2889</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1348" s="7" t="s">
+        <v>2890</v>
+      </c>
+      <c r="B1348" s="19" t="s">
+        <v>2891</v>
+      </c>
+      <c r="C1348" s="19" t="s">
+        <v>2892</v>
+      </c>
+      <c r="D1348" s="10" t="s">
+        <v>2893</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1349" s="7" t="s">
+        <v>2894</v>
+      </c>
+      <c r="B1349" s="19" t="s">
+        <v>2895</v>
+      </c>
+      <c r="C1349" s="19" t="s">
+        <v>2896</v>
+      </c>
+      <c r="D1349" s="10" t="s">
+        <v>2897</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1350" s="7" t="s">
+        <v>2898</v>
+      </c>
+      <c r="B1350" s="19" t="s">
+        <v>2899</v>
+      </c>
+      <c r="C1350" s="19" t="s">
+        <v>2900</v>
+      </c>
+      <c r="D1350" s="10" t="s">
+        <v>2901</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1351" s="7" t="s">
+        <v>2902</v>
+      </c>
+      <c r="B1351" s="19" t="s">
+        <v>2903</v>
+      </c>
+      <c r="C1351" s="19" t="s">
+        <v>2904</v>
+      </c>
+      <c r="D1351" s="10" t="s">
+        <v>2905</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7b1c8268b11fc464/Desktop/PVZ_BOT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Azizbek\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{91613CB0-E373-485E-8FF3-07EBE3DE0C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A09CD3DD-F3E6-4C85-BC08-8F09890761A2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79B27AB-4DC2-46B1-AF5A-B3C7D3405329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="645" windowWidth="12555" windowHeight="15555" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2906" uniqueCount="2906">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2910" uniqueCount="2910">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -8769,6 +8769,18 @@
   </si>
   <si>
     <t>64.673415</t>
+  </si>
+  <si>
+    <t>Sirdaryo sh., Sharq ko'chasi, 5 uy: г. Сырдарья, улица Шарк, дом 5</t>
+  </si>
+  <si>
+    <t>FrСРД-4</t>
+  </si>
+  <si>
+    <t>40.820917</t>
+  </si>
+  <si>
+    <t>68.680055</t>
   </si>
 </sst>
 </file>
@@ -9269,7 +9281,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1351"/>
+  <dimension ref="A1:D1352"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -28193,6 +28205,20 @@
         <v>2905</v>
       </c>
     </row>
+    <row r="1352" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1352" s="1" t="s">
+        <v>2906</v>
+      </c>
+      <c r="B1352" s="18" t="s">
+        <v>2907</v>
+      </c>
+      <c r="C1352" s="17" t="s">
+        <v>2908</v>
+      </c>
+      <c r="D1352" s="10" t="s">
+        <v>2909</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Azizbek\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79B27AB-4DC2-46B1-AF5A-B3C7D3405329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{621407A3-B092-4B08-AF8F-6A1CF1B006A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="645" windowWidth="12555" windowHeight="15555" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2910" uniqueCount="2910">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2942" uniqueCount="2942">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -8781,6 +8781,102 @@
   </si>
   <si>
     <t>68.680055</t>
+  </si>
+  <si>
+    <t>Jiydakapa sh., Uichi ko'chasi, 50 uy: г. Джидакапа, улица Уйчи, дом 50</t>
+  </si>
+  <si>
+    <t>FrДЖП-1</t>
+  </si>
+  <si>
+    <t>40.955646</t>
+  </si>
+  <si>
+    <t>71.811322</t>
+  </si>
+  <si>
+    <t>Toshkent shahar, Uchtepa tumani, Foziltepa MFY, Izza kochasi, 53-uy</t>
+  </si>
+  <si>
+    <t>FrТАШ-353</t>
+  </si>
+  <si>
+    <t>41.281150</t>
+  </si>
+  <si>
+    <t>69.154853</t>
+  </si>
+  <si>
+    <t>Toshkent shahri, Mirzo ulug'bek tumani, Lashkarbegi MFY, Mustaqillik shoh ko'chasi, 65-uy</t>
+  </si>
+  <si>
+    <t>FrТАШ-356</t>
+  </si>
+  <si>
+    <t>41.319716</t>
+  </si>
+  <si>
+    <t>69.297988</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Chilonzor tumani, 5 mavze, 24 mavzesi: г. Ташкент, Чиланзарский район, квартал 5, 24 массив</t>
+  </si>
+  <si>
+    <t>FrТАШ-365</t>
+  </si>
+  <si>
+    <t>41.295488</t>
+  </si>
+  <si>
+    <t>69.217177</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Shayxontoxur tumani, Jarariq mavzesi, 2 uy: г. Ташкент, Шайхантахурский район, массив Джарарык, дом 2</t>
+  </si>
+  <si>
+    <t>FrТАШ-362</t>
+  </si>
+  <si>
+    <t>41.339138</t>
+  </si>
+  <si>
+    <t>69.177322</t>
+  </si>
+  <si>
+    <t>Samarqand sh., Katta O‘zbek Trakti ko'chasi, 8 "B" uy: г. Самарканд, улица Катта Узбек тракт, дом 8 "Б"</t>
+  </si>
+  <si>
+    <t>FrСМК-66</t>
+  </si>
+  <si>
+    <t>39.677929</t>
+  </si>
+  <si>
+    <t>67.006087</t>
+  </si>
+  <si>
+    <t>Urganch sh., Al-Xorazmiy ko'chasi, 137/1 uy: г. Ургенч, улица Аль-Хорезми, дом 137/1</t>
+  </si>
+  <si>
+    <t>FrУРГ-26</t>
+  </si>
+  <si>
+    <t>41.576083</t>
+  </si>
+  <si>
+    <t>60.629658</t>
+  </si>
+  <si>
+    <t>G‘azalkent sh., Birlik ko'chasi, 85 uy: г. Газалкент, улица Бирлик, дом 85</t>
+  </si>
+  <si>
+    <t>FrГАЗ-5</t>
+  </si>
+  <si>
+    <t>41.563630</t>
+  </si>
+  <si>
+    <t>69.779669</t>
   </si>
 </sst>
 </file>
@@ -8848,7 +8944,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -8938,11 +9034,78 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -9000,6 +9163,25 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9281,7 +9463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1352"/>
+  <dimension ref="A1:D1360"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -28219,6 +28401,118 @@
         <v>2909</v>
       </c>
     </row>
+    <row r="1353" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1353" s="20" t="s">
+        <v>2910</v>
+      </c>
+      <c r="B1353" s="21" t="s">
+        <v>2911</v>
+      </c>
+      <c r="C1353" s="22" t="s">
+        <v>2912</v>
+      </c>
+      <c r="D1353" s="10" t="s">
+        <v>2913</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1354" s="23" t="s">
+        <v>2914</v>
+      </c>
+      <c r="B1354" s="25" t="s">
+        <v>2915</v>
+      </c>
+      <c r="C1354" s="24" t="s">
+        <v>2916</v>
+      </c>
+      <c r="D1354" s="10" t="s">
+        <v>2917</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1355" s="26" t="s">
+        <v>2918</v>
+      </c>
+      <c r="B1355" s="25" t="s">
+        <v>2919</v>
+      </c>
+      <c r="C1355" s="25" t="s">
+        <v>2920</v>
+      </c>
+      <c r="D1355" s="10" t="s">
+        <v>2921</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1356" s="7" t="s">
+        <v>2922</v>
+      </c>
+      <c r="B1356" s="18" t="s">
+        <v>2923</v>
+      </c>
+      <c r="C1356" s="19" t="s">
+        <v>2924</v>
+      </c>
+      <c r="D1356" s="10" t="s">
+        <v>2925</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1357" s="7" t="s">
+        <v>2926</v>
+      </c>
+      <c r="B1357" s="18" t="s">
+        <v>2927</v>
+      </c>
+      <c r="C1357" s="19" t="s">
+        <v>2928</v>
+      </c>
+      <c r="D1357" s="10" t="s">
+        <v>2929</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1358" s="1" t="s">
+        <v>2930</v>
+      </c>
+      <c r="B1358" s="18" t="s">
+        <v>2931</v>
+      </c>
+      <c r="C1358" s="17" t="s">
+        <v>2932</v>
+      </c>
+      <c r="D1358" s="10" t="s">
+        <v>2933</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1359" s="1" t="s">
+        <v>2934</v>
+      </c>
+      <c r="B1359" s="18" t="s">
+        <v>2935</v>
+      </c>
+      <c r="C1359" s="17" t="s">
+        <v>2936</v>
+      </c>
+      <c r="D1359" s="10" t="s">
+        <v>2937</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1360" s="7" t="s">
+        <v>2938</v>
+      </c>
+      <c r="B1360" s="18" t="s">
+        <v>2939</v>
+      </c>
+      <c r="C1360" s="19" t="s">
+        <v>2940</v>
+      </c>
+      <c r="D1360" s="10" t="s">
+        <v>2941</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Azizbek\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{621407A3-B092-4B08-AF8F-6A1CF1B006A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{298F5771-802E-4F8D-9F8A-B6EA3EB2D1E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2942" uniqueCount="2942">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2966" uniqueCount="2966">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -8877,6 +8877,78 @@
   </si>
   <si>
     <t>69.779669</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Mirobod tumani, Munis ko'chasi , 9 uy: г. Ташкент , Мирабадский район, улица Мунис, дом 9</t>
+  </si>
+  <si>
+    <t>FrТАШ-368</t>
+  </si>
+  <si>
+    <t>69.322371</t>
+  </si>
+  <si>
+    <t>41.243964</t>
+  </si>
+  <si>
+    <t>Samarqand sh., Mirzo Ulugʻbek MFY, Gulobod ko'chasi, 65 uy: г. Самарканд, МСГ Мирзо Улугбек, улица Гульабад, дом 65</t>
+  </si>
+  <si>
+    <t>FrСМК-64</t>
+  </si>
+  <si>
+    <t>39.624843</t>
+  </si>
+  <si>
+    <t>66.956820</t>
+  </si>
+  <si>
+    <t>Bo'ka sh., Bobur Mirzo ko'chasi, 24 uy: г. Бука, улица Бобур Мирзо, дом 24</t>
+  </si>
+  <si>
+    <t>FrБУК-4</t>
+  </si>
+  <si>
+    <t>40.810526</t>
+  </si>
+  <si>
+    <t>69.206301</t>
+  </si>
+  <si>
+    <t>Yangi Chinoz sh., Chinoz tumani, Navro‘z ko'chasi, 20 uy: г. Янги Чиназ, Чиназский район, улица Навруз, дом 20</t>
+  </si>
+  <si>
+    <t>FrЯЧН-1</t>
+  </si>
+  <si>
+    <t>40.909544</t>
+  </si>
+  <si>
+    <t>68.708088</t>
+  </si>
+  <si>
+    <t>Yallama sh.,Chinoz tumani, Beshchinor ko'chasi, 3 uy: г. Яллама, Чиноз район, улица Бешчинар, дом 3</t>
+  </si>
+  <si>
+    <t>FrЯЛМ-1</t>
+  </si>
+  <si>
+    <t>40.958084</t>
+  </si>
+  <si>
+    <t>68.737732</t>
+  </si>
+  <si>
+    <t>Denov sh., Sharof Rashidov ko'chasi, 258 uy: г. Денау, улица Шарофа Рашидова, дом 258</t>
+  </si>
+  <si>
+    <t>FrДЕН-5</t>
+  </si>
+  <si>
+    <t>38.272660</t>
+  </si>
+  <si>
+    <t>67.895260</t>
   </si>
 </sst>
 </file>
@@ -9463,7 +9535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1360"/>
+  <dimension ref="A1:D1366"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -28513,6 +28585,90 @@
         <v>2941</v>
       </c>
     </row>
+    <row r="1361" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1361" s="7" t="s">
+        <v>2942</v>
+      </c>
+      <c r="B1361" s="17" t="s">
+        <v>2943</v>
+      </c>
+      <c r="C1361" s="19" t="s">
+        <v>2945</v>
+      </c>
+      <c r="D1361" s="10" t="s">
+        <v>2944</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1362" s="7" t="s">
+        <v>2946</v>
+      </c>
+      <c r="B1362" s="17" t="s">
+        <v>2947</v>
+      </c>
+      <c r="C1362" s="19" t="s">
+        <v>2948</v>
+      </c>
+      <c r="D1362" s="10" t="s">
+        <v>2949</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1363" s="7" t="s">
+        <v>2950</v>
+      </c>
+      <c r="B1363" s="17" t="s">
+        <v>2951</v>
+      </c>
+      <c r="C1363" s="19" t="s">
+        <v>2952</v>
+      </c>
+      <c r="D1363" s="10" t="s">
+        <v>2953</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1364" s="7" t="s">
+        <v>2954</v>
+      </c>
+      <c r="B1364" s="17" t="s">
+        <v>2955</v>
+      </c>
+      <c r="C1364" s="19" t="s">
+        <v>2956</v>
+      </c>
+      <c r="D1364" s="10" t="s">
+        <v>2957</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1365" s="7" t="s">
+        <v>2958</v>
+      </c>
+      <c r="B1365" s="17" t="s">
+        <v>2959</v>
+      </c>
+      <c r="C1365" s="19" t="s">
+        <v>2960</v>
+      </c>
+      <c r="D1365" s="10" t="s">
+        <v>2961</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1366" s="7" t="s">
+        <v>2962</v>
+      </c>
+      <c r="B1366" s="17" t="s">
+        <v>2963</v>
+      </c>
+      <c r="C1366" s="19" t="s">
+        <v>2964</v>
+      </c>
+      <c r="D1366" s="10" t="s">
+        <v>2965</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Azizbek\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77F061C9-CFAF-468C-92D2-1B6114D13B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E01BB568-1998-4CB2-9583-9802639560A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="45" yWindow="1815" windowWidth="20190" windowHeight="12600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3042" uniqueCount="3040">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3074" uniqueCount="3072">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -9171,6 +9171,102 @@
   </si>
   <si>
     <t>Toshkent sh., Yakkasaroy tumani, Boshlik dahasi, 25 a uy: г. Ташкент, Яккасарайский район , массив Башлык , дом 5 а. Oq yo'l😄</t>
+  </si>
+  <si>
+    <t>FrСЛБ-1</t>
+  </si>
+  <si>
+    <t>Адрес:  г. Султанабад, Кургантепинский район, улица Жаннат бог, 311 дом</t>
+  </si>
+  <si>
+    <t>40.768393</t>
+  </si>
+  <si>
+    <t>72.973140</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Yangihayot tumani, Tursunzoda ko'chasi, 24/19-uy: г. Ташкент, Янгихаётский район, улица Турсунзаде, дом 24/19</t>
+  </si>
+  <si>
+    <t>FrТАШ-369</t>
+  </si>
+  <si>
+    <t>41.218483</t>
+  </si>
+  <si>
+    <t>69.204929</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Yunusobod tumani, 18 dahasi, 1 uy: г. Ташкент, Юнусабадский район, 18 квартал, дом 1</t>
+  </si>
+  <si>
+    <t>FrТАШ-374</t>
+  </si>
+  <si>
+    <t>41.368651</t>
+  </si>
+  <si>
+    <t>69.314181</t>
+  </si>
+  <si>
+    <t>Nukus sh., Xojeli gúzarı ko'chasi, 85 uy: г. Нукус, улица проспекта Ходжейли, дом 85</t>
+  </si>
+  <si>
+    <t>FrНУК-19</t>
+  </si>
+  <si>
+    <t>42.448982</t>
+  </si>
+  <si>
+    <t>59.565499</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Yunusobod tumani, Bodomzor ko'chasi, 8 uy: г. Ташкент, Юнусабадский район, улица Бадамзар, дом 8</t>
+  </si>
+  <si>
+    <t>FrТАШ-360</t>
+  </si>
+  <si>
+    <t>41.339961</t>
+  </si>
+  <si>
+    <t>69.294479</t>
+  </si>
+  <si>
+    <t>Uychi sh., Amir Temur ko'chasi, 55 uy: г. Уйчи, улица Амира Темура, дом 55</t>
+  </si>
+  <si>
+    <t>FrУЙЧ-3</t>
+  </si>
+  <si>
+    <t>41.028691</t>
+  </si>
+  <si>
+    <t>71.843998</t>
+  </si>
+  <si>
+    <t>Samarqand sh., Tong ko'chasi, 51 a uy: г. Самарканд, улица Тонг, дом 51 а</t>
+  </si>
+  <si>
+    <t>FrСМК-67</t>
+  </si>
+  <si>
+    <t>39.662662</t>
+  </si>
+  <si>
+    <t>66.906624</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Mirzo Ulug‘bek tumani, Qorasuv 6 massivi: г. Ташкент , Мирзо Улугбекский район , массив Карасу 6</t>
+  </si>
+  <si>
+    <t>FrТАШ-375</t>
+  </si>
+  <si>
+    <t>41.319195</t>
+  </si>
+  <si>
+    <t>69.353433</t>
   </si>
 </sst>
 </file>
@@ -9495,7 +9591,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
@@ -9781,7 +9877,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1385"/>
+  <dimension ref="A1:D1393"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -29167,18 +29263,130 @@
         <v>3037</v>
       </c>
     </row>
-    <row r="1385" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1385" s="7" t="s">
+    <row r="1385" spans="1:4" ht="39" x14ac:dyDescent="0.25">
+      <c r="A1385" s="20" t="s">
         <v>3039</v>
       </c>
-      <c r="B1385" s="19" t="s">
+      <c r="B1385" s="22" t="s">
         <v>3018</v>
       </c>
-      <c r="C1385" s="19" t="s">
+      <c r="C1385" s="22" t="s">
         <v>3019</v>
       </c>
       <c r="D1385" s="10" t="s">
         <v>3020</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1386" s="28" t="s">
+        <v>3041</v>
+      </c>
+      <c r="B1386" s="29" t="s">
+        <v>3040</v>
+      </c>
+      <c r="C1386" s="29" t="s">
+        <v>3042</v>
+      </c>
+      <c r="D1386" s="10" t="s">
+        <v>3043</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1387" s="1" t="s">
+        <v>3044</v>
+      </c>
+      <c r="B1387" s="17" t="s">
+        <v>3045</v>
+      </c>
+      <c r="C1387" s="17" t="s">
+        <v>3046</v>
+      </c>
+      <c r="D1387" s="10" t="s">
+        <v>3047</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1388" s="1" t="s">
+        <v>3048</v>
+      </c>
+      <c r="B1388" s="17" t="s">
+        <v>3049</v>
+      </c>
+      <c r="C1388" s="17" t="s">
+        <v>3050</v>
+      </c>
+      <c r="D1388" s="10" t="s">
+        <v>3051</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1389" s="1" t="s">
+        <v>3052</v>
+      </c>
+      <c r="B1389" s="17" t="s">
+        <v>3053</v>
+      </c>
+      <c r="C1389" s="17" t="s">
+        <v>3054</v>
+      </c>
+      <c r="D1389" s="10" t="s">
+        <v>3055</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1390" s="1" t="s">
+        <v>3056</v>
+      </c>
+      <c r="B1390" s="17" t="s">
+        <v>3057</v>
+      </c>
+      <c r="C1390" s="17" t="s">
+        <v>3058</v>
+      </c>
+      <c r="D1390" s="10" t="s">
+        <v>3059</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1391" s="7" t="s">
+        <v>3060</v>
+      </c>
+      <c r="B1391" s="17" t="s">
+        <v>3061</v>
+      </c>
+      <c r="C1391" s="19" t="s">
+        <v>3062</v>
+      </c>
+      <c r="D1391" s="10" t="s">
+        <v>3063</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1392" s="7" t="s">
+        <v>3064</v>
+      </c>
+      <c r="B1392" s="17" t="s">
+        <v>3065</v>
+      </c>
+      <c r="C1392" s="19" t="s">
+        <v>3066</v>
+      </c>
+      <c r="D1392" s="10" t="s">
+        <v>3067</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1393" s="7" t="s">
+        <v>3068</v>
+      </c>
+      <c r="B1393" s="17" t="s">
+        <v>3069</v>
+      </c>
+      <c r="C1393" s="19" t="s">
+        <v>3070</v>
+      </c>
+      <c r="D1393" s="10" t="s">
+        <v>3071</v>
       </c>
     </row>
   </sheetData>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Azizbek\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E01BB568-1998-4CB2-9583-9802639560A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD6D3A7-9B2F-42DB-A07F-660BE1EF72C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45" yWindow="1815" windowWidth="20190" windowHeight="12600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20265" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3074" uniqueCount="3072">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3090" uniqueCount="3088">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -9267,6 +9267,54 @@
   </si>
   <si>
     <t>69.353433</t>
+  </si>
+  <si>
+    <t>Farg'ona sh., Farg'ona ko'chasi, 49 uy: г. Фергана, улица Фергана, дом 49</t>
+  </si>
+  <si>
+    <t>FrФЕР-43</t>
+  </si>
+  <si>
+    <t>40.424956</t>
+  </si>
+  <si>
+    <t>71.773104</t>
+  </si>
+  <si>
+    <t>Jomboy sh., Toshkent-Samarqand yo‘li, 134 uy: г. Джамбай, улица Тошкент Самарканд йули, дом 134</t>
+  </si>
+  <si>
+    <t>FrДЖБ-3</t>
+  </si>
+  <si>
+    <t>39.713819</t>
+  </si>
+  <si>
+    <t>67.101377</t>
+  </si>
+  <si>
+    <t>Do'stlik sh., Axillik ko'chasi, 213 uy: г. Дустлик, улица Ахилли, дом 213</t>
+  </si>
+  <si>
+    <t>FrДТС-2</t>
+  </si>
+  <si>
+    <t>40.520355</t>
+  </si>
+  <si>
+    <t>68.034617</t>
+  </si>
+  <si>
+    <t>Chortoq sh., Namangan ko'chasi, 5 uy: г. Чартак, улица Наманган, дом 5</t>
+  </si>
+  <si>
+    <t>FrЧРК-4</t>
+  </si>
+  <si>
+    <t>41.073550</t>
+  </si>
+  <si>
+    <t>71.806307</t>
   </si>
 </sst>
 </file>
@@ -9877,7 +9925,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1393"/>
+  <dimension ref="A1:D1397"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -10825,7 +10873,7 @@
         <v>60.609267000000003</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>134</v>
       </c>
@@ -18945,7 +18993,7 @@
         <v>59.462802000000003</v>
       </c>
     </row>
-    <row r="648" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A648" s="5" t="s">
         <v>1294</v>
       </c>
@@ -19267,7 +19315,7 @@
         <v>69.202941999999993</v>
       </c>
     </row>
-    <row r="671" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A671" s="5" t="s">
         <v>1340</v>
       </c>
@@ -20681,7 +20729,7 @@
         <v>69.341136000000006</v>
       </c>
     </row>
-    <row r="772" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A772" s="5" t="s">
         <v>1542</v>
       </c>
@@ -21003,7 +21051,7 @@
         <v>72.094283000000004</v>
       </c>
     </row>
-    <row r="795" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A795" s="5" t="s">
         <v>1588</v>
       </c>
@@ -23845,7 +23893,7 @@
         <v>72.833483000000001</v>
       </c>
     </row>
-    <row r="998" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="998" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A998" s="5" t="s">
         <v>1994</v>
       </c>
@@ -28465,7 +28513,7 @@
         <v>2809</v>
       </c>
     </row>
-    <row r="1328" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1328" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1328" s="7" t="s">
         <v>2810</v>
       </c>
@@ -28703,7 +28751,7 @@
         <v>2877</v>
       </c>
     </row>
-    <row r="1345" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1345" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1345" s="7" t="s">
         <v>2878</v>
       </c>
@@ -29387,6 +29435,62 @@
       </c>
       <c r="D1393" s="10" t="s">
         <v>3071</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1394" s="1" t="s">
+        <v>3072</v>
+      </c>
+      <c r="B1394" s="18" t="s">
+        <v>3073</v>
+      </c>
+      <c r="C1394" s="19" t="s">
+        <v>3074</v>
+      </c>
+      <c r="D1394" s="10" t="s">
+        <v>3075</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1395" s="7" t="s">
+        <v>3076</v>
+      </c>
+      <c r="B1395" s="18" t="s">
+        <v>3077</v>
+      </c>
+      <c r="C1395" s="19" t="s">
+        <v>3078</v>
+      </c>
+      <c r="D1395" s="10" t="s">
+        <v>3079</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1396" s="7" t="s">
+        <v>3080</v>
+      </c>
+      <c r="B1396" s="18" t="s">
+        <v>3081</v>
+      </c>
+      <c r="C1396" s="19" t="s">
+        <v>3082</v>
+      </c>
+      <c r="D1396" s="10" t="s">
+        <v>3083</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1397" s="7" t="s">
+        <v>3084</v>
+      </c>
+      <c r="B1397" s="18" t="s">
+        <v>3085</v>
+      </c>
+      <c r="C1397" s="19" t="s">
+        <v>3086</v>
+      </c>
+      <c r="D1397" s="10" t="s">
+        <v>3087</v>
       </c>
     </row>
   </sheetData>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Azizbek\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD6D3A7-9B2F-42DB-A07F-660BE1EF72C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79E31DEF-612B-4DBD-BFDA-788913A84BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20265" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1965" windowWidth="21600" windowHeight="11205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3090" uniqueCount="3088">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3102" uniqueCount="3100">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -9315,6 +9315,42 @@
   </si>
   <si>
     <t>71.806307</t>
+  </si>
+  <si>
+    <t>Qo'qon sh., Imom Buxoriy ko'chasi, 11 uy: г. Коканд, улица Имом Бухорий, дом 11</t>
+  </si>
+  <si>
+    <t>FrККД-18</t>
+  </si>
+  <si>
+    <t>40.538239</t>
+  </si>
+  <si>
+    <t>70.924723</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Yashnobod tumani, Aviasozlar 2 mavzesi, 66 uy: г. Ташкент, Яшнабадский район, Авиасозлар 2 квартал, дом 66</t>
+  </si>
+  <si>
+    <t>FrТАШ-348</t>
+  </si>
+  <si>
+    <t>41.282415</t>
+  </si>
+  <si>
+    <t>69.340538</t>
+  </si>
+  <si>
+    <t>Samarqand sh., Marv ko'chasi, 64 uy: г. Самарканд, улица Марв, дом 64</t>
+  </si>
+  <si>
+    <t>FrСМК-72</t>
+  </si>
+  <si>
+    <t>39.629084</t>
+  </si>
+  <si>
+    <t>66.973481</t>
   </si>
 </sst>
 </file>
@@ -9925,7 +9961,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1397"/>
+  <dimension ref="A1:D1400"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -29493,6 +29529,48 @@
         <v>3087</v>
       </c>
     </row>
+    <row r="1398" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1398" s="7" t="s">
+        <v>3088</v>
+      </c>
+      <c r="B1398" s="17" t="s">
+        <v>3089</v>
+      </c>
+      <c r="C1398" s="19" t="s">
+        <v>3090</v>
+      </c>
+      <c r="D1398" s="10" t="s">
+        <v>3091</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1399" s="7" t="s">
+        <v>3092</v>
+      </c>
+      <c r="B1399" s="17" t="s">
+        <v>3093</v>
+      </c>
+      <c r="C1399" s="19" t="s">
+        <v>3094</v>
+      </c>
+      <c r="D1399" s="10" t="s">
+        <v>3095</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1400" s="7" t="s">
+        <v>3096</v>
+      </c>
+      <c r="B1400" s="17" t="s">
+        <v>3097</v>
+      </c>
+      <c r="C1400" s="19" t="s">
+        <v>3098</v>
+      </c>
+      <c r="D1400" s="10" t="s">
+        <v>3099</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Azizbek\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79E31DEF-612B-4DBD-BFDA-788913A84BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B961F934-C802-435B-8CCD-06B2CFFECFE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1965" windowWidth="21600" windowHeight="11205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3102" uniqueCount="3100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3162" uniqueCount="3160">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -9351,6 +9351,186 @@
   </si>
   <si>
     <t>66.973481</t>
+  </si>
+  <si>
+    <t>Nurobod sh., Ohangaron tumani, Nurobod qo‘rg'oni ko'chasi, 3 b uy: г. Нурабад, Охангаронский район, улица Нуробод Кургони, дом 3 б</t>
+  </si>
+  <si>
+    <t>FrНРБ-2</t>
+  </si>
+  <si>
+    <t>40.907476</t>
+  </si>
+  <si>
+    <t>69.809061</t>
+  </si>
+  <si>
+    <t>Sariasiya sh., Sariosiyo tumani, Oq yo'l ko'chasi, 13 uy: г. Сариасия, Сариасийский район, улица Окйул, дом 13</t>
+  </si>
+  <si>
+    <t>FrСРС-4</t>
+  </si>
+  <si>
+    <t>38.411813</t>
+  </si>
+  <si>
+    <t>67.949819</t>
+  </si>
+  <si>
+    <t>Zomin sh., Mustaqillik ko'chasi, 22 uy: г. Заамин, улица Мустакиллик, дом 22</t>
+  </si>
+  <si>
+    <t>FrЗАМ-4</t>
+  </si>
+  <si>
+    <t>39.971687</t>
+  </si>
+  <si>
+    <t>68.405779</t>
+  </si>
+  <si>
+    <t>Samarqand sh., Abu Mansur Moturidiy ko'chasi, 1/1 uy: г. Самарканд, улица Абу Мансура Мотуриди, дом 1/1</t>
+  </si>
+  <si>
+    <t>FrСМК-70</t>
+  </si>
+  <si>
+    <t>39.685316</t>
+  </si>
+  <si>
+    <t>66.973538</t>
+  </si>
+  <si>
+    <t>Samarqand sh., Kimyogarlar qishlog'i, Zavodskaya ko'chasi, 1 uy: г. Самарканд, поселок Кимёгарлар, улица Заводская, дом 1</t>
+  </si>
+  <si>
+    <t>FrСМК-68</t>
+  </si>
+  <si>
+    <t>39.672647</t>
+  </si>
+  <si>
+    <t>66.845685</t>
+  </si>
+  <si>
+    <t>Yangiariq sh., Mustaqillik ko'chasi, 5/3 uy: г. Янгиарик, улица Мустакиллик, дом 5/3</t>
+  </si>
+  <si>
+    <t>FrЯГБ-3</t>
+  </si>
+  <si>
+    <t>41.367380</t>
+  </si>
+  <si>
+    <t>60.596266</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Yakkasaroy tumani, Bobur ko'chasi, 40B uy: г. Ташкент, Яккасарайский район, улица Бабура, дом 40 б</t>
+  </si>
+  <si>
+    <t>FrТАШ-383</t>
+  </si>
+  <si>
+    <t>41.287467</t>
+  </si>
+  <si>
+    <t>69.252203</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Mirobod tumani, Sayxun ko'chasi, 164 uy: г. Ташкент, Мирабадский район, улица Сайхун, дом 164</t>
+  </si>
+  <si>
+    <t>FrТАШ-382</t>
+  </si>
+  <si>
+    <t>41.280969</t>
+  </si>
+  <si>
+    <t>69.303824</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Yashnobod tumani, Aviasozlar mavzesi, 4 daha, 17а uy: г. Ташкент, Яшнабадский район, массив Авиастроителей , 4 квартал, дом 17а</t>
+  </si>
+  <si>
+    <t>FrТАШ-385</t>
+  </si>
+  <si>
+    <t>41.300504</t>
+  </si>
+  <si>
+    <t>69.343874</t>
+  </si>
+  <si>
+    <t>Samarqand sh., Dahbed ko'chasi, 61 uy: г. Самарканд, улица Дагбитская, дом 61</t>
+  </si>
+  <si>
+    <t>FrСМК-69</t>
+  </si>
+  <si>
+    <t>39.664557</t>
+  </si>
+  <si>
+    <t>66.970730</t>
+  </si>
+  <si>
+    <t>Namangan sh.,Istiqlol ko'chasi, 21 uy: г. Наманган, Истиклол улица, 21 дом</t>
+  </si>
+  <si>
+    <t>FrНАМ-28</t>
+  </si>
+  <si>
+    <t>41.008433</t>
+  </si>
+  <si>
+    <t>71.668956</t>
+  </si>
+  <si>
+    <t>Beruniy sh., Quruvchilar kochasi, 19/1 uy: г. Беруни, улица Курувчилар, дом 19/1</t>
+  </si>
+  <si>
+    <t>FrБЕР-6</t>
+  </si>
+  <si>
+    <t>41.690030</t>
+  </si>
+  <si>
+    <t>60.750267</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Olmazor tumani, Allomalar yo‘li ko'chasi, 24 uy: г. Ташкент, Алмазарский район, улица Алломалар, дом 24</t>
+  </si>
+  <si>
+    <t>FrТАШ-376</t>
+  </si>
+  <si>
+    <t>41.360489</t>
+  </si>
+  <si>
+    <t>69.179899</t>
+  </si>
+  <si>
+    <t>Parkent sh., Alisher Navoiy, 35 uy: г. Паркент, улица Алишера Навои, дом 51</t>
+  </si>
+  <si>
+    <t>FrПРК-5</t>
+  </si>
+  <si>
+    <t>41.295892</t>
+  </si>
+  <si>
+    <t>69.671840</t>
+  </si>
+  <si>
+    <t>Kavardan sh., Yuqorichirchiq tumani, Oqovul ko‘chasi, 415 uy: г. Кавардан, Юкоричирчикский район, улица Оковул, дом 415</t>
+  </si>
+  <si>
+    <t>FrКРД-1</t>
+  </si>
+  <si>
+    <t>41.352353</t>
+  </si>
+  <si>
+    <t>69.555620</t>
   </si>
 </sst>
 </file>
@@ -9961,7 +10141,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1400"/>
+  <dimension ref="A1:D1415"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -29571,6 +29751,216 @@
         <v>3099</v>
       </c>
     </row>
+    <row r="1401" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1401" s="7" t="s">
+        <v>3100</v>
+      </c>
+      <c r="B1401" s="17" t="s">
+        <v>3101</v>
+      </c>
+      <c r="C1401" s="19" t="s">
+        <v>3102</v>
+      </c>
+      <c r="D1401" s="10" t="s">
+        <v>3103</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1402" s="7" t="s">
+        <v>3104</v>
+      </c>
+      <c r="B1402" s="17" t="s">
+        <v>3105</v>
+      </c>
+      <c r="C1402" s="19" t="s">
+        <v>3106</v>
+      </c>
+      <c r="D1402" s="10" t="s">
+        <v>3107</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1403" s="7" t="s">
+        <v>3108</v>
+      </c>
+      <c r="B1403" s="17" t="s">
+        <v>3109</v>
+      </c>
+      <c r="C1403" s="19" t="s">
+        <v>3110</v>
+      </c>
+      <c r="D1403" s="10" t="s">
+        <v>3111</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1404" s="1" t="s">
+        <v>3112</v>
+      </c>
+      <c r="B1404" s="17" t="s">
+        <v>3113</v>
+      </c>
+      <c r="C1404" s="17" t="s">
+        <v>3114</v>
+      </c>
+      <c r="D1404" s="10" t="s">
+        <v>3115</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1405" s="7" t="s">
+        <v>3116</v>
+      </c>
+      <c r="B1405" s="17" t="s">
+        <v>3117</v>
+      </c>
+      <c r="C1405" s="19" t="s">
+        <v>3118</v>
+      </c>
+      <c r="D1405" s="10" t="s">
+        <v>3119</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1406" s="7" t="s">
+        <v>3120</v>
+      </c>
+      <c r="B1406" s="17" t="s">
+        <v>3121</v>
+      </c>
+      <c r="C1406" s="19" t="s">
+        <v>3122</v>
+      </c>
+      <c r="D1406" s="10" t="s">
+        <v>3123</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1407" s="7" t="s">
+        <v>3124</v>
+      </c>
+      <c r="B1407" s="17" t="s">
+        <v>3125</v>
+      </c>
+      <c r="C1407" s="19" t="s">
+        <v>3126</v>
+      </c>
+      <c r="D1407" s="10" t="s">
+        <v>3127</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1408" s="7" t="s">
+        <v>3128</v>
+      </c>
+      <c r="B1408" s="17" t="s">
+        <v>3129</v>
+      </c>
+      <c r="C1408" s="19" t="s">
+        <v>3130</v>
+      </c>
+      <c r="D1408" s="10" t="s">
+        <v>3131</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1409" s="7" t="s">
+        <v>3132</v>
+      </c>
+      <c r="B1409" s="19" t="s">
+        <v>3133</v>
+      </c>
+      <c r="C1409" s="19" t="s">
+        <v>3134</v>
+      </c>
+      <c r="D1409" s="10" t="s">
+        <v>3135</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1410" s="7" t="s">
+        <v>3136</v>
+      </c>
+      <c r="B1410" s="17" t="s">
+        <v>3137</v>
+      </c>
+      <c r="C1410" s="19" t="s">
+        <v>3138</v>
+      </c>
+      <c r="D1410" s="10" t="s">
+        <v>3139</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1411" s="7" t="s">
+        <v>3140</v>
+      </c>
+      <c r="B1411" s="17" t="s">
+        <v>3141</v>
+      </c>
+      <c r="C1411" s="19" t="s">
+        <v>3142</v>
+      </c>
+      <c r="D1411" s="10" t="s">
+        <v>3143</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1412" s="7" t="s">
+        <v>3144</v>
+      </c>
+      <c r="B1412" s="17" t="s">
+        <v>3145</v>
+      </c>
+      <c r="C1412" s="19" t="s">
+        <v>3146</v>
+      </c>
+      <c r="D1412" s="10" t="s">
+        <v>3147</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1413" s="7" t="s">
+        <v>3148</v>
+      </c>
+      <c r="B1413" s="17" t="s">
+        <v>3149</v>
+      </c>
+      <c r="C1413" s="19" t="s">
+        <v>3150</v>
+      </c>
+      <c r="D1413" s="10" t="s">
+        <v>3151</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1414" s="7" t="s">
+        <v>3152</v>
+      </c>
+      <c r="B1414" s="17" t="s">
+        <v>3153</v>
+      </c>
+      <c r="C1414" s="19" t="s">
+        <v>3154</v>
+      </c>
+      <c r="D1414" s="10" t="s">
+        <v>3155</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1415" s="7" t="s">
+        <v>3156</v>
+      </c>
+      <c r="B1415" s="19" t="s">
+        <v>3157</v>
+      </c>
+      <c r="C1415" s="19" t="s">
+        <v>3158</v>
+      </c>
+      <c r="D1415" s="10" t="s">
+        <v>3159</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Azizbek\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B961F934-C802-435B-8CCD-06B2CFFECFE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9186E583-41C7-43C2-8CD5-D4A13C5C57A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3162" uniqueCount="3160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3350" uniqueCount="3348">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -9531,6 +9531,570 @@
   </si>
   <si>
     <t>69.555620</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Uchtepa tumani, Dilnoz ko'chasi, 33 uy: г. Ташкент, Учтепинский район, улица Дильноз, дом 33</t>
+  </si>
+  <si>
+    <t>FrТАШ-355</t>
+  </si>
+  <si>
+    <t>41.306859</t>
+  </si>
+  <si>
+    <t>69.178542</t>
+  </si>
+  <si>
+    <t>Samarqand sh., Panjakent ko'chasi ko‘chasi, 468 uy: г. Самарканд, улица Пенджикентская, дом 468</t>
+  </si>
+  <si>
+    <t>FrСМК-71</t>
+  </si>
+  <si>
+    <t>39.638142</t>
+  </si>
+  <si>
+    <t>67.033913</t>
+  </si>
+  <si>
+    <t>Urganch sh., Baxtli oilalar ko'chasi, 7/1 uy: г. Ургенч, улица Бахтли Оилалар, дом 7/1</t>
+  </si>
+  <si>
+    <t>FrУРГ-27</t>
+  </si>
+  <si>
+    <t>41.559674</t>
+  </si>
+  <si>
+    <t>60.619968</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Mirzo Ulug‘bek tumani, Buz-2 massivi, 24 uy: г. Ташкент , Мирзо Улугбекский район , массив Буз-2, дом 24</t>
+  </si>
+  <si>
+    <t>FrТАШ-377</t>
+  </si>
+  <si>
+    <t>41.347555</t>
+  </si>
+  <si>
+    <t>69.350314</t>
+  </si>
+  <si>
+    <t>Chirchiq sh., Qirq-urug koʻchasi, 2 uy: г. Чирчик, улица Кирк Уруг, дом 2</t>
+  </si>
+  <si>
+    <t>FrЧИР-21</t>
+  </si>
+  <si>
+    <t>41.439202</t>
+  </si>
+  <si>
+    <t>69.565677</t>
+  </si>
+  <si>
+    <t>Sharg'un sh., Mashrab ko'chasi, 89 uy: г. Шаргунь, улица Машраба, дом 89</t>
+  </si>
+  <si>
+    <t>FrШРГ-3</t>
+  </si>
+  <si>
+    <t>38.471886</t>
+  </si>
+  <si>
+    <t>67.964452</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Yunusobod tumani, Niyozbek Yo‘li ko‘chasi, 12 uy: г. Ташкент, Юнусабадский район, улица Ниёзбек Йули, 12 дом</t>
+  </si>
+  <si>
+    <t>FrТАШ-372</t>
+  </si>
+  <si>
+    <t>41.325224</t>
+  </si>
+  <si>
+    <t>69.285252</t>
+  </si>
+  <si>
+    <t>Gazli sh., Baynalminal ko'chasi, 44 uy: г. Газли, улица Байналминал, дом 44</t>
+  </si>
+  <si>
+    <t>FrГЗИ-1</t>
+  </si>
+  <si>
+    <t>40.124573</t>
+  </si>
+  <si>
+    <t>63.454653</t>
+  </si>
+  <si>
+    <t>Qumqo'rg'on sh., Beruniy ko'chasi, 89 j uy: г. Кумкурган, улица Беруни, дом 89 ж</t>
+  </si>
+  <si>
+    <t>FrКУМ-4</t>
+  </si>
+  <si>
+    <t>Samarqand sh., Toshkent ko'chasi, 63 uy: г. Самарканд, улица Ташкент, дом 63</t>
+  </si>
+  <si>
+    <t>FrСМК-73</t>
+  </si>
+  <si>
+    <t>Denov sh., Shifokorlar ko'chasi, 137 uy: г. Денау, улица Шифокорлар, дом 137</t>
+  </si>
+  <si>
+    <t>FrДЕН-6</t>
+  </si>
+  <si>
+    <t>Mevazor sh., Qiyichirchiq tumani, Amanov ko‘chasi, 321 uy: г. Мевазор, Куйичирчикский район, улица Аманова, дом 321</t>
+  </si>
+  <si>
+    <t>FrМЕВ-1</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Olmazor tumani, Qorasqamish mavzesi 1/2, Savdo markazining binosi: г. Ташкент, Алмазарский район, массив Каракамыш 1/2, дом савдо маркази</t>
+  </si>
+  <si>
+    <t>FrТАШ-389</t>
+  </si>
+  <si>
+    <t>Bogot sh., O'zbekiston ko'chasi, 873 uy: г. Багат, улица Узбекистон, дом 873</t>
+  </si>
+  <si>
+    <t>FrБГТ-3</t>
+  </si>
+  <si>
+    <t>Samarqand sh., Tashabbuskor ko'chasi, 84 uy: г. Самарканд , улица Ташаббускор , дом 84</t>
+  </si>
+  <si>
+    <t>FrСМК-74</t>
+  </si>
+  <si>
+    <t>To'rtko'l sh., Izboskan tumani, Alisher Navoiy ko'chasi, 22 uy: г. Турткуль, Избасканский район, улица Алишер Навоий, дом 22</t>
+  </si>
+  <si>
+    <t>FrТРУ-1</t>
+  </si>
+  <si>
+    <t>Qarshi sh., Yerko‘rg‘on ko'chasi, 113 uy: г. Карши, улица Еркургон, дом 113</t>
+  </si>
+  <si>
+    <t>FrКРШ-28</t>
+  </si>
+  <si>
+    <t>Gurlan sh., Ziroatchilar ko'chasi, 17 uy: г. Гурлен, улица Зироатчилар, дом 17</t>
+  </si>
+  <si>
+    <t>FrГУР-3</t>
+  </si>
+  <si>
+    <t>Suv Hovuzi sh., Kattaqo‘rg‘on tumani, Bozorboshi ko'chasi, 81 uy: г. Сув Ховузи, Каттакурганский район, улица Базарбаши, дом 81</t>
+  </si>
+  <si>
+    <t>FrСХВ-1</t>
+  </si>
+  <si>
+    <t>Chibintepa sh., O‘rtachirchiq tumani, Qutb Yulduzi ko'chasi, 247 uy: г. Чибинтепа, Уртачирчикский район, улица Кутб Юлдузи, дом 247</t>
+  </si>
+  <si>
+    <t>FrЧБП-1</t>
+  </si>
+  <si>
+    <t>Vorsin sh., Tayloq tumani, Vorsin ko'chasi, 25 uy: г. Ворсин, Тайлакский район, улица Ворсин, дом 25</t>
+  </si>
+  <si>
+    <t>FrВРН-1</t>
+  </si>
+  <si>
+    <t>Karmana sh., Beshkent ko'chasi, 306 uy: г. Кармана, улица Бешкент, дом 306</t>
+  </si>
+  <si>
+    <t>FrКРМ-5</t>
+  </si>
+  <si>
+    <t>Uychi sh., Abu Rayhon Beruniy ko'chasi, 415 uy: г. Уйчи, улица Абу-Райхон Беруний, дом 415</t>
+  </si>
+  <si>
+    <t>FrУЙЧ-2</t>
+  </si>
+  <si>
+    <t>Norinkapa sh., Mustaqillik ko'chasi, 5 uy: г. Нарынкапа, улица Мустакиллик, дом 5</t>
+  </si>
+  <si>
+    <t>FrНРК-2</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Yangihayot tumani, Sokhil ko‘chasi: г. Ташкент, Янгихаётский район, улица Сохил</t>
+  </si>
+  <si>
+    <t>FrТАШ-379</t>
+  </si>
+  <si>
+    <t>Zafarobod sh., Xovos tumani, Chinobod ko'chasi, 3/1 uy: г. Зафарабад, Хавастский район, улица Чинобод, дом 3/1</t>
+  </si>
+  <si>
+    <t>FrЗРД-1</t>
+  </si>
+  <si>
+    <t>Samarqand sh., Al Xorazmiy ko'chasi, 31 uy: г. Самарканд , улица Ал Хоразмий , дом 31</t>
+  </si>
+  <si>
+    <t>FrСМК-77</t>
+  </si>
+  <si>
+    <t>Piskent, A.To‘qay ko'chasi, 40 uy: г. Пскент, улица А. Тукай, 40 дом</t>
+  </si>
+  <si>
+    <t>FrПСК-5</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Mirzo Ulug'bek tumani, Yalangach dahasi, 101 uy: г. Ташкент, Мирзо Улугбекский район, квартал Ялангач, дом 101</t>
+  </si>
+  <si>
+    <t>FrТАШ-390</t>
+  </si>
+  <si>
+    <t>Suv Hovuzi sh., Kattaqo‘rg‘on tumani, 1 Alisher Navoiy ko'chasi, 30 uy: г. Сув Ховузи, Каттакурганский район, улица Алишер Навойи 1, дом 30</t>
+  </si>
+  <si>
+    <t>FrСХВ-2</t>
+  </si>
+  <si>
+    <t>Termiz sh., Al hakim at Termiziy ko'chasi, 18 a uy: г. Термез, улица Аль-Хакима ат-Тирмизи, дом 18 а</t>
+  </si>
+  <si>
+    <t>FrТЕР-24</t>
+  </si>
+  <si>
+    <t>Samarqand sh., Al Xorazmiy ko'chasi, 127 uy: г. Самарканд , улица Ал Хоразмий , дом 127</t>
+  </si>
+  <si>
+    <t>FrСМК-75</t>
+  </si>
+  <si>
+    <t>Ayvalik sh., Ohangaron tumani, Eyvalek qo‘rg‘oni ko'chasi, 254 uy: г. Эйвалек, Ахангаранский район, улица Эйвалек , дом 254</t>
+  </si>
+  <si>
+    <t>FrЭВЛ-1</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Yakkasaroy tumani, Sh.Rustavelli ko‘chasi, 138 uy: г. Ташкент, Яккасарайский район, улица Ш. Руставелли, дом 138</t>
+  </si>
+  <si>
+    <t>FrТАШ-386</t>
+  </si>
+  <si>
+    <t>Batosh sh., Bogi Shamol ko'chasi, 125 uy: г. Баташ , улица Боги Шамол , дом 125</t>
+  </si>
+  <si>
+    <t>FrБТШ-1</t>
+  </si>
+  <si>
+    <t>Chimboy sh., Qalli Ayimbetov ko'chasi, 148/6 uy: г. Чимбай, улица Калли Айимбетов, дом 148/6</t>
+  </si>
+  <si>
+    <t>FrЧИМ-3</t>
+  </si>
+  <si>
+    <t>Parkent sh., Alisher Navoiy ko‘chasi, 100 uy: г. Паркент, улица Алишера Навои, дом 100</t>
+  </si>
+  <si>
+    <t>FrПРК-6</t>
+  </si>
+  <si>
+    <t>Do'rmon sh., Qibray tumani, Markaziy ko‘chasi, 79 uy: г. Дурмон, Кибрайский район, улица Маркази, дом 79</t>
+  </si>
+  <si>
+    <t>FrДМН-1</t>
+  </si>
+  <si>
+    <t>Oqqovoq sh., Qibray tumani, Botanika ko‘chasi, 171 uy: г. Аккавак, Кибрайский район, улица Ботаник, дом 171</t>
+  </si>
+  <si>
+    <t>FrАКВ-1</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Yunusobod tumani, Bog'iravon ko'chasi, 55 uy: г. Ташкент, Юнусабадский район, улица Богиравон, дом 55</t>
+  </si>
+  <si>
+    <t>FrТАШ-392</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Yakkasaroy tumani, Mirobod ko‘chasi, 60a: г. Ташкент, Яккасарайский район, улица Мирабад, дом 60а</t>
+  </si>
+  <si>
+    <t>ТАШ-300</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Sirg'ali tumani, Sirg'ali tumani, Sirg'ali-1 mavzesi, 28 uy: г. Ташкент, Сергелийский район, массив Сергели-1, дом 28</t>
+  </si>
+  <si>
+    <t>FrТАШ-378</t>
+  </si>
+  <si>
+    <t>Sherobod sh., Mustaqillik ko'chasi, 12 uy: г. Шерабад, улица Мустакиллик, дом 12</t>
+  </si>
+  <si>
+    <t>FrШЕР-4</t>
+  </si>
+  <si>
+    <t>Farg‘ona sh., Mustaqillik ko'chasi, 68 uy: г. Фергана, улица Мустакиллик, дом 68</t>
+  </si>
+  <si>
+    <t>FrФЕР-44</t>
+  </si>
+  <si>
+    <t>Termiz sh., Soliobod MFY, Soliobod ko'chasi, 1 g uy: г. Термез, МСГ Солиобод, улица Солиобод, дом 1 г</t>
+  </si>
+  <si>
+    <t>FrТЕР-25</t>
+  </si>
+  <si>
+    <t>Bekobod sh., Binokor ko'chasi, 330 uy: г. Бекабад, улица Бинокор, дом 330</t>
+  </si>
+  <si>
+    <t>FrБЕК-9</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Olmazor tumani, Gulsaroy ko'chasi, 15 a uy: г. Ташкент, Алмазарский район, улица Гулсарай, дом 15 а</t>
+  </si>
+  <si>
+    <t>FrТАШ-395</t>
+  </si>
+  <si>
+    <t>37.838293</t>
+  </si>
+  <si>
+    <t>67.584805</t>
+  </si>
+  <si>
+    <t>39.622626</t>
+  </si>
+  <si>
+    <t>66.994306</t>
+  </si>
+  <si>
+    <t>38.317549</t>
+  </si>
+  <si>
+    <t>67.903272</t>
+  </si>
+  <si>
+    <t>41.015435</t>
+  </si>
+  <si>
+    <t>69.046381</t>
+  </si>
+  <si>
+    <t>41.357010</t>
+  </si>
+  <si>
+    <t>69.236835</t>
+  </si>
+  <si>
+    <t>41.363445</t>
+  </si>
+  <si>
+    <t>60.816741</t>
+  </si>
+  <si>
+    <t>39.700703</t>
+  </si>
+  <si>
+    <t>66.953796</t>
+  </si>
+  <si>
+    <t>40.885311</t>
+  </si>
+  <si>
+    <t>72.186903</t>
+  </si>
+  <si>
+    <t>38.898253</t>
+  </si>
+  <si>
+    <t>65.802077</t>
+  </si>
+  <si>
+    <t>41.841548</t>
+  </si>
+  <si>
+    <t>60.400618</t>
+  </si>
+  <si>
+    <t>39.866017</t>
+  </si>
+  <si>
+    <t>66.270839</t>
+  </si>
+  <si>
+    <t>41.136935</t>
+  </si>
+  <si>
+    <t>69.302309</t>
+  </si>
+  <si>
+    <t>39.634950</t>
+  </si>
+  <si>
+    <t>67.046997</t>
+  </si>
+  <si>
+    <t>40.142576</t>
+  </si>
+  <si>
+    <t>65.355757</t>
+  </si>
+  <si>
+    <t>41.021053</t>
+  </si>
+  <si>
+    <t>71.852631</t>
+  </si>
+  <si>
+    <t>40.929105</t>
+  </si>
+  <si>
+    <t>71.911380</t>
+  </si>
+  <si>
+    <t>41.179010</t>
+  </si>
+  <si>
+    <t>69.247053</t>
+  </si>
+  <si>
+    <t>40.295873</t>
+  </si>
+  <si>
+    <t>68.779106</t>
+  </si>
+  <si>
+    <t>39.682450</t>
+  </si>
+  <si>
+    <t>66.921839</t>
+  </si>
+  <si>
+    <t>40.899835</t>
+  </si>
+  <si>
+    <t>69.362791</t>
+  </si>
+  <si>
+    <t>41.352340</t>
+  </si>
+  <si>
+    <t>69.340264</t>
+  </si>
+  <si>
+    <t>39.854659</t>
+  </si>
+  <si>
+    <t>66.265988</t>
+  </si>
+  <si>
+    <t>37.233090</t>
+  </si>
+  <si>
+    <t>67.278054</t>
+  </si>
+  <si>
+    <t>39.674960</t>
+  </si>
+  <si>
+    <t>66.940998</t>
+  </si>
+  <si>
+    <t>40.945177</t>
+  </si>
+  <si>
+    <t>69.524515</t>
+  </si>
+  <si>
+    <t>41.263538</t>
+  </si>
+  <si>
+    <t>69.228841</t>
+  </si>
+  <si>
+    <t>38.122275</t>
+  </si>
+  <si>
+    <t>67.723603</t>
+  </si>
+  <si>
+    <t>42.923239</t>
+  </si>
+  <si>
+    <t>59.780839</t>
+  </si>
+  <si>
+    <t>41.297123</t>
+  </si>
+  <si>
+    <t>69.664087</t>
+  </si>
+  <si>
+    <t>41.366024</t>
+  </si>
+  <si>
+    <t>69.414960</t>
+  </si>
+  <si>
+    <t>41.413434</t>
+  </si>
+  <si>
+    <t>69.486704</t>
+  </si>
+  <si>
+    <t>41.345885</t>
+  </si>
+  <si>
+    <t>69.265056</t>
+  </si>
+  <si>
+    <t>41.292799</t>
+  </si>
+  <si>
+    <t>69.269495</t>
+  </si>
+  <si>
+    <t>41.208081</t>
+  </si>
+  <si>
+    <t>69.214593</t>
+  </si>
+  <si>
+    <t>37.682605</t>
+  </si>
+  <si>
+    <t>67.013314</t>
+  </si>
+  <si>
+    <t>40.371825</t>
+  </si>
+  <si>
+    <t>71.722926</t>
+  </si>
+  <si>
+    <t>37.283254</t>
+  </si>
+  <si>
+    <t>67.341866</t>
+  </si>
+  <si>
+    <t>40.220688</t>
+  </si>
+  <si>
+    <t>69.187962</t>
+  </si>
+  <si>
+    <t>41.361811</t>
+  </si>
+  <si>
+    <t>69.233498</t>
   </si>
 </sst>
 </file>
@@ -9774,7 +10338,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -9860,6 +10424,27 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10141,7 +10726,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1415"/>
+  <dimension ref="A1:D1462"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -29961,6 +30546,664 @@
         <v>3159</v>
       </c>
     </row>
+    <row r="1416" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1416" s="7" t="s">
+        <v>3160</v>
+      </c>
+      <c r="B1416" s="17" t="s">
+        <v>3161</v>
+      </c>
+      <c r="C1416" s="19" t="s">
+        <v>3162</v>
+      </c>
+      <c r="D1416" s="10" t="s">
+        <v>3163</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1417" s="7" t="s">
+        <v>3164</v>
+      </c>
+      <c r="B1417" s="17" t="s">
+        <v>3165</v>
+      </c>
+      <c r="C1417" s="19" t="s">
+        <v>3166</v>
+      </c>
+      <c r="D1417" s="10" t="s">
+        <v>3167</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1418" s="7" t="s">
+        <v>3168</v>
+      </c>
+      <c r="B1418" s="17" t="s">
+        <v>3169</v>
+      </c>
+      <c r="C1418" s="19" t="s">
+        <v>3170</v>
+      </c>
+      <c r="D1418" s="10" t="s">
+        <v>3171</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1419" s="7" t="s">
+        <v>3172</v>
+      </c>
+      <c r="B1419" s="17" t="s">
+        <v>3173</v>
+      </c>
+      <c r="C1419" s="19" t="s">
+        <v>3174</v>
+      </c>
+      <c r="D1419" s="10" t="s">
+        <v>3175</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1420" s="7" t="s">
+        <v>3176</v>
+      </c>
+      <c r="B1420" s="17" t="s">
+        <v>3177</v>
+      </c>
+      <c r="C1420" s="19" t="s">
+        <v>3178</v>
+      </c>
+      <c r="D1420" s="10" t="s">
+        <v>3179</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1421" s="7" t="s">
+        <v>3180</v>
+      </c>
+      <c r="B1421" s="17" t="s">
+        <v>3181</v>
+      </c>
+      <c r="C1421" s="19" t="s">
+        <v>3182</v>
+      </c>
+      <c r="D1421" s="10" t="s">
+        <v>3183</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1422" s="7" t="s">
+        <v>3184</v>
+      </c>
+      <c r="B1422" s="17" t="s">
+        <v>3185</v>
+      </c>
+      <c r="C1422" s="19" t="s">
+        <v>3186</v>
+      </c>
+      <c r="D1422" s="10" t="s">
+        <v>3187</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1423" s="7" t="s">
+        <v>3188</v>
+      </c>
+      <c r="B1423" s="17" t="s">
+        <v>3189</v>
+      </c>
+      <c r="C1423" s="19" t="s">
+        <v>3190</v>
+      </c>
+      <c r="D1423" s="10" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1424" s="7" t="s">
+        <v>3192</v>
+      </c>
+      <c r="B1424" s="17" t="s">
+        <v>3193</v>
+      </c>
+      <c r="C1424" s="31" t="s">
+        <v>3270</v>
+      </c>
+      <c r="D1424" s="10" t="s">
+        <v>3271</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1425" s="5" t="s">
+        <v>3194</v>
+      </c>
+      <c r="B1425" s="30" t="s">
+        <v>3195</v>
+      </c>
+      <c r="C1425" s="32" t="s">
+        <v>3272</v>
+      </c>
+      <c r="D1425" s="10" t="s">
+        <v>3273</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1426" s="5" t="s">
+        <v>3196</v>
+      </c>
+      <c r="B1426" s="30" t="s">
+        <v>3197</v>
+      </c>
+      <c r="C1426" s="32" t="s">
+        <v>3274</v>
+      </c>
+      <c r="D1426" s="10" t="s">
+        <v>3275</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1427" s="5" t="s">
+        <v>3198</v>
+      </c>
+      <c r="B1427" s="30" t="s">
+        <v>3199</v>
+      </c>
+      <c r="C1427" s="32" t="s">
+        <v>3276</v>
+      </c>
+      <c r="D1427" s="10" t="s">
+        <v>3277</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1428" s="5" t="s">
+        <v>3200</v>
+      </c>
+      <c r="B1428" s="30" t="s">
+        <v>3201</v>
+      </c>
+      <c r="C1428" s="32" t="s">
+        <v>3278</v>
+      </c>
+      <c r="D1428" s="10" t="s">
+        <v>3279</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1429" s="5" t="s">
+        <v>3202</v>
+      </c>
+      <c r="B1429" s="30" t="s">
+        <v>3203</v>
+      </c>
+      <c r="C1429" s="32" t="s">
+        <v>3280</v>
+      </c>
+      <c r="D1429" s="10" t="s">
+        <v>3281</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1430" s="5" t="s">
+        <v>3204</v>
+      </c>
+      <c r="B1430" s="30" t="s">
+        <v>3205</v>
+      </c>
+      <c r="C1430" s="32" t="s">
+        <v>3282</v>
+      </c>
+      <c r="D1430" s="10" t="s">
+        <v>3283</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1431" s="5" t="s">
+        <v>3206</v>
+      </c>
+      <c r="B1431" s="30" t="s">
+        <v>3207</v>
+      </c>
+      <c r="C1431" s="32" t="s">
+        <v>3284</v>
+      </c>
+      <c r="D1431" s="10" t="s">
+        <v>3285</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1432" s="5" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B1432" s="30" t="s">
+        <v>3209</v>
+      </c>
+      <c r="C1432" s="32" t="s">
+        <v>3286</v>
+      </c>
+      <c r="D1432" s="10" t="s">
+        <v>3287</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1433" s="5" t="s">
+        <v>3210</v>
+      </c>
+      <c r="B1433" s="30" t="s">
+        <v>3211</v>
+      </c>
+      <c r="C1433" s="32" t="s">
+        <v>3288</v>
+      </c>
+      <c r="D1433" s="10" t="s">
+        <v>3289</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1434" s="5" t="s">
+        <v>3212</v>
+      </c>
+      <c r="B1434" s="30" t="s">
+        <v>3213</v>
+      </c>
+      <c r="C1434" s="32" t="s">
+        <v>3290</v>
+      </c>
+      <c r="D1434" s="10" t="s">
+        <v>3291</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1435" s="5" t="s">
+        <v>3214</v>
+      </c>
+      <c r="B1435" s="30" t="s">
+        <v>3215</v>
+      </c>
+      <c r="C1435" s="32" t="s">
+        <v>3292</v>
+      </c>
+      <c r="D1435" s="10" t="s">
+        <v>3293</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1436" s="5" t="s">
+        <v>3216</v>
+      </c>
+      <c r="B1436" s="30" t="s">
+        <v>3217</v>
+      </c>
+      <c r="C1436" s="32" t="s">
+        <v>3294</v>
+      </c>
+      <c r="D1436" s="10" t="s">
+        <v>3295</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1437" s="5" t="s">
+        <v>3218</v>
+      </c>
+      <c r="B1437" s="30" t="s">
+        <v>3219</v>
+      </c>
+      <c r="C1437" s="32" t="s">
+        <v>3296</v>
+      </c>
+      <c r="D1437" s="10" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1438" s="5" t="s">
+        <v>3220</v>
+      </c>
+      <c r="B1438" s="30" t="s">
+        <v>3221</v>
+      </c>
+      <c r="C1438" s="32" t="s">
+        <v>3298</v>
+      </c>
+      <c r="D1438" s="10" t="s">
+        <v>3299</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1439" s="5" t="s">
+        <v>3222</v>
+      </c>
+      <c r="B1439" s="30" t="s">
+        <v>3223</v>
+      </c>
+      <c r="C1439" s="32" t="s">
+        <v>3300</v>
+      </c>
+      <c r="D1439" s="10" t="s">
+        <v>3301</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1440" s="5" t="s">
+        <v>3224</v>
+      </c>
+      <c r="B1440" s="30" t="s">
+        <v>3225</v>
+      </c>
+      <c r="C1440" s="32" t="s">
+        <v>3302</v>
+      </c>
+      <c r="D1440" s="10" t="s">
+        <v>3303</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1441" s="2" t="s">
+        <v>3226</v>
+      </c>
+      <c r="B1441" s="30" t="s">
+        <v>3227</v>
+      </c>
+      <c r="C1441" s="33" t="s">
+        <v>3304</v>
+      </c>
+      <c r="D1441" s="10" t="s">
+        <v>3305</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1442" s="2" t="s">
+        <v>3228</v>
+      </c>
+      <c r="B1442" s="30" t="s">
+        <v>3229</v>
+      </c>
+      <c r="C1442" s="33" t="s">
+        <v>3306</v>
+      </c>
+      <c r="D1442" s="10" t="s">
+        <v>3307</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1443" s="2" t="s">
+        <v>3230</v>
+      </c>
+      <c r="B1443" s="30" t="s">
+        <v>3231</v>
+      </c>
+      <c r="C1443" s="33" t="s">
+        <v>3308</v>
+      </c>
+      <c r="D1443" s="10" t="s">
+        <v>3309</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1444" s="2" t="s">
+        <v>3232</v>
+      </c>
+      <c r="B1444" s="30" t="s">
+        <v>3233</v>
+      </c>
+      <c r="C1444" s="33" t="s">
+        <v>3310</v>
+      </c>
+      <c r="D1444" s="10" t="s">
+        <v>3311</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1445" s="2" t="s">
+        <v>3234</v>
+      </c>
+      <c r="B1445" s="30" t="s">
+        <v>3235</v>
+      </c>
+      <c r="C1445" s="33" t="s">
+        <v>3312</v>
+      </c>
+      <c r="D1445" s="10" t="s">
+        <v>3313</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1446" s="2" t="s">
+        <v>3236</v>
+      </c>
+      <c r="B1446" s="30" t="s">
+        <v>3237</v>
+      </c>
+      <c r="C1446" s="33" t="s">
+        <v>3314</v>
+      </c>
+      <c r="D1446" s="10" t="s">
+        <v>3315</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1447" s="5" t="s">
+        <v>3238</v>
+      </c>
+      <c r="B1447" s="30" t="s">
+        <v>3239</v>
+      </c>
+      <c r="C1447" s="32" t="s">
+        <v>3316</v>
+      </c>
+      <c r="D1447" s="10" t="s">
+        <v>3317</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1448" s="5" t="s">
+        <v>3240</v>
+      </c>
+      <c r="B1448" s="30" t="s">
+        <v>3241</v>
+      </c>
+      <c r="C1448" s="32" t="s">
+        <v>3318</v>
+      </c>
+      <c r="D1448" s="10" t="s">
+        <v>3319</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1449" s="5" t="s">
+        <v>3242</v>
+      </c>
+      <c r="B1449" s="30" t="s">
+        <v>3243</v>
+      </c>
+      <c r="C1449" s="32" t="s">
+        <v>3320</v>
+      </c>
+      <c r="D1449" s="10" t="s">
+        <v>3321</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1450" s="5" t="s">
+        <v>3244</v>
+      </c>
+      <c r="B1450" s="30" t="s">
+        <v>3245</v>
+      </c>
+      <c r="C1450" s="32" t="s">
+        <v>3322</v>
+      </c>
+      <c r="D1450" s="10" t="s">
+        <v>3323</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1451" s="2" t="s">
+        <v>3246</v>
+      </c>
+      <c r="B1451" s="30" t="s">
+        <v>3247</v>
+      </c>
+      <c r="C1451" s="33" t="s">
+        <v>3324</v>
+      </c>
+      <c r="D1451" s="10" t="s">
+        <v>3325</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1452" s="5" t="s">
+        <v>3248</v>
+      </c>
+      <c r="B1452" s="30" t="s">
+        <v>3249</v>
+      </c>
+      <c r="C1452" s="32" t="s">
+        <v>3326</v>
+      </c>
+      <c r="D1452" s="10" t="s">
+        <v>3327</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1453" s="5" t="s">
+        <v>3250</v>
+      </c>
+      <c r="B1453" s="30" t="s">
+        <v>3251</v>
+      </c>
+      <c r="C1453" s="32" t="s">
+        <v>3328</v>
+      </c>
+      <c r="D1453" s="10" t="s">
+        <v>3329</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1454" s="5" t="s">
+        <v>3252</v>
+      </c>
+      <c r="B1454" s="30" t="s">
+        <v>3253</v>
+      </c>
+      <c r="C1454" s="32" t="s">
+        <v>3330</v>
+      </c>
+      <c r="D1454" s="10" t="s">
+        <v>3331</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1455" s="5" t="s">
+        <v>3254</v>
+      </c>
+      <c r="B1455" s="30" t="s">
+        <v>3255</v>
+      </c>
+      <c r="C1455" s="32" t="s">
+        <v>3332</v>
+      </c>
+      <c r="D1455" s="10" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1456" s="5" t="s">
+        <v>3256</v>
+      </c>
+      <c r="B1456" s="30" t="s">
+        <v>3257</v>
+      </c>
+      <c r="C1456" s="32" t="s">
+        <v>3334</v>
+      </c>
+      <c r="D1456" s="10" t="s">
+        <v>3335</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1457" s="5" t="s">
+        <v>3258</v>
+      </c>
+      <c r="B1457" s="30" t="s">
+        <v>3259</v>
+      </c>
+      <c r="C1457" s="32" t="s">
+        <v>3336</v>
+      </c>
+      <c r="D1457" s="10" t="s">
+        <v>3337</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1458" s="5" t="s">
+        <v>3260</v>
+      </c>
+      <c r="B1458" s="30" t="s">
+        <v>3261</v>
+      </c>
+      <c r="C1458" s="32" t="s">
+        <v>3338</v>
+      </c>
+      <c r="D1458" s="10" t="s">
+        <v>3339</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1459" s="5" t="s">
+        <v>3262</v>
+      </c>
+      <c r="B1459" s="30" t="s">
+        <v>3263</v>
+      </c>
+      <c r="C1459" s="32" t="s">
+        <v>3340</v>
+      </c>
+      <c r="D1459" s="10" t="s">
+        <v>3341</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1460" s="2" t="s">
+        <v>3264</v>
+      </c>
+      <c r="B1460" s="35" t="s">
+        <v>3265</v>
+      </c>
+      <c r="C1460" s="33" t="s">
+        <v>3342</v>
+      </c>
+      <c r="D1460" s="10" t="s">
+        <v>3343</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1461" s="2" t="s">
+        <v>3266</v>
+      </c>
+      <c r="B1461" s="35" t="s">
+        <v>3267</v>
+      </c>
+      <c r="C1461" s="33" t="s">
+        <v>3344</v>
+      </c>
+      <c r="D1461" s="10" t="s">
+        <v>3345</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1462" s="34" t="s">
+        <v>3268</v>
+      </c>
+      <c r="B1462" s="35" t="s">
+        <v>3269</v>
+      </c>
+      <c r="C1462" s="36" t="s">
+        <v>3346</v>
+      </c>
+      <c r="D1462" s="10" t="s">
+        <v>3347</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Azizbek\Desktop\PVZ_BOT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Caplan\OneDrive\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9186E583-41C7-43C2-8CD5-D4A13C5C57A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46AA9CD7-1107-41A5-80B8-108DD0BF4AE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3350" uniqueCount="3348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3418" uniqueCount="3416">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -10095,6 +10095,210 @@
   </si>
   <si>
     <t>69.233498</t>
+  </si>
+  <si>
+    <t>Qiyot sh., Ishtixon tumani, Qiyot MFY, 87 uy: г. Кият, Иштыханский район, Кият МСГ, дом 87</t>
+  </si>
+  <si>
+    <t>FrКИЯ-1</t>
+  </si>
+  <si>
+    <t>39.975145</t>
+  </si>
+  <si>
+    <t>66.613648</t>
+  </si>
+  <si>
+    <t>Juma sh., Yoshlar qishlog'i, 5/4 uy: г. Джума, кишлак Ёшлар, дом 5/4</t>
+  </si>
+  <si>
+    <t>FrЖУМ-4</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Bektemir tumani, Jamil Tashkandi ko'chasi, 86 uy: г. Ташкент, Бектемирский район, улица Джамиля Ташканди, дом 86</t>
+  </si>
+  <si>
+    <t>FrТАШ-394</t>
+  </si>
+  <si>
+    <t>Uchqizil sh., Gulzor ko'chasi, 124 uy: г. Учкизил, улица Гульзор, дом 124</t>
+  </si>
+  <si>
+    <t>FrКИЗ-2</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Yashnobod tumani, Murabbiy ko‘chasi, 269 uy: г. Ташкент, Яшнабадский район, улица Мурабби, дом 269</t>
+  </si>
+  <si>
+    <t>FrТАШ-384</t>
+  </si>
+  <si>
+    <t>Fayziobod sh., Uychi tumani, Boymirza Xayitov ko'chasi, 26 uy: г. Файзиабад, Уйчинский район, улица Боймирзы Хайитова, дом 26</t>
+  </si>
+  <si>
+    <t>FrФЗБ-1</t>
+  </si>
+  <si>
+    <t>Unqo'rg'on sh., T.Ochilov ko‘chasi, 52 a uy: г. Ункурган, улица Т. Очилов, дом 52 а</t>
+  </si>
+  <si>
+    <t>FrУНК-2</t>
+  </si>
+  <si>
+    <t>Qorako'l sh., O'tik Do'rman ko'chasi, 199 uy : г. Каракуль, улица Утик Дурман, дом 199</t>
+  </si>
+  <si>
+    <t>FrКРК-5</t>
+  </si>
+  <si>
+    <t>Samarqand sh., Kamoliddin Behzod ko'chasi, 14 uy: г. Самарканд , улица Камолиддина Бехзода , дом 14</t>
+  </si>
+  <si>
+    <t>FrСМК-76</t>
+  </si>
+  <si>
+    <t>Olmaliq sh., Gallaba ko'chasi, 1 uy: г. Алмалык, улица Галлаба, дом 1</t>
+  </si>
+  <si>
+    <t>FrАЛМ-14</t>
+  </si>
+  <si>
+    <t>Beruniy sh., Kat kochasi 25 uy: г. Беруни, улица Кат, дом 25</t>
+  </si>
+  <si>
+    <t>FrБЕР-9</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Yangihayot tumani, Yangi Sergeli ko'chasi, 1 uy: г. Ташкент, Янгихаётский район, улица Янги Сергели, 1 дом</t>
+  </si>
+  <si>
+    <t>FrТАШ-266</t>
+  </si>
+  <si>
+    <t>Dehoji sh., Yangiobod kochasi 59 uy: г. Деходжи, улица Янгиабад, дом 59</t>
+  </si>
+  <si>
+    <t>FrДХЖ-1</t>
+  </si>
+  <si>
+    <t>Yurchi sh., Denov tumani, Ipak yo'li kochasi 16 a uy: г. Юрчи, Денауский район, улица Ипак йули, дом 16 а</t>
+  </si>
+  <si>
+    <t>FrЮРЧ-1</t>
+  </si>
+  <si>
+    <t>Ko'kdala sh., Yangi chorvog‘ kochasi 4 uy: г. Кукдала, улица Янги Чарвог, дом 4</t>
+  </si>
+  <si>
+    <t>FrКДЛ-1</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Chilonzor tumani, Chilonzor ko'chasi, 82 uy: г. Ташкент, Чиланзарский район, улица Чиланзар, дом 82</t>
+  </si>
+  <si>
+    <t>ТАШ-301</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Chilonzor tumani, Asrlar Sadosi ko'chasi, 10 uy: г. Ташкент, Чиланзарский район, улица Асрлар Садоси, дом 10</t>
+  </si>
+  <si>
+    <t>ТАШ-302</t>
+  </si>
+  <si>
+    <t>39.710926</t>
+  </si>
+  <si>
+    <t>66.647140</t>
+  </si>
+  <si>
+    <t>41.224592</t>
+  </si>
+  <si>
+    <t>69.329377</t>
+  </si>
+  <si>
+    <t>37.309259</t>
+  </si>
+  <si>
+    <t>67.197153</t>
+  </si>
+  <si>
+    <t>41.303305</t>
+  </si>
+  <si>
+    <t>69.399916</t>
+  </si>
+  <si>
+    <t>41.010903</t>
+  </si>
+  <si>
+    <t>71.813030</t>
+  </si>
+  <si>
+    <t>41.402182</t>
+  </si>
+  <si>
+    <t>69.334822</t>
+  </si>
+  <si>
+    <t>39.536271</t>
+  </si>
+  <si>
+    <t>63.881112</t>
+  </si>
+  <si>
+    <t>39.624320</t>
+  </si>
+  <si>
+    <t>66.940937</t>
+  </si>
+  <si>
+    <t>40.889696</t>
+  </si>
+  <si>
+    <t>69.572798</t>
+  </si>
+  <si>
+    <t>41.680960</t>
+  </si>
+  <si>
+    <t>60.750646</t>
+  </si>
+  <si>
+    <t>41.251556</t>
+  </si>
+  <si>
+    <t>69.217042</t>
+  </si>
+  <si>
+    <t>39.812402</t>
+  </si>
+  <si>
+    <t>64.347451</t>
+  </si>
+  <si>
+    <t>38.339561</t>
+  </si>
+  <si>
+    <t>67.913440</t>
+  </si>
+  <si>
+    <t>39.215805</t>
+  </si>
+  <si>
+    <t>66.250640</t>
+  </si>
+  <si>
+    <t>41.280212</t>
+  </si>
+  <si>
+    <t>69.218980</t>
+  </si>
+  <si>
+    <t>41.299767</t>
+  </si>
+  <si>
+    <t>69.201538</t>
   </si>
 </sst>
 </file>
@@ -10338,7 +10542,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -10446,9 +10650,12 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -10726,7 +10933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1462"/>
+  <dimension ref="A1:D1479"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -31204,8 +31411,246 @@
         <v>3347</v>
       </c>
     </row>
+    <row r="1463" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1463" s="1" t="s">
+        <v>3348</v>
+      </c>
+      <c r="B1463" s="17" t="s">
+        <v>3349</v>
+      </c>
+      <c r="C1463" s="17" t="s">
+        <v>3350</v>
+      </c>
+      <c r="D1463" s="10" t="s">
+        <v>3351</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1464" s="7" t="s">
+        <v>3352</v>
+      </c>
+      <c r="B1464" s="17" t="s">
+        <v>3353</v>
+      </c>
+      <c r="C1464" s="31" t="s">
+        <v>3384</v>
+      </c>
+      <c r="D1464" s="10" t="s">
+        <v>3385</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1465" s="5" t="s">
+        <v>3354</v>
+      </c>
+      <c r="B1465" s="30" t="s">
+        <v>3355</v>
+      </c>
+      <c r="C1465" s="32" t="s">
+        <v>3386</v>
+      </c>
+      <c r="D1465" s="10" t="s">
+        <v>3387</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1466" s="5" t="s">
+        <v>3356</v>
+      </c>
+      <c r="B1466" s="30" t="s">
+        <v>3357</v>
+      </c>
+      <c r="C1466" s="32" t="s">
+        <v>3388</v>
+      </c>
+      <c r="D1466" s="10" t="s">
+        <v>3389</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1467" s="5" t="s">
+        <v>3358</v>
+      </c>
+      <c r="B1467" s="30" t="s">
+        <v>3359</v>
+      </c>
+      <c r="C1467" s="32" t="s">
+        <v>3390</v>
+      </c>
+      <c r="D1467" s="10" t="s">
+        <v>3391</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1468" s="5" t="s">
+        <v>3360</v>
+      </c>
+      <c r="B1468" s="30" t="s">
+        <v>3361</v>
+      </c>
+      <c r="C1468" s="32" t="s">
+        <v>3392</v>
+      </c>
+      <c r="D1468" s="10" t="s">
+        <v>3393</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1469" s="2" t="s">
+        <v>3362</v>
+      </c>
+      <c r="B1469" s="30" t="s">
+        <v>3363</v>
+      </c>
+      <c r="C1469" s="33" t="s">
+        <v>3394</v>
+      </c>
+      <c r="D1469" s="10" t="s">
+        <v>3395</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1470" s="2" t="s">
+        <v>3364</v>
+      </c>
+      <c r="B1470" s="30" t="s">
+        <v>3365</v>
+      </c>
+      <c r="C1470" s="33" t="s">
+        <v>3396</v>
+      </c>
+      <c r="D1470" s="10" t="s">
+        <v>3397</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1471" s="5" t="s">
+        <v>3366</v>
+      </c>
+      <c r="B1471" s="30" t="s">
+        <v>3367</v>
+      </c>
+      <c r="C1471" s="32" t="s">
+        <v>3398</v>
+      </c>
+      <c r="D1471" s="10" t="s">
+        <v>3399</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1472" s="5" t="s">
+        <v>3368</v>
+      </c>
+      <c r="B1472" s="30" t="s">
+        <v>3369</v>
+      </c>
+      <c r="C1472" s="32" t="s">
+        <v>3400</v>
+      </c>
+      <c r="D1472" s="10" t="s">
+        <v>3401</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1473" s="5" t="s">
+        <v>3370</v>
+      </c>
+      <c r="B1473" s="30" t="s">
+        <v>3371</v>
+      </c>
+      <c r="C1473" s="32" t="s">
+        <v>3402</v>
+      </c>
+      <c r="D1473" s="10" t="s">
+        <v>3403</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1474" s="5" t="s">
+        <v>3372</v>
+      </c>
+      <c r="B1474" s="30" t="s">
+        <v>3373</v>
+      </c>
+      <c r="C1474" s="32" t="s">
+        <v>3404</v>
+      </c>
+      <c r="D1474" s="10" t="s">
+        <v>3405</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1475" s="5" t="s">
+        <v>3374</v>
+      </c>
+      <c r="B1475" s="30" t="s">
+        <v>3375</v>
+      </c>
+      <c r="C1475" s="32" t="s">
+        <v>3406</v>
+      </c>
+      <c r="D1475" s="10" t="s">
+        <v>3407</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1476" s="5" t="s">
+        <v>3376</v>
+      </c>
+      <c r="B1476" s="30" t="s">
+        <v>3377</v>
+      </c>
+      <c r="C1476" s="32" t="s">
+        <v>3408</v>
+      </c>
+      <c r="D1476" s="10" t="s">
+        <v>3409</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1477" s="5" t="s">
+        <v>3378</v>
+      </c>
+      <c r="B1477" s="30" t="s">
+        <v>3379</v>
+      </c>
+      <c r="C1477" s="32" t="s">
+        <v>3410</v>
+      </c>
+      <c r="D1477" s="10" t="s">
+        <v>3411</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1478" s="5" t="s">
+        <v>3380</v>
+      </c>
+      <c r="B1478" s="37" t="s">
+        <v>3381</v>
+      </c>
+      <c r="C1478" s="32" t="s">
+        <v>3412</v>
+      </c>
+      <c r="D1478" s="10" t="s">
+        <v>3413</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1479" s="5" t="s">
+        <v>3382</v>
+      </c>
+      <c r="B1479" s="37" t="s">
+        <v>3383</v>
+      </c>
+      <c r="C1479" s="32" t="s">
+        <v>3414</v>
+      </c>
+      <c r="D1479" s="10" t="s">
+        <v>3415</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Caplan\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78C8E39-0F4A-4257-A5A6-439F31F8BB75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01C1E097-F358-4FB8-ADC8-E4569966AF06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3498" uniqueCount="3496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3526" uniqueCount="3524">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -10539,6 +10539,90 @@
   </si>
   <si>
     <t>69.438515</t>
+  </si>
+  <si>
+    <t>Olmaliq sh., Gagarin ko'chasi, 17 uy: г. Алмалык, улица Гагарина, дом 17</t>
+  </si>
+  <si>
+    <t>FrАЛМ-15</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Mirobod tumani, Kushko'prik ko'chasi, 30 uy: г. Ташкент, Мирабадский район, улица Кушкуприк, дом 30</t>
+  </si>
+  <si>
+    <t>FrТАШ-399</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Sirg'ali tumani, 8A mavzesi, 17 uy: г. Ташкент, Сергелийский район, массив 8А, дом 17</t>
+  </si>
+  <si>
+    <t>FrТАШ-398</t>
+  </si>
+  <si>
+    <t>Go‘zalkent sh., Pastdarg‘om tumani, Jaxongir kochasi: г. Гузалкент, Пастдаргомский район, улица Джахонгира</t>
+  </si>
+  <si>
+    <t>FrГКТ-1</t>
+  </si>
+  <si>
+    <t>Navoiy sh., Gulchilar ko'chasi, 50 uy: г. Навои, улица Гулчилар, дом 50</t>
+  </si>
+  <si>
+    <t>FrНАВ-25</t>
+  </si>
+  <si>
+    <t>Mamurabod sh., Qo'rg'ontepa tumani, Favvora ko'chasi, 497 uy: г. Мамурабад, Кургантепинский район, улица Фаввора, дом 497</t>
+  </si>
+  <si>
+    <t>FrММБ-1</t>
+  </si>
+  <si>
+    <t>Xatinariq sh., Mustaqillik ko'chasi, 75 uy: г. Хатынарык, улица Мустакиллик, дом 75</t>
+  </si>
+  <si>
+    <t>FrХТН-1</t>
+  </si>
+  <si>
+    <t>41.290496</t>
+  </si>
+  <si>
+    <t>69.295581</t>
+  </si>
+  <si>
+    <t>40.847699</t>
+  </si>
+  <si>
+    <t>69.612176</t>
+  </si>
+  <si>
+    <t>41.225153</t>
+  </si>
+  <si>
+    <t>69.216065</t>
+  </si>
+  <si>
+    <t>39.751913</t>
+  </si>
+  <si>
+    <t>66.580536</t>
+  </si>
+  <si>
+    <t>40.112105</t>
+  </si>
+  <si>
+    <t>65.391380</t>
+  </si>
+  <si>
+    <t>40.725340</t>
+  </si>
+  <si>
+    <t>72.809964</t>
+  </si>
+  <si>
+    <t>40.500667</t>
+  </si>
+  <si>
+    <t>71.720797</t>
   </si>
 </sst>
 </file>
@@ -11173,7 +11257,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1499"/>
+  <dimension ref="A1:D1506"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.5546875" customWidth="1"/>
@@ -32169,6 +32253,104 @@
         <v>3495</v>
       </c>
     </row>
+    <row r="1500" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1500" s="7" t="s">
+        <v>3496</v>
+      </c>
+      <c r="B1500" s="18" t="s">
+        <v>3497</v>
+      </c>
+      <c r="C1500" s="31" t="s">
+        <v>3512</v>
+      </c>
+      <c r="D1500" s="10" t="s">
+        <v>3513</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1501" s="5" t="s">
+        <v>3498</v>
+      </c>
+      <c r="B1501" s="35" t="s">
+        <v>3499</v>
+      </c>
+      <c r="C1501" s="32" t="s">
+        <v>3510</v>
+      </c>
+      <c r="D1501" s="10" t="s">
+        <v>3511</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1502" s="5" t="s">
+        <v>3500</v>
+      </c>
+      <c r="B1502" s="35" t="s">
+        <v>3501</v>
+      </c>
+      <c r="C1502" s="32" t="s">
+        <v>3514</v>
+      </c>
+      <c r="D1502" s="10" t="s">
+        <v>3515</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1503" s="5" t="s">
+        <v>3502</v>
+      </c>
+      <c r="B1503" s="35" t="s">
+        <v>3503</v>
+      </c>
+      <c r="C1503" s="32" t="s">
+        <v>3516</v>
+      </c>
+      <c r="D1503" s="10" t="s">
+        <v>3517</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1504" s="5" t="s">
+        <v>3504</v>
+      </c>
+      <c r="B1504" s="35" t="s">
+        <v>3505</v>
+      </c>
+      <c r="C1504" s="32" t="s">
+        <v>3518</v>
+      </c>
+      <c r="D1504" s="10" t="s">
+        <v>3519</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:4" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1505" s="5" t="s">
+        <v>3506</v>
+      </c>
+      <c r="B1505" s="37" t="s">
+        <v>3507</v>
+      </c>
+      <c r="C1505" s="32" t="s">
+        <v>3520</v>
+      </c>
+      <c r="D1505" s="10" t="s">
+        <v>3521</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1506" s="5" t="s">
+        <v>3508</v>
+      </c>
+      <c r="B1506" s="37" t="s">
+        <v>3509</v>
+      </c>
+      <c r="C1506" s="32" t="s">
+        <v>3522</v>
+      </c>
+      <c r="D1506" s="10" t="s">
+        <v>3523</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\OneDrive\Desktop\PVZ_BOT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7b1c8268b11fc464/Desktop/PVZ_BOT/PVZ_BOT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABEEFE6-6591-4A53-8F26-5A011DE70B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{AF6DC62A-60C5-4896-A29D-DC5F3DC93527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3554" uniqueCount="3552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3582" uniqueCount="3580">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -10707,6 +10707,90 @@
   </si>
   <si>
     <t>67.997538</t>
+  </si>
+  <si>
+    <t>Tuyabo'g'iz sh., Alisher Navoiy ko‘chasi, 77 uy: г. Туябугуз, улица Алишера Навоий, дом 77</t>
+  </si>
+  <si>
+    <t>FrТБЗ-1</t>
+  </si>
+  <si>
+    <t>Yangiyer sh., Qumqo‘rg‘on tumani, Sharof Rashidov ko‘chasi, 60 b uy: г. Янгиер, Кумкурганский район, улица Шароф Рашидов, дом 60 б</t>
+  </si>
+  <si>
+    <t>FrЯНИ-1</t>
+  </si>
+  <si>
+    <t>Angren sh, Qori Niyoziy ko'chasi, 105 uy: г. Ангрен, улица Кори Ниёзий, дом 105</t>
+  </si>
+  <si>
+    <t>FrАНГ-10</t>
+  </si>
+  <si>
+    <t>Parkent sh., Gulzor ko‘chasi, 199А uy: г. Паркент, улица Гульзор, дом 199А</t>
+  </si>
+  <si>
+    <t>FrПРК-7</t>
+  </si>
+  <si>
+    <t>Gagarin sh., Zangiota tumani, Amir Temur ko‘chasi, 6 uy: г. Гагарин, Зангиатинский район, улица Амира Темура, дом 6</t>
+  </si>
+  <si>
+    <t>FrГРН-1</t>
+  </si>
+  <si>
+    <t>O'zbekiston sh., Zangiota tumani, Amir Temur ko‘chasi, 7 uy: г. Узбекистан, Зангиатинский район, улица Амира Темура, дом 7</t>
+  </si>
+  <si>
+    <t>FrУЗТ-1</t>
+  </si>
+  <si>
+    <t>Yangi Hazorbog` sh., Bog'ichinor ko‘chasi, 59 uy: г. Янги Хазорбог, улица Богичинор, дом 59</t>
+  </si>
+  <si>
+    <t>FrХАЗ-1</t>
+  </si>
+  <si>
+    <t>40.997528</t>
+  </si>
+  <si>
+    <t>69.300259</t>
+  </si>
+  <si>
+    <t>37.753466</t>
+  </si>
+  <si>
+    <t>67.587828</t>
+  </si>
+  <si>
+    <t>41.033962</t>
+  </si>
+  <si>
+    <t>70.067603</t>
+  </si>
+  <si>
+    <t>41.301257</t>
+  </si>
+  <si>
+    <t>69.655181</t>
+  </si>
+  <si>
+    <t>41.210924</t>
+  </si>
+  <si>
+    <t>69.098945</t>
+  </si>
+  <si>
+    <t>41.206783</t>
+  </si>
+  <si>
+    <t>69.086847</t>
+  </si>
+  <si>
+    <t>38.199247</t>
+  </si>
+  <si>
+    <t>67.833194</t>
   </si>
 </sst>
 </file>
@@ -11398,7 +11482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1513"/>
+  <dimension ref="A1:D1520"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -32590,6 +32674,104 @@
         <v>3551</v>
       </c>
     </row>
+    <row r="1514" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1514" s="7" t="s">
+        <v>3552</v>
+      </c>
+      <c r="B1514" s="17" t="s">
+        <v>3553</v>
+      </c>
+      <c r="C1514" s="31" t="s">
+        <v>3566</v>
+      </c>
+      <c r="D1514" s="10" t="s">
+        <v>3567</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1515" s="5" t="s">
+        <v>3554</v>
+      </c>
+      <c r="B1515" s="30" t="s">
+        <v>3555</v>
+      </c>
+      <c r="C1515" s="32" t="s">
+        <v>3568</v>
+      </c>
+      <c r="D1515" s="10" t="s">
+        <v>3569</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1516" s="5" t="s">
+        <v>3556</v>
+      </c>
+      <c r="B1516" s="30" t="s">
+        <v>3557</v>
+      </c>
+      <c r="C1516" s="32" t="s">
+        <v>3570</v>
+      </c>
+      <c r="D1516" s="10" t="s">
+        <v>3571</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1517" s="5" t="s">
+        <v>3558</v>
+      </c>
+      <c r="B1517" s="30" t="s">
+        <v>3559</v>
+      </c>
+      <c r="C1517" s="32" t="s">
+        <v>3572</v>
+      </c>
+      <c r="D1517" s="10" t="s">
+        <v>3573</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1518" s="5" t="s">
+        <v>3560</v>
+      </c>
+      <c r="B1518" s="30" t="s">
+        <v>3561</v>
+      </c>
+      <c r="C1518" s="32" t="s">
+        <v>3574</v>
+      </c>
+      <c r="D1518" s="10" t="s">
+        <v>3575</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1519" s="5" t="s">
+        <v>3562</v>
+      </c>
+      <c r="B1519" s="30" t="s">
+        <v>3563</v>
+      </c>
+      <c r="C1519" s="32" t="s">
+        <v>3576</v>
+      </c>
+      <c r="D1519" s="10" t="s">
+        <v>3577</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1520" s="5" t="s">
+        <v>3564</v>
+      </c>
+      <c r="B1520" s="30" t="s">
+        <v>3565</v>
+      </c>
+      <c r="C1520" s="32" t="s">
+        <v>3578</v>
+      </c>
+      <c r="D1520" s="10" t="s">
+        <v>3579</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7b1c8268b11fc464/Desktop/PVZ_BOT/PVZ_BOT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{AF6DC62A-60C5-4896-A29D-DC5F3DC93527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{A0C27A4F-7447-4D1C-9308-04189DE431FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3582" uniqueCount="3580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3618" uniqueCount="3616">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -10791,6 +10791,114 @@
   </si>
   <si>
     <t>67.833194</t>
+  </si>
+  <si>
+    <t>Quva sh., Kalinpustin ko'chasi, 113 uy: г. Кува, улица Калинпустин, дом 113</t>
+  </si>
+  <si>
+    <t>FrКВА-4</t>
+  </si>
+  <si>
+    <t>Toshbuloq sh., Maskan ko'chasi, 11 uy: г.Ташбулак, улица Маскан, дом 11</t>
+  </si>
+  <si>
+    <t>FrТШБ-4</t>
+  </si>
+  <si>
+    <t>Kauchun sh., Qarshi tumani, Qovchin ko'chasi, 126/1 uy: г.Каучун, Каршинский район, улица Каучун, дом 126/1</t>
+  </si>
+  <si>
+    <t>FrКЧН-1</t>
+  </si>
+  <si>
+    <t>Avliyoota sh., Karvon yo‘li ko‘chasi, 38 uy: г. Авлиёота, улица Карвон йули, дом 38</t>
+  </si>
+  <si>
+    <t>FrАВТ-2</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Yunusobod tumani, Kulolkurgon 6 to'r ko'ch, 46 uy: г. Ташкент, Юнусабадский район, 6 й проезд Кулолкургон, дом 46</t>
+  </si>
+  <si>
+    <t>FrТАШ-380</t>
+  </si>
+  <si>
+    <t>Tegalak sh., Qo‘shko‘pir tumani, Jasorat ko‘chasi, 94 uy: г. Тегалак, Кошкупырский район, улица Жасорат, дом 94</t>
+  </si>
+  <si>
+    <t>FrТГЛ-1</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Mirzo Ulug'bek tumani, Milliy bog‘ ko'chasi, 88b uy: г. Ташкент, Мирзо Улугбекский район, улица Миллий Бог, дом 88 б</t>
+  </si>
+  <si>
+    <t>FrТАШ-396</t>
+  </si>
+  <si>
+    <t>Angren sh, Qadriyat ko'chasi, 1а uy: г. Ангрен, улица Кадрият, дом 1а</t>
+  </si>
+  <si>
+    <t>FrАНГ-11</t>
+  </si>
+  <si>
+    <t>Argen sh, Qibray tumani, Markaziy ko'chasi, 153 а uy: г. Арген, Кибрайский район, улица Марказий, дом 153 а</t>
+  </si>
+  <si>
+    <t>FrАГН-1</t>
+  </si>
+  <si>
+    <t>40.521069</t>
+  </si>
+  <si>
+    <t>72.048318</t>
+  </si>
+  <si>
+    <t>38.783286</t>
+  </si>
+  <si>
+    <t>65.542882</t>
+  </si>
+  <si>
+    <t>41.403900</t>
+  </si>
+  <si>
+    <t>69.282800</t>
+  </si>
+  <si>
+    <t>41.377549</t>
+  </si>
+  <si>
+    <t>69.288797</t>
+  </si>
+  <si>
+    <t>41.458217</t>
+  </si>
+  <si>
+    <t>60.200904</t>
+  </si>
+  <si>
+    <t>41.335935</t>
+  </si>
+  <si>
+    <t>69.442683</t>
+  </si>
+  <si>
+    <t>40.985126</t>
+  </si>
+  <si>
+    <t>70.085888</t>
+  </si>
+  <si>
+    <t>41.371199</t>
+  </si>
+  <si>
+    <t>69.425864</t>
+  </si>
+  <si>
+    <t>40.924776</t>
+  </si>
+  <si>
+    <t>71.571093</t>
   </si>
 </sst>
 </file>
@@ -11482,7 +11590,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1520"/>
+  <dimension ref="A1:D1529"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -32772,6 +32880,132 @@
         <v>3579</v>
       </c>
     </row>
+    <row r="1521" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1521" s="7" t="s">
+        <v>3580</v>
+      </c>
+      <c r="B1521" s="17" t="s">
+        <v>3581</v>
+      </c>
+      <c r="C1521" s="31" t="s">
+        <v>3598</v>
+      </c>
+      <c r="D1521" s="10" t="s">
+        <v>3599</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1522" s="2" t="s">
+        <v>3582</v>
+      </c>
+      <c r="B1522" s="30" t="s">
+        <v>3583</v>
+      </c>
+      <c r="C1522" s="33" t="s">
+        <v>3614</v>
+      </c>
+      <c r="D1522" s="10" t="s">
+        <v>3615</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1523" s="2" t="s">
+        <v>3584</v>
+      </c>
+      <c r="B1523" s="30" t="s">
+        <v>3585</v>
+      </c>
+      <c r="C1523" s="33" t="s">
+        <v>3600</v>
+      </c>
+      <c r="D1523" s="10" t="s">
+        <v>3601</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1524" s="2" t="s">
+        <v>3586</v>
+      </c>
+      <c r="B1524" s="30" t="s">
+        <v>3587</v>
+      </c>
+      <c r="C1524" s="33" t="s">
+        <v>3602</v>
+      </c>
+      <c r="D1524" s="10" t="s">
+        <v>3603</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1525" s="2" t="s">
+        <v>3588</v>
+      </c>
+      <c r="B1525" s="30" t="s">
+        <v>3589</v>
+      </c>
+      <c r="C1525" s="33" t="s">
+        <v>3604</v>
+      </c>
+      <c r="D1525" s="10" t="s">
+        <v>3605</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1526" s="2" t="s">
+        <v>3590</v>
+      </c>
+      <c r="B1526" s="30" t="s">
+        <v>3591</v>
+      </c>
+      <c r="C1526" s="33" t="s">
+        <v>3606</v>
+      </c>
+      <c r="D1526" s="10" t="s">
+        <v>3607</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1527" s="2" t="s">
+        <v>3592</v>
+      </c>
+      <c r="B1527" s="30" t="s">
+        <v>3593</v>
+      </c>
+      <c r="C1527" s="33" t="s">
+        <v>3608</v>
+      </c>
+      <c r="D1527" s="10" t="s">
+        <v>3609</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1528" s="2" t="s">
+        <v>3594</v>
+      </c>
+      <c r="B1528" s="30" t="s">
+        <v>3595</v>
+      </c>
+      <c r="C1528" s="33" t="s">
+        <v>3610</v>
+      </c>
+      <c r="D1528" s="10" t="s">
+        <v>3611</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1529" s="2" t="s">
+        <v>3596</v>
+      </c>
+      <c r="B1529" s="30" t="s">
+        <v>3597</v>
+      </c>
+      <c r="C1529" s="33" t="s">
+        <v>3612</v>
+      </c>
+      <c r="D1529" s="10" t="s">
+        <v>3613</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\OneDrive\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0037507-2ED7-4F24-AEB6-49B2D456D627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E382E1DE-8AFB-41AD-9849-4BEB55F1C83C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10829,9 +10829,6 @@
     <t>FrТГЛ-1</t>
   </si>
   <si>
-    <t>Toshkent sh., Mirzo Ulug'bek tumani, Milliy bog‘ ko'chasi, 88b uy: г. Ташкент, Мирзо Улугбекский район, улица Миллий Бог, дом 88 б</t>
-  </si>
-  <si>
     <t>FrТАШ-396</t>
   </si>
   <si>
@@ -10899,6 +10896,9 @@
   </si>
   <si>
     <t>69.440775</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Mirzo Ulug'bek tumani, Milliy bog‘ ko'chasi, 88b uy: г. Ташкент, Мирзо Улугбекский район, улица Миллий Бог, дом 86 б</t>
   </si>
 </sst>
 </file>
@@ -11181,7 +11181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -11309,6 +11309,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -32888,10 +32891,10 @@
         <v>3581</v>
       </c>
       <c r="C1521" s="31" t="s">
+        <v>3597</v>
+      </c>
+      <c r="D1521" s="10" t="s">
         <v>3598</v>
-      </c>
-      <c r="D1521" s="10" t="s">
-        <v>3599</v>
       </c>
     </row>
     <row r="1522" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -32902,10 +32905,10 @@
         <v>3583</v>
       </c>
       <c r="C1522" s="33" t="s">
+        <v>3611</v>
+      </c>
+      <c r="D1522" s="10" t="s">
         <v>3612</v>
-      </c>
-      <c r="D1522" s="10" t="s">
-        <v>3613</v>
       </c>
     </row>
     <row r="1523" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
@@ -32916,10 +32919,10 @@
         <v>3585</v>
       </c>
       <c r="C1523" s="33" t="s">
+        <v>3599</v>
+      </c>
+      <c r="D1523" s="10" t="s">
         <v>3600</v>
-      </c>
-      <c r="D1523" s="10" t="s">
-        <v>3601</v>
       </c>
     </row>
     <row r="1524" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -32930,10 +32933,10 @@
         <v>3587</v>
       </c>
       <c r="C1524" s="33" t="s">
+        <v>3601</v>
+      </c>
+      <c r="D1524" s="10" t="s">
         <v>3602</v>
-      </c>
-      <c r="D1524" s="10" t="s">
-        <v>3603</v>
       </c>
     </row>
     <row r="1525" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
@@ -32944,10 +32947,10 @@
         <v>3589</v>
       </c>
       <c r="C1525" s="33" t="s">
+        <v>3603</v>
+      </c>
+      <c r="D1525" s="10" t="s">
         <v>3604</v>
-      </c>
-      <c r="D1525" s="10" t="s">
-        <v>3605</v>
       </c>
     </row>
     <row r="1526" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
@@ -32958,52 +32961,52 @@
         <v>3591</v>
       </c>
       <c r="C1526" s="33" t="s">
+        <v>3605</v>
+      </c>
+      <c r="D1526" s="10" t="s">
         <v>3606</v>
-      </c>
-      <c r="D1526" s="10" t="s">
-        <v>3607</v>
       </c>
     </row>
     <row r="1527" spans="1:4" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1527" s="2" t="s">
+        <v>3615</v>
+      </c>
+      <c r="B1527" s="11" t="s">
         <v>3592</v>
       </c>
-      <c r="B1527" s="30" t="s">
-        <v>3593</v>
-      </c>
-      <c r="C1527" s="33" t="s">
+      <c r="C1527" s="44" t="s">
+        <v>3613</v>
+      </c>
+      <c r="D1527" s="10" t="s">
         <v>3614</v>
-      </c>
-      <c r="D1527" s="10" t="s">
-        <v>3615</v>
       </c>
     </row>
     <row r="1528" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1528" s="2" t="s">
+        <v>3593</v>
+      </c>
+      <c r="B1528" s="30" t="s">
         <v>3594</v>
       </c>
-      <c r="B1528" s="30" t="s">
-        <v>3595</v>
-      </c>
       <c r="C1528" s="33" t="s">
+        <v>3607</v>
+      </c>
+      <c r="D1528" s="10" t="s">
         <v>3608</v>
-      </c>
-      <c r="D1528" s="10" t="s">
-        <v>3609</v>
       </c>
     </row>
     <row r="1529" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1529" s="2" t="s">
+        <v>3595</v>
+      </c>
+      <c r="B1529" s="30" t="s">
         <v>3596</v>
       </c>
-      <c r="B1529" s="30" t="s">
-        <v>3597</v>
-      </c>
       <c r="C1529" s="33" t="s">
+        <v>3609</v>
+      </c>
+      <c r="D1529" s="10" t="s">
         <v>3610</v>
-      </c>
-      <c r="D1529" s="10" t="s">
-        <v>3611</v>
       </c>
     </row>
   </sheetData>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\OneDrive\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E382E1DE-8AFB-41AD-9849-4BEB55F1C83C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B0D01B0-8525-4A6A-A6A3-6E9228C7D4B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10898,7 +10898,7 @@
     <t>69.440775</t>
   </si>
   <si>
-    <t>Toshkent sh., Mirzo Ulug'bek tumani, Milliy bog‘ ko'chasi, 88b uy: г. Ташкент, Мирзо Улугбекский район, улица Миллий Бог, дом 86 б</t>
+    <t>Toshkent sh., Mirzo Ulug'bek tumani, Milliy bog‘ ko'chasi, 86b uy: г. Ташкент, Мирзо Улугбекский район, улица Миллий Бог, дом 86 б</t>
   </si>
 </sst>
 </file>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\OneDrive\Desktop\PVZ_BOT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89448743-B47C-4562-A5F2-7257792A22B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA4AF1E7-9BD7-4E5C-AC44-D05F5C370856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3654" uniqueCount="3652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3674" uniqueCount="3672">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -11007,6 +11007,66 @@
   </si>
   <si>
     <t>69.109380</t>
+  </si>
+  <si>
+    <t>Shahrisabz sh., Bunyodkor ko‘chasi, 4 uy: г. Шахрисабз, улица Бунедкор, дом 4</t>
+  </si>
+  <si>
+    <t>FrШРЗ-9</t>
+  </si>
+  <si>
+    <t>Nurafshon sh., Toshkent yoʼli ko'chasi, 199 uy: г. Нурафшан, улица Тошкент Йули, дом 199</t>
+  </si>
+  <si>
+    <t>FrНУР-7</t>
+  </si>
+  <si>
+    <t>39.093200</t>
+  </si>
+  <si>
+    <t>66.831581</t>
+  </si>
+  <si>
+    <t>41.055786</t>
+  </si>
+  <si>
+    <t>69.351688</t>
+  </si>
+  <si>
+    <t>Sariasiya sh., Islom Karimov ko'chasi, 52 uy: г. Сариасия, улица Ислама Каримова, дом 52</t>
+  </si>
+  <si>
+    <t>FrСРС-5</t>
+  </si>
+  <si>
+    <t>Angren sh, 32 mavze, 3 uy: г. Ангрен, 32 квартал, дом 3</t>
+  </si>
+  <si>
+    <t>FrАНГ-12</t>
+  </si>
+  <si>
+    <t>Qo'shrobod sh., Buloqboshi ko'chasi, 156 uy: г. Кушрабад, улица Булокбоши, дом 156</t>
+  </si>
+  <si>
+    <t>FrКШР-2</t>
+  </si>
+  <si>
+    <t>38.428084</t>
+  </si>
+  <si>
+    <t>67.954500</t>
+  </si>
+  <si>
+    <t>41.018302</t>
+  </si>
+  <si>
+    <t>70.086017</t>
+  </si>
+  <si>
+    <t>40.261737</t>
+  </si>
+  <si>
+    <t>66.637302</t>
   </si>
 </sst>
 </file>
@@ -11423,7 +11483,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -11701,7 +11761,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1538"/>
+  <dimension ref="A1:D1543"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -33243,6 +33303,76 @@
         <v>3651</v>
       </c>
     </row>
+    <row r="1539" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1539" s="7" t="s">
+        <v>3652</v>
+      </c>
+      <c r="B1539" s="18" t="s">
+        <v>3653</v>
+      </c>
+      <c r="C1539" s="31" t="s">
+        <v>3656</v>
+      </c>
+      <c r="D1539" s="10" t="s">
+        <v>3657</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1540" s="5" t="s">
+        <v>3654</v>
+      </c>
+      <c r="B1540" s="35" t="s">
+        <v>3655</v>
+      </c>
+      <c r="C1540" s="32" t="s">
+        <v>3658</v>
+      </c>
+      <c r="D1540" s="10" t="s">
+        <v>3659</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1541" s="7" t="s">
+        <v>3660</v>
+      </c>
+      <c r="B1541" s="17" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1541" s="31" t="s">
+        <v>3666</v>
+      </c>
+      <c r="D1541" s="10" t="s">
+        <v>3667</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1542" s="2" t="s">
+        <v>3662</v>
+      </c>
+      <c r="B1542" s="30" t="s">
+        <v>3663</v>
+      </c>
+      <c r="C1542" s="32" t="s">
+        <v>3668</v>
+      </c>
+      <c r="D1542" s="10" t="s">
+        <v>3669</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1543" s="5" t="s">
+        <v>3664</v>
+      </c>
+      <c r="B1543" s="30" t="s">
+        <v>3665</v>
+      </c>
+      <c r="C1543" s="32" t="s">
+        <v>3670</v>
+      </c>
+      <c r="D1543" s="10" t="s">
+        <v>3671</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA4AF1E7-9BD7-4E5C-AC44-D05F5C370856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970D8974-3048-4E7A-9C21-668725DA5CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17580" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3674" uniqueCount="3672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3690" uniqueCount="3688">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -11067,6 +11067,54 @@
   </si>
   <si>
     <t>66.637302</t>
+  </si>
+  <si>
+    <t>Mitan sh., Alisher Navoiy ko‘chasi, 43 uy: г. Митан, улица Алишер Навоий, дом 43</t>
+  </si>
+  <si>
+    <t>FrМТН-2</t>
+  </si>
+  <si>
+    <t>Karmana sh., Talqoq ko'chasi, 174 uy: г. Кармана, улица Талкок, дом 174</t>
+  </si>
+  <si>
+    <t>FrКРМ-7</t>
+  </si>
+  <si>
+    <t>40.005954</t>
+  </si>
+  <si>
+    <t>66.549823</t>
+  </si>
+  <si>
+    <t>40.146900</t>
+  </si>
+  <si>
+    <t>65.329100</t>
+  </si>
+  <si>
+    <t>Abdulla Qaxxor ko'chasi, 2 uy: г. Алмалык, улица Абдуллы Каххара, дом 2</t>
+  </si>
+  <si>
+    <t>FrАЛМ-16</t>
+  </si>
+  <si>
+    <t>Zomin sh., Mustaqillik ko'chasi, 75 uy: г. Заамин, улица Мустакиллик, дом 75</t>
+  </si>
+  <si>
+    <t>FrЗАМ-5</t>
+  </si>
+  <si>
+    <t>40.862331</t>
+  </si>
+  <si>
+    <t>69.603246</t>
+  </si>
+  <si>
+    <t>39.964642</t>
+  </si>
+  <si>
+    <t>68.398551</t>
   </si>
 </sst>
 </file>
@@ -11761,7 +11809,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1543"/>
+  <dimension ref="A1:D1547"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -33373,6 +33421,62 @@
         <v>3671</v>
       </c>
     </row>
+    <row r="1544" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1544" s="7" t="s">
+        <v>3672</v>
+      </c>
+      <c r="B1544" s="19" t="s">
+        <v>3673</v>
+      </c>
+      <c r="C1544" s="31" t="s">
+        <v>3676</v>
+      </c>
+      <c r="D1544" s="10" t="s">
+        <v>3677</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1545" s="5" t="s">
+        <v>3674</v>
+      </c>
+      <c r="B1545" s="37" t="s">
+        <v>3675</v>
+      </c>
+      <c r="C1545" s="32" t="s">
+        <v>3678</v>
+      </c>
+      <c r="D1545" s="10" t="s">
+        <v>3679</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1546" s="7" t="s">
+        <v>3680</v>
+      </c>
+      <c r="B1546" s="19" t="s">
+        <v>3681</v>
+      </c>
+      <c r="C1546" s="31" t="s">
+        <v>3684</v>
+      </c>
+      <c r="D1546" s="10" t="s">
+        <v>3685</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1547" s="5" t="s">
+        <v>3682</v>
+      </c>
+      <c r="B1547" s="37" t="s">
+        <v>3683</v>
+      </c>
+      <c r="C1547" s="32" t="s">
+        <v>3686</v>
+      </c>
+      <c r="D1547" s="10" t="s">
+        <v>3687</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970D8974-3048-4E7A-9C21-668725DA5CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCFBB163-BE0F-439D-A5CF-02FBD9BE6C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17580" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3690" uniqueCount="3688">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3714" uniqueCount="3712">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -11115,6 +11115,78 @@
   </si>
   <si>
     <t>68.398551</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Olmazor tumani, Qora-Qamish massivi, 2/4 kvartal, 2A uy: г. Ташкент, Алмазарский район, массив Кара-Камыш, квартал 2/4 дом 2А</t>
+  </si>
+  <si>
+    <t>FrТАШ-401</t>
+  </si>
+  <si>
+    <t>Andijon sh., S.Zunnunova kuchasi, 3/a uy: г. Андижан, улица С.Зуннуновой, дом 3/а</t>
+  </si>
+  <si>
+    <t>FrАНД-28</t>
+  </si>
+  <si>
+    <t>Urganch sh., Xonqa ko'chasi, 117 uy: г. Ургенч, улица Хонка, дом 117</t>
+  </si>
+  <si>
+    <t>FrУРГ-29</t>
+  </si>
+  <si>
+    <t>Shexoncha sh., Shexoncha ko'chasi, 384 uy: г. Шайханча, улица Шайханча, дом 384</t>
+  </si>
+  <si>
+    <t>FrШХЧ-1</t>
+  </si>
+  <si>
+    <t>Samarqand sh., Marokanda ko'chasi, 37 uy: г. Самарканд, улица Мароканд, дом 37</t>
+  </si>
+  <si>
+    <t>FrСМК-78</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Shayxontohur tumani, Beltepa ko'chasi, 2 uy: г. Ташкент, Шайхантахурский район, улица Белтепа, дом 2</t>
+  </si>
+  <si>
+    <t>FrТАШ-402</t>
+  </si>
+  <si>
+    <t>41.366503</t>
+  </si>
+  <si>
+    <t>69.213673</t>
+  </si>
+  <si>
+    <t>40.776044</t>
+  </si>
+  <si>
+    <t>72.330208</t>
+  </si>
+  <si>
+    <t>41.533674</t>
+  </si>
+  <si>
+    <t>60.663786</t>
+  </si>
+  <si>
+    <t>39.813530</t>
+  </si>
+  <si>
+    <t>64.409274</t>
+  </si>
+  <si>
+    <t>39.674905</t>
+  </si>
+  <si>
+    <t>66.977906</t>
+  </si>
+  <si>
+    <t>41.346533</t>
+  </si>
+  <si>
+    <t>69.165829</t>
   </si>
 </sst>
 </file>
@@ -11809,7 +11881,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1547"/>
+  <dimension ref="A1:D1553"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -33477,6 +33549,90 @@
         <v>3687</v>
       </c>
     </row>
+    <row r="1548" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1548" s="7" t="s">
+        <v>3688</v>
+      </c>
+      <c r="B1548" s="17" t="s">
+        <v>3689</v>
+      </c>
+      <c r="C1548" s="31" t="s">
+        <v>3700</v>
+      </c>
+      <c r="D1548" s="10" t="s">
+        <v>3701</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1549" s="5" t="s">
+        <v>3690</v>
+      </c>
+      <c r="B1549" s="30" t="s">
+        <v>3691</v>
+      </c>
+      <c r="C1549" s="32" t="s">
+        <v>3702</v>
+      </c>
+      <c r="D1549" s="10" t="s">
+        <v>3703</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1550" s="5" t="s">
+        <v>3692</v>
+      </c>
+      <c r="B1550" s="30" t="s">
+        <v>3693</v>
+      </c>
+      <c r="C1550" s="32" t="s">
+        <v>3704</v>
+      </c>
+      <c r="D1550" s="10" t="s">
+        <v>3705</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1551" s="5" t="s">
+        <v>3694</v>
+      </c>
+      <c r="B1551" s="30" t="s">
+        <v>3695</v>
+      </c>
+      <c r="C1551" s="32" t="s">
+        <v>3706</v>
+      </c>
+      <c r="D1551" s="10" t="s">
+        <v>3707</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1552" s="5" t="s">
+        <v>3696</v>
+      </c>
+      <c r="B1552" s="30" t="s">
+        <v>3697</v>
+      </c>
+      <c r="C1552" s="32" t="s">
+        <v>3708</v>
+      </c>
+      <c r="D1552" s="10" t="s">
+        <v>3709</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1553" s="5" t="s">
+        <v>3698</v>
+      </c>
+      <c r="B1553" s="30" t="s">
+        <v>3699</v>
+      </c>
+      <c r="C1553" s="32" t="s">
+        <v>3710</v>
+      </c>
+      <c r="D1553" s="10" t="s">
+        <v>3711</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCFBB163-BE0F-439D-A5CF-02FBD9BE6C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A53D906A-D086-4B14-A70C-7D1EB9C5F802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3714" uniqueCount="3712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3750" uniqueCount="3748">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -11187,6 +11187,114 @@
   </si>
   <si>
     <t>69.165829</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Mirzo Ulug'bek tumani, Ulug‘bek shaxarchasi mikrorayoni, 1 g uy: г. Ташкент, Мирзо Улугбекский район, Микрорайон Улугбека, дом 1 г</t>
+  </si>
+  <si>
+    <t>FrТАШ-404</t>
+  </si>
+  <si>
+    <t>Xonobod sh., Buxoro tumani, Xonobod ko'chasi, 150 uy: г. Хонобод, Бухарский район, улица Хонабод, дом 150</t>
+  </si>
+  <si>
+    <t>FrХОН-1</t>
+  </si>
+  <si>
+    <t>To'rtqo'rg'on sh., Namuna ko'chasi, 21 uy: г. Турткурган, улица Наъмуна, дом 21</t>
+  </si>
+  <si>
+    <t>FrТКГ-1</t>
+  </si>
+  <si>
+    <t>Bahrin sh., Bahrin ko'chasi, 19 uy: г. Бахрин, улица Бахрин, дом 19</t>
+  </si>
+  <si>
+    <t>FrБРН-1</t>
+  </si>
+  <si>
+    <t>Toyloq sh., Qishloq Yangi Tayloq ko‘chasi, 21 uy: г. Тайлак, улица Кишлак Янги Тайлок, дом 21</t>
+  </si>
+  <si>
+    <t>FrТАЙ-3</t>
+  </si>
+  <si>
+    <t>Mustaqillik sh., Qibray tumani, Birdamlik: г. Мустакиллик, Кибрайский район, улица Бирдамлик</t>
+  </si>
+  <si>
+    <t>FrМУС-1</t>
+  </si>
+  <si>
+    <t>Charxin sh., Urta Charxin MFY, 27 uy: г. Чархин, Урта-Чархин МСГ, дом 27</t>
+  </si>
+  <si>
+    <t>FrЧРХ-2</t>
+  </si>
+  <si>
+    <t>Kattaqo‘rg‘on sh., Go'zal qishlog'i, 63 uy: г. Каттакурган, улица Гозал кишлоги , дом 63</t>
+  </si>
+  <si>
+    <t>FrКТГ-9</t>
+  </si>
+  <si>
+    <t>Olmazor sh., Chinoz tuman, Porloq kelajak ko'chasi, 5 uy : г. Алмазар, Чиназский район, улица Порлок Келаджак, дом 5</t>
+  </si>
+  <si>
+    <t>FrАЛР-1</t>
+  </si>
+  <si>
+    <t>41.412144</t>
+  </si>
+  <si>
+    <t>69.468435</t>
+  </si>
+  <si>
+    <t>39.780912</t>
+  </si>
+  <si>
+    <t>64.382829</t>
+  </si>
+  <si>
+    <t>41.172755</t>
+  </si>
+  <si>
+    <t>69.293790</t>
+  </si>
+  <si>
+    <t>40.004155</t>
+  </si>
+  <si>
+    <t>66.497052</t>
+  </si>
+  <si>
+    <t>39.608141</t>
+  </si>
+  <si>
+    <t>67.084367</t>
+  </si>
+  <si>
+    <t>41.429755</t>
+  </si>
+  <si>
+    <t>69.362947</t>
+  </si>
+  <si>
+    <t>39.712000</t>
+  </si>
+  <si>
+    <t>66.806200</t>
+  </si>
+  <si>
+    <t>39.879470</t>
+  </si>
+  <si>
+    <t>66.269195</t>
+  </si>
+  <si>
+    <t>40.977968</t>
+  </si>
+  <si>
+    <t>68.841186</t>
   </si>
 </sst>
 </file>
@@ -11881,7 +11989,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1553"/>
+  <dimension ref="A1:D1562"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -33633,6 +33741,132 @@
         <v>3711</v>
       </c>
     </row>
+    <row r="1554" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1554" s="7" t="s">
+        <v>3712</v>
+      </c>
+      <c r="B1554" s="17" t="s">
+        <v>3713</v>
+      </c>
+      <c r="C1554" s="31" t="s">
+        <v>3730</v>
+      </c>
+      <c r="D1554" s="10" t="s">
+        <v>3731</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1555" s="5" t="s">
+        <v>3714</v>
+      </c>
+      <c r="B1555" s="30" t="s">
+        <v>3715</v>
+      </c>
+      <c r="C1555" s="32" t="s">
+        <v>3732</v>
+      </c>
+      <c r="D1555" s="10" t="s">
+        <v>3733</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1556" s="5" t="s">
+        <v>3716</v>
+      </c>
+      <c r="B1556" s="30" t="s">
+        <v>3717</v>
+      </c>
+      <c r="C1556" s="32" t="s">
+        <v>3734</v>
+      </c>
+      <c r="D1556" s="10" t="s">
+        <v>3735</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1557" s="5" t="s">
+        <v>3718</v>
+      </c>
+      <c r="B1557" s="30" t="s">
+        <v>3719</v>
+      </c>
+      <c r="C1557" s="32" t="s">
+        <v>3736</v>
+      </c>
+      <c r="D1557" s="10" t="s">
+        <v>3737</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1558" s="5" t="s">
+        <v>3720</v>
+      </c>
+      <c r="B1558" s="30" t="s">
+        <v>3721</v>
+      </c>
+      <c r="C1558" s="32" t="s">
+        <v>3738</v>
+      </c>
+      <c r="D1558" s="10" t="s">
+        <v>3739</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1559" s="5" t="s">
+        <v>3722</v>
+      </c>
+      <c r="B1559" s="30" t="s">
+        <v>3723</v>
+      </c>
+      <c r="C1559" s="32" t="s">
+        <v>3740</v>
+      </c>
+      <c r="D1559" s="10" t="s">
+        <v>3741</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1560" s="5" t="s">
+        <v>3724</v>
+      </c>
+      <c r="B1560" s="30" t="s">
+        <v>3725</v>
+      </c>
+      <c r="C1560" s="32" t="s">
+        <v>3742</v>
+      </c>
+      <c r="D1560" s="10" t="s">
+        <v>3743</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1561" s="5" t="s">
+        <v>3726</v>
+      </c>
+      <c r="B1561" s="30" t="s">
+        <v>3727</v>
+      </c>
+      <c r="C1561" s="32" t="s">
+        <v>3744</v>
+      </c>
+      <c r="D1561" s="10" t="s">
+        <v>3745</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1562" s="5" t="s">
+        <v>3728</v>
+      </c>
+      <c r="B1562" s="30" t="s">
+        <v>3729</v>
+      </c>
+      <c r="C1562" s="32" t="s">
+        <v>3746</v>
+      </c>
+      <c r="D1562" s="10" t="s">
+        <v>3747</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A53D906A-D086-4B14-A70C-7D1EB9C5F802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{451DB57C-BE7A-4296-82B4-B2191FC748EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2610" yWindow="1395" windowWidth="17130" windowHeight="13995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3750" uniqueCount="3748">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3754" uniqueCount="3752">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -11295,6 +11295,18 @@
   </si>
   <si>
     <t>68.841186</t>
+  </si>
+  <si>
+    <t>Olmaliq sh., Gulshan ko'chasi, 12 uy: г. Алмалык, улица Гулшан, дом 12</t>
+  </si>
+  <si>
+    <t>FrАЛМ-17</t>
+  </si>
+  <si>
+    <t>40.843130</t>
+  </si>
+  <si>
+    <t>69.604969</t>
   </si>
 </sst>
 </file>
@@ -11577,7 +11589,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -11627,36 +11639,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -11664,38 +11657,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -11703,10 +11669,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -11989,7 +11988,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1562"/>
+  <dimension ref="A1:D1563"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -12293,7 +12292,7 @@
         <v>71.809231999999994</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>42</v>
       </c>
@@ -14295,7 +14294,7 @@
         <v>69.343695999999994</v>
       </c>
     </row>
-    <row r="165" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="5" t="s">
         <v>328</v>
       </c>
@@ -15191,7 +15190,7 @@
         <v>72.999573999999996</v>
       </c>
     </row>
-    <row r="229" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="5" t="s">
         <v>456</v>
       </c>
@@ -15359,7 +15358,7 @@
         <v>64.434209999999993</v>
       </c>
     </row>
-    <row r="241" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="5" t="s">
         <v>480</v>
       </c>
@@ -16087,7 +16086,7 @@
         <v>70.059414000000004</v>
       </c>
     </row>
-    <row r="293" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="5" t="s">
         <v>584</v>
       </c>
@@ -18691,7 +18690,7 @@
         <v>69.23648</v>
       </c>
     </row>
-    <row r="479" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A479" s="5" t="s">
         <v>956</v>
       </c>
@@ -21057,7 +21056,7 @@
         <v>59.462802000000003</v>
       </c>
     </row>
-    <row r="648" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A648" s="5" t="s">
         <v>1294</v>
       </c>
@@ -21379,7 +21378,7 @@
         <v>69.202941999999993</v>
       </c>
     </row>
-    <row r="671" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A671" s="5" t="s">
         <v>1340</v>
       </c>
@@ -21771,7 +21770,7 @@
         <v>72.069658000000004</v>
       </c>
     </row>
-    <row r="699" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A699" s="5" t="s">
         <v>1396</v>
       </c>
@@ -22107,7 +22106,7 @@
         <v>72.754859999999994</v>
       </c>
     </row>
-    <row r="723" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A723" s="5" t="s">
         <v>1444</v>
       </c>
@@ -22793,7 +22792,7 @@
         <v>69.341136000000006</v>
       </c>
     </row>
-    <row r="772" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A772" s="5" t="s">
         <v>1542</v>
       </c>
@@ -23115,7 +23114,7 @@
         <v>72.094283000000004</v>
       </c>
     </row>
-    <row r="795" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A795" s="5" t="s">
         <v>1588</v>
       </c>
@@ -23591,7 +23590,7 @@
         <v>60.602592999999999</v>
       </c>
     </row>
-    <row r="829" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A829" s="5" t="s">
         <v>1656</v>
       </c>
@@ -25047,7 +25046,7 @@
         <v>69.221705</v>
       </c>
     </row>
-    <row r="933" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="933" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A933" s="5" t="s">
         <v>1864</v>
       </c>
@@ -25495,7 +25494,7 @@
         <v>69.371487000000002</v>
       </c>
     </row>
-    <row r="965" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="965" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A965" s="5" t="s">
         <v>1928</v>
       </c>
@@ -25957,7 +25956,7 @@
         <v>72.833483000000001</v>
       </c>
     </row>
-    <row r="998" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="998" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A998" s="5" t="s">
         <v>1994</v>
       </c>
@@ -30021,10 +30020,10 @@
       <c r="A1288" s="1" t="s">
         <v>2650</v>
       </c>
-      <c r="B1288" s="17" t="s">
+      <c r="B1288" s="9" t="s">
         <v>2651</v>
       </c>
-      <c r="C1288" s="17" t="s">
+      <c r="C1288" s="9" t="s">
         <v>2652</v>
       </c>
       <c r="D1288" s="10" t="s">
@@ -30035,10 +30034,10 @@
       <c r="A1289" s="1" t="s">
         <v>2654</v>
       </c>
-      <c r="B1289" s="17" t="s">
+      <c r="B1289" s="9" t="s">
         <v>2655</v>
       </c>
-      <c r="C1289" s="17" t="s">
+      <c r="C1289" s="9" t="s">
         <v>2656</v>
       </c>
       <c r="D1289" s="10" t="s">
@@ -30049,10 +30048,10 @@
       <c r="A1290" s="1" t="s">
         <v>2658</v>
       </c>
-      <c r="B1290" s="17" t="s">
+      <c r="B1290" s="9" t="s">
         <v>2659</v>
       </c>
-      <c r="C1290" s="17" t="s">
+      <c r="C1290" s="9" t="s">
         <v>2660</v>
       </c>
       <c r="D1290" s="10" t="s">
@@ -30063,10 +30062,10 @@
       <c r="A1291" s="1" t="s">
         <v>2662</v>
       </c>
-      <c r="B1291" s="17" t="s">
+      <c r="B1291" s="9" t="s">
         <v>2663</v>
       </c>
-      <c r="C1291" s="17" t="s">
+      <c r="C1291" s="9" t="s">
         <v>2664</v>
       </c>
       <c r="D1291" s="10" t="s">
@@ -30077,10 +30076,10 @@
       <c r="A1292" s="1" t="s">
         <v>2666</v>
       </c>
-      <c r="B1292" s="17" t="s">
+      <c r="B1292" s="9" t="s">
         <v>2667</v>
       </c>
-      <c r="C1292" s="17" t="s">
+      <c r="C1292" s="9" t="s">
         <v>2668</v>
       </c>
       <c r="D1292" s="10" t="s">
@@ -30091,10 +30090,10 @@
       <c r="A1293" s="1" t="s">
         <v>2670</v>
       </c>
-      <c r="B1293" s="17" t="s">
+      <c r="B1293" s="9" t="s">
         <v>2671</v>
       </c>
-      <c r="C1293" s="17" t="s">
+      <c r="C1293" s="9" t="s">
         <v>2672</v>
       </c>
       <c r="D1293" s="10" t="s">
@@ -30105,10 +30104,10 @@
       <c r="A1294" s="1" t="s">
         <v>2674</v>
       </c>
-      <c r="B1294" s="17" t="s">
+      <c r="B1294" s="9" t="s">
         <v>2675</v>
       </c>
-      <c r="C1294" s="17" t="s">
+      <c r="C1294" s="9" t="s">
         <v>2676</v>
       </c>
       <c r="D1294" s="10" t="s">
@@ -30119,10 +30118,10 @@
       <c r="A1295" s="1" t="s">
         <v>2678</v>
       </c>
-      <c r="B1295" s="17" t="s">
+      <c r="B1295" s="9" t="s">
         <v>2679</v>
       </c>
-      <c r="C1295" s="17" t="s">
+      <c r="C1295" s="9" t="s">
         <v>2680</v>
       </c>
       <c r="D1295" s="10" t="s">
@@ -30133,10 +30132,10 @@
       <c r="A1296" s="1" t="s">
         <v>2682</v>
       </c>
-      <c r="B1296" s="17" t="s">
+      <c r="B1296" s="9" t="s">
         <v>2683</v>
       </c>
-      <c r="C1296" s="17" t="s">
+      <c r="C1296" s="9" t="s">
         <v>2684</v>
       </c>
       <c r="D1296" s="10" t="s">
@@ -30147,10 +30146,10 @@
       <c r="A1297" s="1" t="s">
         <v>2686</v>
       </c>
-      <c r="B1297" s="17" t="s">
+      <c r="B1297" s="9" t="s">
         <v>2687</v>
       </c>
-      <c r="C1297" s="17" t="s">
+      <c r="C1297" s="9" t="s">
         <v>2688</v>
       </c>
       <c r="D1297" s="10" t="s">
@@ -30161,10 +30160,10 @@
       <c r="A1298" s="8" t="s">
         <v>2690</v>
       </c>
-      <c r="B1298" s="18" t="s">
+      <c r="B1298" s="16" t="s">
         <v>2691</v>
       </c>
-      <c r="C1298" s="18" t="s">
+      <c r="C1298" s="16" t="s">
         <v>2692</v>
       </c>
       <c r="D1298" s="10" t="s">
@@ -30175,10 +30174,10 @@
       <c r="A1299" s="7" t="s">
         <v>2694</v>
       </c>
-      <c r="B1299" s="17" t="s">
+      <c r="B1299" s="9" t="s">
         <v>2695</v>
       </c>
-      <c r="C1299" s="19" t="s">
+      <c r="C1299" s="15" t="s">
         <v>2696</v>
       </c>
       <c r="D1299" s="10" t="s">
@@ -30189,10 +30188,10 @@
       <c r="A1300" s="1" t="s">
         <v>2698</v>
       </c>
-      <c r="B1300" s="17" t="s">
+      <c r="B1300" s="9" t="s">
         <v>2699</v>
       </c>
-      <c r="C1300" s="17" t="s">
+      <c r="C1300" s="9" t="s">
         <v>2700</v>
       </c>
       <c r="D1300" s="10" t="s">
@@ -30203,10 +30202,10 @@
       <c r="A1301" s="1" t="s">
         <v>2702</v>
       </c>
-      <c r="B1301" s="17" t="s">
+      <c r="B1301" s="9" t="s">
         <v>2703</v>
       </c>
-      <c r="C1301" s="17" t="s">
+      <c r="C1301" s="9" t="s">
         <v>2704</v>
       </c>
       <c r="D1301" s="10" t="s">
@@ -30217,10 +30216,10 @@
       <c r="A1302" s="1" t="s">
         <v>2706</v>
       </c>
-      <c r="B1302" s="17" t="s">
+      <c r="B1302" s="9" t="s">
         <v>2707</v>
       </c>
-      <c r="C1302" s="17" t="s">
+      <c r="C1302" s="9" t="s">
         <v>2708</v>
       </c>
       <c r="D1302" s="10" t="s">
@@ -30231,10 +30230,10 @@
       <c r="A1303" s="1" t="s">
         <v>2710</v>
       </c>
-      <c r="B1303" s="17" t="s">
+      <c r="B1303" s="9" t="s">
         <v>2711</v>
       </c>
-      <c r="C1303" s="17" t="s">
+      <c r="C1303" s="9" t="s">
         <v>2712</v>
       </c>
       <c r="D1303" s="10" t="s">
@@ -30245,10 +30244,10 @@
       <c r="A1304" s="1" t="s">
         <v>2714</v>
       </c>
-      <c r="B1304" s="17" t="s">
+      <c r="B1304" s="9" t="s">
         <v>2715</v>
       </c>
-      <c r="C1304" s="17" t="s">
+      <c r="C1304" s="9" t="s">
         <v>2716</v>
       </c>
       <c r="D1304" s="10" t="s">
@@ -30259,10 +30258,10 @@
       <c r="A1305" s="1" t="s">
         <v>2718</v>
       </c>
-      <c r="B1305" s="17" t="s">
+      <c r="B1305" s="9" t="s">
         <v>2719</v>
       </c>
-      <c r="C1305" s="17" t="s">
+      <c r="C1305" s="9" t="s">
         <v>2720</v>
       </c>
       <c r="D1305" s="10" t="s">
@@ -30273,10 +30272,10 @@
       <c r="A1306" s="1" t="s">
         <v>2722</v>
       </c>
-      <c r="B1306" s="17" t="s">
+      <c r="B1306" s="9" t="s">
         <v>2723</v>
       </c>
-      <c r="C1306" s="17" t="s">
+      <c r="C1306" s="9" t="s">
         <v>2724</v>
       </c>
       <c r="D1306" s="10" t="s">
@@ -30287,10 +30286,10 @@
       <c r="A1307" s="1" t="s">
         <v>2726</v>
       </c>
-      <c r="B1307" s="17" t="s">
+      <c r="B1307" s="9" t="s">
         <v>2727</v>
       </c>
-      <c r="C1307" s="17" t="s">
+      <c r="C1307" s="9" t="s">
         <v>2728</v>
       </c>
       <c r="D1307" s="10" t="s">
@@ -30301,10 +30300,10 @@
       <c r="A1308" s="1" t="s">
         <v>2730</v>
       </c>
-      <c r="B1308" s="17" t="s">
+      <c r="B1308" s="9" t="s">
         <v>2731</v>
       </c>
-      <c r="C1308" s="17" t="s">
+      <c r="C1308" s="9" t="s">
         <v>2732</v>
       </c>
       <c r="D1308" s="10" t="s">
@@ -30315,10 +30314,10 @@
       <c r="A1309" s="1" t="s">
         <v>2734</v>
       </c>
-      <c r="B1309" s="17" t="s">
+      <c r="B1309" s="9" t="s">
         <v>2735</v>
       </c>
-      <c r="C1309" s="17" t="s">
+      <c r="C1309" s="9" t="s">
         <v>2736</v>
       </c>
       <c r="D1309" s="10" t="s">
@@ -30329,10 +30328,10 @@
       <c r="A1310" s="1" t="s">
         <v>2738</v>
       </c>
-      <c r="B1310" s="17" t="s">
+      <c r="B1310" s="9" t="s">
         <v>2739</v>
       </c>
-      <c r="C1310" s="17" t="s">
+      <c r="C1310" s="9" t="s">
         <v>2740</v>
       </c>
       <c r="D1310" s="10" t="s">
@@ -30343,10 +30342,10 @@
       <c r="A1311" s="1" t="s">
         <v>2742</v>
       </c>
-      <c r="B1311" s="17" t="s">
+      <c r="B1311" s="9" t="s">
         <v>2743</v>
       </c>
-      <c r="C1311" s="17" t="s">
+      <c r="C1311" s="9" t="s">
         <v>2744</v>
       </c>
       <c r="D1311" s="10" t="s">
@@ -30357,10 +30356,10 @@
       <c r="A1312" s="1" t="s">
         <v>2746</v>
       </c>
-      <c r="B1312" s="17" t="s">
+      <c r="B1312" s="9" t="s">
         <v>2747</v>
       </c>
-      <c r="C1312" s="17" t="s">
+      <c r="C1312" s="9" t="s">
         <v>2748</v>
       </c>
       <c r="D1312" s="10" t="s">
@@ -30371,10 +30370,10 @@
       <c r="A1313" s="1" t="s">
         <v>2750</v>
       </c>
-      <c r="B1313" s="17" t="s">
+      <c r="B1313" s="9" t="s">
         <v>2751</v>
       </c>
-      <c r="C1313" s="17" t="s">
+      <c r="C1313" s="9" t="s">
         <v>2752</v>
       </c>
       <c r="D1313" s="10" t="s">
@@ -30385,10 +30384,10 @@
       <c r="A1314" s="7" t="s">
         <v>2754</v>
       </c>
-      <c r="B1314" s="17" t="s">
+      <c r="B1314" s="9" t="s">
         <v>2755</v>
       </c>
-      <c r="C1314" s="19" t="s">
+      <c r="C1314" s="15" t="s">
         <v>2756</v>
       </c>
       <c r="D1314" s="10" t="s">
@@ -30399,10 +30398,10 @@
       <c r="A1315" s="7" t="s">
         <v>2758</v>
       </c>
-      <c r="B1315" s="17" t="s">
+      <c r="B1315" s="9" t="s">
         <v>2759</v>
       </c>
-      <c r="C1315" s="19" t="s">
+      <c r="C1315" s="15" t="s">
         <v>2760</v>
       </c>
       <c r="D1315" s="10" t="s">
@@ -30413,10 +30412,10 @@
       <c r="A1316" s="7" t="s">
         <v>2762</v>
       </c>
-      <c r="B1316" s="17" t="s">
+      <c r="B1316" s="9" t="s">
         <v>2763</v>
       </c>
-      <c r="C1316" s="19" t="s">
+      <c r="C1316" s="15" t="s">
         <v>2764</v>
       </c>
       <c r="D1316" s="10" t="s">
@@ -30427,10 +30426,10 @@
       <c r="A1317" s="7" t="s">
         <v>2766</v>
       </c>
-      <c r="B1317" s="17" t="s">
+      <c r="B1317" s="9" t="s">
         <v>2767</v>
       </c>
-      <c r="C1317" s="19" t="s">
+      <c r="C1317" s="15" t="s">
         <v>2768</v>
       </c>
       <c r="D1317" s="10" t="s">
@@ -30441,10 +30440,10 @@
       <c r="A1318" s="1" t="s">
         <v>2770</v>
       </c>
-      <c r="B1318" s="17" t="s">
+      <c r="B1318" s="9" t="s">
         <v>2771</v>
       </c>
-      <c r="C1318" s="17" t="s">
+      <c r="C1318" s="9" t="s">
         <v>2772</v>
       </c>
       <c r="D1318" s="10" t="s">
@@ -30455,10 +30454,10 @@
       <c r="A1319" s="7" t="s">
         <v>2774</v>
       </c>
-      <c r="B1319" s="17" t="s">
+      <c r="B1319" s="9" t="s">
         <v>2775</v>
       </c>
-      <c r="C1319" s="19" t="s">
+      <c r="C1319" s="15" t="s">
         <v>2776</v>
       </c>
       <c r="D1319" s="10" t="s">
@@ -30469,10 +30468,10 @@
       <c r="A1320" s="7" t="s">
         <v>2778</v>
       </c>
-      <c r="B1320" s="17" t="s">
+      <c r="B1320" s="9" t="s">
         <v>2779</v>
       </c>
-      <c r="C1320" s="19" t="s">
+      <c r="C1320" s="15" t="s">
         <v>2780</v>
       </c>
       <c r="D1320" s="10" t="s">
@@ -30483,10 +30482,10 @@
       <c r="A1321" s="7" t="s">
         <v>2782</v>
       </c>
-      <c r="B1321" s="17" t="s">
+      <c r="B1321" s="9" t="s">
         <v>2783</v>
       </c>
-      <c r="C1321" s="19" t="s">
+      <c r="C1321" s="15" t="s">
         <v>2784</v>
       </c>
       <c r="D1321" s="10" t="s">
@@ -30497,10 +30496,10 @@
       <c r="A1322" s="7" t="s">
         <v>2786</v>
       </c>
-      <c r="B1322" s="17" t="s">
+      <c r="B1322" s="9" t="s">
         <v>2787</v>
       </c>
-      <c r="C1322" s="19" t="s">
+      <c r="C1322" s="15" t="s">
         <v>2788</v>
       </c>
       <c r="D1322" s="10" t="s">
@@ -30511,10 +30510,10 @@
       <c r="A1323" s="8" t="s">
         <v>2790</v>
       </c>
-      <c r="B1323" s="18" t="s">
+      <c r="B1323" s="16" t="s">
         <v>2791</v>
       </c>
-      <c r="C1323" s="18" t="s">
+      <c r="C1323" s="16" t="s">
         <v>2792</v>
       </c>
       <c r="D1323" s="10" t="s">
@@ -30525,10 +30524,10 @@
       <c r="A1324" s="8" t="s">
         <v>2794</v>
       </c>
-      <c r="B1324" s="18" t="s">
+      <c r="B1324" s="16" t="s">
         <v>2795</v>
       </c>
-      <c r="C1324" s="18" t="s">
+      <c r="C1324" s="16" t="s">
         <v>2796</v>
       </c>
       <c r="D1324" s="10" t="s">
@@ -30539,10 +30538,10 @@
       <c r="A1325" s="1" t="s">
         <v>2798</v>
       </c>
-      <c r="B1325" s="17" t="s">
+      <c r="B1325" s="9" t="s">
         <v>2799</v>
       </c>
-      <c r="C1325" s="17" t="s">
+      <c r="C1325" s="9" t="s">
         <v>2800</v>
       </c>
       <c r="D1325" s="10" t="s">
@@ -30553,10 +30552,10 @@
       <c r="A1326" s="7" t="s">
         <v>2802</v>
       </c>
-      <c r="B1326" s="17" t="s">
+      <c r="B1326" s="9" t="s">
         <v>2803</v>
       </c>
-      <c r="C1326" s="19" t="s">
+      <c r="C1326" s="15" t="s">
         <v>2804</v>
       </c>
       <c r="D1326" s="10" t="s">
@@ -30567,10 +30566,10 @@
       <c r="A1327" s="7" t="s">
         <v>2806</v>
       </c>
-      <c r="B1327" s="17" t="s">
+      <c r="B1327" s="9" t="s">
         <v>2807</v>
       </c>
-      <c r="C1327" s="19" t="s">
+      <c r="C1327" s="15" t="s">
         <v>2808</v>
       </c>
       <c r="D1327" s="10" t="s">
@@ -30581,10 +30580,10 @@
       <c r="A1328" s="7" t="s">
         <v>2810</v>
       </c>
-      <c r="B1328" s="17" t="s">
+      <c r="B1328" s="9" t="s">
         <v>2811</v>
       </c>
-      <c r="C1328" s="19" t="s">
+      <c r="C1328" s="15" t="s">
         <v>2812</v>
       </c>
       <c r="D1328" s="10" t="s">
@@ -30595,10 +30594,10 @@
       <c r="A1329" s="1" t="s">
         <v>2814</v>
       </c>
-      <c r="B1329" s="17" t="s">
+      <c r="B1329" s="9" t="s">
         <v>2815</v>
       </c>
-      <c r="C1329" s="17" t="s">
+      <c r="C1329" s="9" t="s">
         <v>2816</v>
       </c>
       <c r="D1329" s="10" t="s">
@@ -30609,10 +30608,10 @@
       <c r="A1330" s="1" t="s">
         <v>2818</v>
       </c>
-      <c r="B1330" s="17" t="s">
+      <c r="B1330" s="9" t="s">
         <v>2819</v>
       </c>
-      <c r="C1330" s="17" t="s">
+      <c r="C1330" s="9" t="s">
         <v>2820</v>
       </c>
       <c r="D1330" s="10" t="s">
@@ -30623,10 +30622,10 @@
       <c r="A1331" s="1" t="s">
         <v>2822</v>
       </c>
-      <c r="B1331" s="17" t="s">
+      <c r="B1331" s="9" t="s">
         <v>2823</v>
       </c>
-      <c r="C1331" s="17" t="s">
+      <c r="C1331" s="9" t="s">
         <v>2824</v>
       </c>
       <c r="D1331" s="10" t="s">
@@ -30637,10 +30636,10 @@
       <c r="A1332" s="1" t="s">
         <v>2826</v>
       </c>
-      <c r="B1332" s="17" t="s">
+      <c r="B1332" s="9" t="s">
         <v>2827</v>
       </c>
-      <c r="C1332" s="17" t="s">
+      <c r="C1332" s="9" t="s">
         <v>2828</v>
       </c>
       <c r="D1332" s="10" t="s">
@@ -30651,10 +30650,10 @@
       <c r="A1333" s="1" t="s">
         <v>2830</v>
       </c>
-      <c r="B1333" s="18" t="s">
+      <c r="B1333" s="16" t="s">
         <v>2831</v>
       </c>
-      <c r="C1333" s="17" t="s">
+      <c r="C1333" s="9" t="s">
         <v>2832</v>
       </c>
       <c r="D1333" s="10" t="s">
@@ -30665,10 +30664,10 @@
       <c r="A1334" s="1" t="s">
         <v>2834</v>
       </c>
-      <c r="B1334" s="18" t="s">
+      <c r="B1334" s="16" t="s">
         <v>2835</v>
       </c>
-      <c r="C1334" s="17" t="s">
+      <c r="C1334" s="9" t="s">
         <v>2836</v>
       </c>
       <c r="D1334" s="10" t="s">
@@ -30679,10 +30678,10 @@
       <c r="A1335" s="1" t="s">
         <v>2838</v>
       </c>
-      <c r="B1335" s="18" t="s">
+      <c r="B1335" s="16" t="s">
         <v>2839</v>
       </c>
-      <c r="C1335" s="17" t="s">
+      <c r="C1335" s="9" t="s">
         <v>2840</v>
       </c>
       <c r="D1335" s="10" t="s">
@@ -30693,10 +30692,10 @@
       <c r="A1336" s="1" t="s">
         <v>2842</v>
       </c>
-      <c r="B1336" s="18" t="s">
+      <c r="B1336" s="16" t="s">
         <v>2843</v>
       </c>
-      <c r="C1336" s="17" t="s">
+      <c r="C1336" s="9" t="s">
         <v>2844</v>
       </c>
       <c r="D1336" s="10" t="s">
@@ -30707,10 +30706,10 @@
       <c r="A1337" s="1" t="s">
         <v>2846</v>
       </c>
-      <c r="B1337" s="18" t="s">
+      <c r="B1337" s="16" t="s">
         <v>2847</v>
       </c>
-      <c r="C1337" s="17" t="s">
+      <c r="C1337" s="9" t="s">
         <v>2848</v>
       </c>
       <c r="D1337" s="10" t="s">
@@ -30721,10 +30720,10 @@
       <c r="A1338" s="7" t="s">
         <v>2850</v>
       </c>
-      <c r="B1338" s="17" t="s">
+      <c r="B1338" s="9" t="s">
         <v>2851</v>
       </c>
-      <c r="C1338" s="19" t="s">
+      <c r="C1338" s="15" t="s">
         <v>2852</v>
       </c>
       <c r="D1338" s="10" t="s">
@@ -30735,10 +30734,10 @@
       <c r="A1339" s="7" t="s">
         <v>2854</v>
       </c>
-      <c r="B1339" s="17" t="s">
+      <c r="B1339" s="9" t="s">
         <v>2855</v>
       </c>
-      <c r="C1339" s="19" t="s">
+      <c r="C1339" s="15" t="s">
         <v>2856</v>
       </c>
       <c r="D1339" s="10" t="s">
@@ -30749,10 +30748,10 @@
       <c r="A1340" s="7" t="s">
         <v>2858</v>
       </c>
-      <c r="B1340" s="17" t="s">
+      <c r="B1340" s="9" t="s">
         <v>2859</v>
       </c>
-      <c r="C1340" s="19" t="s">
+      <c r="C1340" s="15" t="s">
         <v>2860</v>
       </c>
       <c r="D1340" s="10" t="s">
@@ -30763,10 +30762,10 @@
       <c r="A1341" s="1" t="s">
         <v>2862</v>
       </c>
-      <c r="B1341" s="17" t="s">
+      <c r="B1341" s="9" t="s">
         <v>2863</v>
       </c>
-      <c r="C1341" s="17" t="s">
+      <c r="C1341" s="9" t="s">
         <v>2864</v>
       </c>
       <c r="D1341" s="10" t="s">
@@ -30777,10 +30776,10 @@
       <c r="A1342" s="7" t="s">
         <v>2866</v>
       </c>
-      <c r="B1342" s="17" t="s">
+      <c r="B1342" s="9" t="s">
         <v>2867</v>
       </c>
-      <c r="C1342" s="19" t="s">
+      <c r="C1342" s="15" t="s">
         <v>2868</v>
       </c>
       <c r="D1342" s="10" t="s">
@@ -30791,10 +30790,10 @@
       <c r="A1343" s="7" t="s">
         <v>2870</v>
       </c>
-      <c r="B1343" s="17" t="s">
+      <c r="B1343" s="9" t="s">
         <v>2871</v>
       </c>
-      <c r="C1343" s="19" t="s">
+      <c r="C1343" s="15" t="s">
         <v>2872</v>
       </c>
       <c r="D1343" s="10" t="s">
@@ -30805,10 +30804,10 @@
       <c r="A1344" s="7" t="s">
         <v>2874</v>
       </c>
-      <c r="B1344" s="17" t="s">
+      <c r="B1344" s="9" t="s">
         <v>2875</v>
       </c>
-      <c r="C1344" s="19" t="s">
+      <c r="C1344" s="15" t="s">
         <v>2876</v>
       </c>
       <c r="D1344" s="10" t="s">
@@ -30819,10 +30818,10 @@
       <c r="A1345" s="7" t="s">
         <v>2878</v>
       </c>
-      <c r="B1345" s="17" t="s">
+      <c r="B1345" s="9" t="s">
         <v>2879</v>
       </c>
-      <c r="C1345" s="19" t="s">
+      <c r="C1345" s="15" t="s">
         <v>2880</v>
       </c>
       <c r="D1345" s="10" t="s">
@@ -30833,10 +30832,10 @@
       <c r="A1346" s="7" t="s">
         <v>2882</v>
       </c>
-      <c r="B1346" s="18" t="s">
+      <c r="B1346" s="16" t="s">
         <v>2883</v>
       </c>
-      <c r="C1346" s="19" t="s">
+      <c r="C1346" s="15" t="s">
         <v>2884</v>
       </c>
       <c r="D1346" s="10" t="s">
@@ -30847,10 +30846,10 @@
       <c r="A1347" s="7" t="s">
         <v>2886</v>
       </c>
-      <c r="B1347" s="19" t="s">
+      <c r="B1347" s="15" t="s">
         <v>2887</v>
       </c>
-      <c r="C1347" s="19" t="s">
+      <c r="C1347" s="15" t="s">
         <v>2888</v>
       </c>
       <c r="D1347" s="10" t="s">
@@ -30861,10 +30860,10 @@
       <c r="A1348" s="7" t="s">
         <v>2890</v>
       </c>
-      <c r="B1348" s="19" t="s">
+      <c r="B1348" s="15" t="s">
         <v>2891</v>
       </c>
-      <c r="C1348" s="19" t="s">
+      <c r="C1348" s="15" t="s">
         <v>2892</v>
       </c>
       <c r="D1348" s="10" t="s">
@@ -30875,10 +30874,10 @@
       <c r="A1349" s="7" t="s">
         <v>2894</v>
       </c>
-      <c r="B1349" s="19" t="s">
+      <c r="B1349" s="15" t="s">
         <v>2895</v>
       </c>
-      <c r="C1349" s="19" t="s">
+      <c r="C1349" s="15" t="s">
         <v>2896</v>
       </c>
       <c r="D1349" s="10" t="s">
@@ -30889,10 +30888,10 @@
       <c r="A1350" s="7" t="s">
         <v>2898</v>
       </c>
-      <c r="B1350" s="19" t="s">
+      <c r="B1350" s="15" t="s">
         <v>2899</v>
       </c>
-      <c r="C1350" s="19" t="s">
+      <c r="C1350" s="15" t="s">
         <v>2900</v>
       </c>
       <c r="D1350" s="10" t="s">
@@ -30903,10 +30902,10 @@
       <c r="A1351" s="7" t="s">
         <v>2902</v>
       </c>
-      <c r="B1351" s="19" t="s">
+      <c r="B1351" s="15" t="s">
         <v>2903</v>
       </c>
-      <c r="C1351" s="19" t="s">
+      <c r="C1351" s="15" t="s">
         <v>2904</v>
       </c>
       <c r="D1351" s="10" t="s">
@@ -30917,10 +30916,10 @@
       <c r="A1352" s="1" t="s">
         <v>2906</v>
       </c>
-      <c r="B1352" s="18" t="s">
+      <c r="B1352" s="16" t="s">
         <v>2907</v>
       </c>
-      <c r="C1352" s="17" t="s">
+      <c r="C1352" s="9" t="s">
         <v>2908</v>
       </c>
       <c r="D1352" s="10" t="s">
@@ -30928,13 +30927,13 @@
       </c>
     </row>
     <row r="1353" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1353" s="20" t="s">
+      <c r="A1353" s="17" t="s">
         <v>2910</v>
       </c>
-      <c r="B1353" s="21" t="s">
+      <c r="B1353" s="30" t="s">
         <v>2911</v>
       </c>
-      <c r="C1353" s="22" t="s">
+      <c r="C1353" s="31" t="s">
         <v>2912</v>
       </c>
       <c r="D1353" s="10" t="s">
@@ -30942,13 +30941,13 @@
       </c>
     </row>
     <row r="1354" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1354" s="23" t="s">
+      <c r="A1354" s="18" t="s">
         <v>2914</v>
       </c>
-      <c r="B1354" s="25" t="s">
+      <c r="B1354" s="19" t="s">
         <v>2915</v>
       </c>
-      <c r="C1354" s="24" t="s">
+      <c r="C1354" s="32" t="s">
         <v>2916</v>
       </c>
       <c r="D1354" s="10" t="s">
@@ -30956,13 +30955,13 @@
       </c>
     </row>
     <row r="1355" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1355" s="26" t="s">
+      <c r="A1355" s="20" t="s">
         <v>2918</v>
       </c>
-      <c r="B1355" s="25" t="s">
+      <c r="B1355" s="19" t="s">
         <v>2919</v>
       </c>
-      <c r="C1355" s="25" t="s">
+      <c r="C1355" s="19" t="s">
         <v>2920</v>
       </c>
       <c r="D1355" s="10" t="s">
@@ -30973,10 +30972,10 @@
       <c r="A1356" s="7" t="s">
         <v>2922</v>
       </c>
-      <c r="B1356" s="18" t="s">
+      <c r="B1356" s="16" t="s">
         <v>2923</v>
       </c>
-      <c r="C1356" s="19" t="s">
+      <c r="C1356" s="15" t="s">
         <v>2924</v>
       </c>
       <c r="D1356" s="10" t="s">
@@ -30987,10 +30986,10 @@
       <c r="A1357" s="7" t="s">
         <v>2926</v>
       </c>
-      <c r="B1357" s="18" t="s">
+      <c r="B1357" s="16" t="s">
         <v>2927</v>
       </c>
-      <c r="C1357" s="19" t="s">
+      <c r="C1357" s="15" t="s">
         <v>2928</v>
       </c>
       <c r="D1357" s="10" t="s">
@@ -31001,10 +31000,10 @@
       <c r="A1358" s="1" t="s">
         <v>2930</v>
       </c>
-      <c r="B1358" s="18" t="s">
+      <c r="B1358" s="16" t="s">
         <v>2931</v>
       </c>
-      <c r="C1358" s="17" t="s">
+      <c r="C1358" s="9" t="s">
         <v>2932</v>
       </c>
       <c r="D1358" s="10" t="s">
@@ -31015,10 +31014,10 @@
       <c r="A1359" s="1" t="s">
         <v>2934</v>
       </c>
-      <c r="B1359" s="18" t="s">
+      <c r="B1359" s="16" t="s">
         <v>2935</v>
       </c>
-      <c r="C1359" s="17" t="s">
+      <c r="C1359" s="9" t="s">
         <v>2936</v>
       </c>
       <c r="D1359" s="10" t="s">
@@ -31029,10 +31028,10 @@
       <c r="A1360" s="7" t="s">
         <v>2938</v>
       </c>
-      <c r="B1360" s="18" t="s">
+      <c r="B1360" s="16" t="s">
         <v>2939</v>
       </c>
-      <c r="C1360" s="19" t="s">
+      <c r="C1360" s="15" t="s">
         <v>2940</v>
       </c>
       <c r="D1360" s="10" t="s">
@@ -31043,10 +31042,10 @@
       <c r="A1361" s="7" t="s">
         <v>2942</v>
       </c>
-      <c r="B1361" s="17" t="s">
+      <c r="B1361" s="9" t="s">
         <v>2943</v>
       </c>
-      <c r="C1361" s="19" t="s">
+      <c r="C1361" s="15" t="s">
         <v>2945</v>
       </c>
       <c r="D1361" s="10" t="s">
@@ -31057,10 +31056,10 @@
       <c r="A1362" s="7" t="s">
         <v>2946</v>
       </c>
-      <c r="B1362" s="17" t="s">
+      <c r="B1362" s="9" t="s">
         <v>2947</v>
       </c>
-      <c r="C1362" s="19" t="s">
+      <c r="C1362" s="15" t="s">
         <v>2948</v>
       </c>
       <c r="D1362" s="10" t="s">
@@ -31071,10 +31070,10 @@
       <c r="A1363" s="7" t="s">
         <v>2950</v>
       </c>
-      <c r="B1363" s="17" t="s">
+      <c r="B1363" s="9" t="s">
         <v>2951</v>
       </c>
-      <c r="C1363" s="19" t="s">
+      <c r="C1363" s="15" t="s">
         <v>2952</v>
       </c>
       <c r="D1363" s="10" t="s">
@@ -31085,10 +31084,10 @@
       <c r="A1364" s="7" t="s">
         <v>2954</v>
       </c>
-      <c r="B1364" s="17" t="s">
+      <c r="B1364" s="9" t="s">
         <v>2955</v>
       </c>
-      <c r="C1364" s="19" t="s">
+      <c r="C1364" s="15" t="s">
         <v>2956</v>
       </c>
       <c r="D1364" s="10" t="s">
@@ -31099,10 +31098,10 @@
       <c r="A1365" s="7" t="s">
         <v>2958</v>
       </c>
-      <c r="B1365" s="17" t="s">
+      <c r="B1365" s="9" t="s">
         <v>2959</v>
       </c>
-      <c r="C1365" s="19" t="s">
+      <c r="C1365" s="15" t="s">
         <v>2960</v>
       </c>
       <c r="D1365" s="10" t="s">
@@ -31113,10 +31112,10 @@
       <c r="A1366" s="7" t="s">
         <v>2962</v>
       </c>
-      <c r="B1366" s="17" t="s">
+      <c r="B1366" s="9" t="s">
         <v>2963</v>
       </c>
-      <c r="C1366" s="19" t="s">
+      <c r="C1366" s="15" t="s">
         <v>2964</v>
       </c>
       <c r="D1366" s="10" t="s">
@@ -31127,10 +31126,10 @@
       <c r="A1367" s="7" t="s">
         <v>2966</v>
       </c>
-      <c r="B1367" s="17" t="s">
+      <c r="B1367" s="9" t="s">
         <v>2967</v>
       </c>
-      <c r="C1367" s="19" t="s">
+      <c r="C1367" s="15" t="s">
         <v>2968</v>
       </c>
       <c r="D1367" s="10" t="s">
@@ -31141,10 +31140,10 @@
       <c r="A1368" s="1" t="s">
         <v>2970</v>
       </c>
-      <c r="B1368" s="17" t="s">
+      <c r="B1368" s="9" t="s">
         <v>2971</v>
       </c>
-      <c r="C1368" s="17" t="s">
+      <c r="C1368" s="9" t="s">
         <v>2972</v>
       </c>
       <c r="D1368" s="10" t="s">
@@ -31155,10 +31154,10 @@
       <c r="A1369" s="1" t="s">
         <v>2974</v>
       </c>
-      <c r="B1369" s="17" t="s">
+      <c r="B1369" s="9" t="s">
         <v>2975</v>
       </c>
-      <c r="C1369" s="17" t="s">
+      <c r="C1369" s="9" t="s">
         <v>2976</v>
       </c>
       <c r="D1369" s="10" t="s">
@@ -31169,10 +31168,10 @@
       <c r="A1370" s="1" t="s">
         <v>2978</v>
       </c>
-      <c r="B1370" s="17" t="s">
+      <c r="B1370" s="9" t="s">
         <v>2979</v>
       </c>
-      <c r="C1370" s="17" t="s">
+      <c r="C1370" s="9" t="s">
         <v>2980</v>
       </c>
       <c r="D1370" s="10" t="s">
@@ -31183,10 +31182,10 @@
       <c r="A1371" s="1" t="s">
         <v>2982</v>
       </c>
-      <c r="B1371" s="17" t="s">
+      <c r="B1371" s="9" t="s">
         <v>2983</v>
       </c>
-      <c r="C1371" s="17" t="s">
+      <c r="C1371" s="9" t="s">
         <v>2984</v>
       </c>
       <c r="D1371" s="10" t="s">
@@ -31197,10 +31196,10 @@
       <c r="A1372" s="1" t="s">
         <v>2986</v>
       </c>
-      <c r="B1372" s="17" t="s">
+      <c r="B1372" s="9" t="s">
         <v>2987</v>
       </c>
-      <c r="C1372" s="17" t="s">
+      <c r="C1372" s="9" t="s">
         <v>2988</v>
       </c>
       <c r="D1372" s="10" t="s">
@@ -31211,10 +31210,10 @@
       <c r="A1373" s="1" t="s">
         <v>2990</v>
       </c>
-      <c r="B1373" s="17" t="s">
+      <c r="B1373" s="9" t="s">
         <v>2991</v>
       </c>
-      <c r="C1373" s="17" t="s">
+      <c r="C1373" s="9" t="s">
         <v>2992</v>
       </c>
       <c r="D1373" s="10" t="s">
@@ -31225,10 +31224,10 @@
       <c r="A1374" s="1" t="s">
         <v>2994</v>
       </c>
-      <c r="B1374" s="17" t="s">
+      <c r="B1374" s="9" t="s">
         <v>2995</v>
       </c>
-      <c r="C1374" s="17" t="s">
+      <c r="C1374" s="9" t="s">
         <v>2996</v>
       </c>
       <c r="D1374" s="10" t="s">
@@ -31239,10 +31238,10 @@
       <c r="A1375" s="7" t="s">
         <v>2998</v>
       </c>
-      <c r="B1375" s="17" t="s">
+      <c r="B1375" s="9" t="s">
         <v>2999</v>
       </c>
-      <c r="C1375" s="19" t="s">
+      <c r="C1375" s="15" t="s">
         <v>3000</v>
       </c>
       <c r="D1375" s="10" t="s">
@@ -31253,10 +31252,10 @@
       <c r="A1376" s="7" t="s">
         <v>3002</v>
       </c>
-      <c r="B1376" s="17" t="s">
+      <c r="B1376" s="9" t="s">
         <v>3003</v>
       </c>
-      <c r="C1376" s="19" t="s">
+      <c r="C1376" s="15" t="s">
         <v>3004</v>
       </c>
       <c r="D1376" s="10" t="s">
@@ -31267,10 +31266,10 @@
       <c r="A1377" s="7" t="s">
         <v>3006</v>
       </c>
-      <c r="B1377" s="17" t="s">
+      <c r="B1377" s="9" t="s">
         <v>3007</v>
       </c>
-      <c r="C1377" s="19" t="s">
+      <c r="C1377" s="15" t="s">
         <v>3008</v>
       </c>
       <c r="D1377" s="10" t="s">
@@ -31281,10 +31280,10 @@
       <c r="A1378" s="7" t="s">
         <v>3010</v>
       </c>
-      <c r="B1378" s="17" t="s">
+      <c r="B1378" s="9" t="s">
         <v>3011</v>
       </c>
-      <c r="C1378" s="19" t="s">
+      <c r="C1378" s="15" t="s">
         <v>3012</v>
       </c>
       <c r="D1378" s="10" t="s">
@@ -31292,13 +31291,13 @@
       </c>
     </row>
     <row r="1379" spans="1:4" ht="39" x14ac:dyDescent="0.25">
-      <c r="A1379" s="20" t="s">
+      <c r="A1379" s="17" t="s">
         <v>3014</v>
       </c>
-      <c r="B1379" s="27" t="s">
+      <c r="B1379" s="33" t="s">
         <v>3015</v>
       </c>
-      <c r="C1379" s="22" t="s">
+      <c r="C1379" s="31" t="s">
         <v>3016</v>
       </c>
       <c r="D1379" s="10" t="s">
@@ -31306,16 +31305,16 @@
       </c>
     </row>
     <row r="1380" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1380" s="28" t="s">
+      <c r="A1380" s="21" t="s">
         <v>3021</v>
       </c>
-      <c r="B1380" s="29" t="s">
+      <c r="B1380" s="22" t="s">
         <v>3022</v>
       </c>
-      <c r="C1380" s="29" t="s">
+      <c r="C1380" s="22" t="s">
         <v>3019</v>
       </c>
-      <c r="D1380" s="29" t="s">
+      <c r="D1380" s="22" t="s">
         <v>3020</v>
       </c>
     </row>
@@ -31323,10 +31322,10 @@
       <c r="A1381" s="7" t="s">
         <v>3026</v>
       </c>
-      <c r="B1381" s="19" t="s">
+      <c r="B1381" s="15" t="s">
         <v>3023</v>
       </c>
-      <c r="C1381" s="19" t="s">
+      <c r="C1381" s="15" t="s">
         <v>3024</v>
       </c>
       <c r="D1381" s="10" t="s">
@@ -31337,10 +31336,10 @@
       <c r="A1382" s="7" t="s">
         <v>3030</v>
       </c>
-      <c r="B1382" s="19" t="s">
+      <c r="B1382" s="15" t="s">
         <v>3027</v>
       </c>
-      <c r="C1382" s="19" t="s">
+      <c r="C1382" s="15" t="s">
         <v>3028</v>
       </c>
       <c r="D1382" s="10" t="s">
@@ -31351,10 +31350,10 @@
       <c r="A1383" s="7" t="s">
         <v>3034</v>
       </c>
-      <c r="B1383" s="19" t="s">
+      <c r="B1383" s="15" t="s">
         <v>3031</v>
       </c>
-      <c r="C1383" s="19" t="s">
+      <c r="C1383" s="15" t="s">
         <v>3032</v>
       </c>
       <c r="D1383" s="10" t="s">
@@ -31365,10 +31364,10 @@
       <c r="A1384" s="7" t="s">
         <v>3038</v>
       </c>
-      <c r="B1384" s="19" t="s">
+      <c r="B1384" s="15" t="s">
         <v>3035</v>
       </c>
-      <c r="C1384" s="19" t="s">
+      <c r="C1384" s="15" t="s">
         <v>3036</v>
       </c>
       <c r="D1384" s="10" t="s">
@@ -31376,13 +31375,13 @@
       </c>
     </row>
     <row r="1385" spans="1:4" ht="39" x14ac:dyDescent="0.25">
-      <c r="A1385" s="20" t="s">
+      <c r="A1385" s="17" t="s">
         <v>3039</v>
       </c>
-      <c r="B1385" s="22" t="s">
+      <c r="B1385" s="31" t="s">
         <v>3018</v>
       </c>
-      <c r="C1385" s="22" t="s">
+      <c r="C1385" s="31" t="s">
         <v>3019</v>
       </c>
       <c r="D1385" s="10" t="s">
@@ -31390,13 +31389,13 @@
       </c>
     </row>
     <row r="1386" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1386" s="28" t="s">
+      <c r="A1386" s="21" t="s">
         <v>3041</v>
       </c>
-      <c r="B1386" s="29" t="s">
+      <c r="B1386" s="22" t="s">
         <v>3040</v>
       </c>
-      <c r="C1386" s="29" t="s">
+      <c r="C1386" s="22" t="s">
         <v>3042</v>
       </c>
       <c r="D1386" s="10" t="s">
@@ -31407,10 +31406,10 @@
       <c r="A1387" s="1" t="s">
         <v>3044</v>
       </c>
-      <c r="B1387" s="17" t="s">
+      <c r="B1387" s="9" t="s">
         <v>3045</v>
       </c>
-      <c r="C1387" s="17" t="s">
+      <c r="C1387" s="9" t="s">
         <v>3046</v>
       </c>
       <c r="D1387" s="10" t="s">
@@ -31421,10 +31420,10 @@
       <c r="A1388" s="1" t="s">
         <v>3048</v>
       </c>
-      <c r="B1388" s="17" t="s">
+      <c r="B1388" s="9" t="s">
         <v>3049</v>
       </c>
-      <c r="C1388" s="17" t="s">
+      <c r="C1388" s="9" t="s">
         <v>3050</v>
       </c>
       <c r="D1388" s="10" t="s">
@@ -31435,10 +31434,10 @@
       <c r="A1389" s="1" t="s">
         <v>3052</v>
       </c>
-      <c r="B1389" s="17" t="s">
+      <c r="B1389" s="9" t="s">
         <v>3053</v>
       </c>
-      <c r="C1389" s="17" t="s">
+      <c r="C1389" s="9" t="s">
         <v>3054</v>
       </c>
       <c r="D1389" s="10" t="s">
@@ -31449,10 +31448,10 @@
       <c r="A1390" s="1" t="s">
         <v>3056</v>
       </c>
-      <c r="B1390" s="17" t="s">
+      <c r="B1390" s="9" t="s">
         <v>3057</v>
       </c>
-      <c r="C1390" s="17" t="s">
+      <c r="C1390" s="9" t="s">
         <v>3058</v>
       </c>
       <c r="D1390" s="10" t="s">
@@ -31463,10 +31462,10 @@
       <c r="A1391" s="7" t="s">
         <v>3060</v>
       </c>
-      <c r="B1391" s="17" t="s">
+      <c r="B1391" s="9" t="s">
         <v>3061</v>
       </c>
-      <c r="C1391" s="19" t="s">
+      <c r="C1391" s="15" t="s">
         <v>3062</v>
       </c>
       <c r="D1391" s="10" t="s">
@@ -31477,10 +31476,10 @@
       <c r="A1392" s="7" t="s">
         <v>3064</v>
       </c>
-      <c r="B1392" s="17" t="s">
+      <c r="B1392" s="9" t="s">
         <v>3065</v>
       </c>
-      <c r="C1392" s="19" t="s">
+      <c r="C1392" s="15" t="s">
         <v>3066</v>
       </c>
       <c r="D1392" s="10" t="s">
@@ -31491,10 +31490,10 @@
       <c r="A1393" s="7" t="s">
         <v>3068</v>
       </c>
-      <c r="B1393" s="17" t="s">
+      <c r="B1393" s="9" t="s">
         <v>3069</v>
       </c>
-      <c r="C1393" s="19" t="s">
+      <c r="C1393" s="15" t="s">
         <v>3070</v>
       </c>
       <c r="D1393" s="10" t="s">
@@ -31505,10 +31504,10 @@
       <c r="A1394" s="1" t="s">
         <v>3072</v>
       </c>
-      <c r="B1394" s="18" t="s">
+      <c r="B1394" s="16" t="s">
         <v>3073</v>
       </c>
-      <c r="C1394" s="19" t="s">
+      <c r="C1394" s="15" t="s">
         <v>3074</v>
       </c>
       <c r="D1394" s="10" t="s">
@@ -31519,10 +31518,10 @@
       <c r="A1395" s="7" t="s">
         <v>3076</v>
       </c>
-      <c r="B1395" s="18" t="s">
+      <c r="B1395" s="16" t="s">
         <v>3077</v>
       </c>
-      <c r="C1395" s="19" t="s">
+      <c r="C1395" s="15" t="s">
         <v>3078</v>
       </c>
       <c r="D1395" s="10" t="s">
@@ -31533,10 +31532,10 @@
       <c r="A1396" s="7" t="s">
         <v>3080</v>
       </c>
-      <c r="B1396" s="18" t="s">
+      <c r="B1396" s="16" t="s">
         <v>3081</v>
       </c>
-      <c r="C1396" s="19" t="s">
+      <c r="C1396" s="15" t="s">
         <v>3082</v>
       </c>
       <c r="D1396" s="10" t="s">
@@ -31547,10 +31546,10 @@
       <c r="A1397" s="7" t="s">
         <v>3084</v>
       </c>
-      <c r="B1397" s="18" t="s">
+      <c r="B1397" s="16" t="s">
         <v>3085</v>
       </c>
-      <c r="C1397" s="19" t="s">
+      <c r="C1397" s="15" t="s">
         <v>3086</v>
       </c>
       <c r="D1397" s="10" t="s">
@@ -31561,10 +31560,10 @@
       <c r="A1398" s="7" t="s">
         <v>3088</v>
       </c>
-      <c r="B1398" s="17" t="s">
+      <c r="B1398" s="9" t="s">
         <v>3089</v>
       </c>
-      <c r="C1398" s="19" t="s">
+      <c r="C1398" s="15" t="s">
         <v>3090</v>
       </c>
       <c r="D1398" s="10" t="s">
@@ -31575,10 +31574,10 @@
       <c r="A1399" s="7" t="s">
         <v>3092</v>
       </c>
-      <c r="B1399" s="17" t="s">
+      <c r="B1399" s="9" t="s">
         <v>3093</v>
       </c>
-      <c r="C1399" s="19" t="s">
+      <c r="C1399" s="15" t="s">
         <v>3094</v>
       </c>
       <c r="D1399" s="10" t="s">
@@ -31589,10 +31588,10 @@
       <c r="A1400" s="7" t="s">
         <v>3096</v>
       </c>
-      <c r="B1400" s="17" t="s">
+      <c r="B1400" s="9" t="s">
         <v>3097</v>
       </c>
-      <c r="C1400" s="19" t="s">
+      <c r="C1400" s="15" t="s">
         <v>3098</v>
       </c>
       <c r="D1400" s="10" t="s">
@@ -31603,10 +31602,10 @@
       <c r="A1401" s="7" t="s">
         <v>3100</v>
       </c>
-      <c r="B1401" s="17" t="s">
+      <c r="B1401" s="9" t="s">
         <v>3101</v>
       </c>
-      <c r="C1401" s="19" t="s">
+      <c r="C1401" s="15" t="s">
         <v>3102</v>
       </c>
       <c r="D1401" s="10" t="s">
@@ -31617,10 +31616,10 @@
       <c r="A1402" s="7" t="s">
         <v>3104</v>
       </c>
-      <c r="B1402" s="17" t="s">
+      <c r="B1402" s="9" t="s">
         <v>3105</v>
       </c>
-      <c r="C1402" s="19" t="s">
+      <c r="C1402" s="15" t="s">
         <v>3106</v>
       </c>
       <c r="D1402" s="10" t="s">
@@ -31631,10 +31630,10 @@
       <c r="A1403" s="7" t="s">
         <v>3108</v>
       </c>
-      <c r="B1403" s="17" t="s">
+      <c r="B1403" s="9" t="s">
         <v>3109</v>
       </c>
-      <c r="C1403" s="19" t="s">
+      <c r="C1403" s="15" t="s">
         <v>3110</v>
       </c>
       <c r="D1403" s="10" t="s">
@@ -31645,10 +31644,10 @@
       <c r="A1404" s="1" t="s">
         <v>3112</v>
       </c>
-      <c r="B1404" s="17" t="s">
+      <c r="B1404" s="9" t="s">
         <v>3113</v>
       </c>
-      <c r="C1404" s="17" t="s">
+      <c r="C1404" s="9" t="s">
         <v>3114</v>
       </c>
       <c r="D1404" s="10" t="s">
@@ -31659,10 +31658,10 @@
       <c r="A1405" s="7" t="s">
         <v>3116</v>
       </c>
-      <c r="B1405" s="17" t="s">
+      <c r="B1405" s="9" t="s">
         <v>3117</v>
       </c>
-      <c r="C1405" s="19" t="s">
+      <c r="C1405" s="15" t="s">
         <v>3118</v>
       </c>
       <c r="D1405" s="10" t="s">
@@ -31673,10 +31672,10 @@
       <c r="A1406" s="7" t="s">
         <v>3120</v>
       </c>
-      <c r="B1406" s="17" t="s">
+      <c r="B1406" s="9" t="s">
         <v>3121</v>
       </c>
-      <c r="C1406" s="19" t="s">
+      <c r="C1406" s="15" t="s">
         <v>3122</v>
       </c>
       <c r="D1406" s="10" t="s">
@@ -31687,10 +31686,10 @@
       <c r="A1407" s="7" t="s">
         <v>3124</v>
       </c>
-      <c r="B1407" s="17" t="s">
+      <c r="B1407" s="9" t="s">
         <v>3125</v>
       </c>
-      <c r="C1407" s="19" t="s">
+      <c r="C1407" s="15" t="s">
         <v>3126</v>
       </c>
       <c r="D1407" s="10" t="s">
@@ -31701,10 +31700,10 @@
       <c r="A1408" s="7" t="s">
         <v>3128</v>
       </c>
-      <c r="B1408" s="17" t="s">
+      <c r="B1408" s="9" t="s">
         <v>3129</v>
       </c>
-      <c r="C1408" s="19" t="s">
+      <c r="C1408" s="15" t="s">
         <v>3130</v>
       </c>
       <c r="D1408" s="10" t="s">
@@ -31715,10 +31714,10 @@
       <c r="A1409" s="7" t="s">
         <v>3132</v>
       </c>
-      <c r="B1409" s="19" t="s">
+      <c r="B1409" s="15" t="s">
         <v>3133</v>
       </c>
-      <c r="C1409" s="19" t="s">
+      <c r="C1409" s="15" t="s">
         <v>3134</v>
       </c>
       <c r="D1409" s="10" t="s">
@@ -31729,10 +31728,10 @@
       <c r="A1410" s="7" t="s">
         <v>3136</v>
       </c>
-      <c r="B1410" s="17" t="s">
+      <c r="B1410" s="9" t="s">
         <v>3137</v>
       </c>
-      <c r="C1410" s="19" t="s">
+      <c r="C1410" s="15" t="s">
         <v>3138</v>
       </c>
       <c r="D1410" s="10" t="s">
@@ -31743,10 +31742,10 @@
       <c r="A1411" s="7" t="s">
         <v>3140</v>
       </c>
-      <c r="B1411" s="17" t="s">
+      <c r="B1411" s="9" t="s">
         <v>3141</v>
       </c>
-      <c r="C1411" s="19" t="s">
+      <c r="C1411" s="15" t="s">
         <v>3142</v>
       </c>
       <c r="D1411" s="10" t="s">
@@ -31757,10 +31756,10 @@
       <c r="A1412" s="7" t="s">
         <v>3144</v>
       </c>
-      <c r="B1412" s="17" t="s">
+      <c r="B1412" s="9" t="s">
         <v>3145</v>
       </c>
-      <c r="C1412" s="19" t="s">
+      <c r="C1412" s="15" t="s">
         <v>3146</v>
       </c>
       <c r="D1412" s="10" t="s">
@@ -31771,10 +31770,10 @@
       <c r="A1413" s="7" t="s">
         <v>3148</v>
       </c>
-      <c r="B1413" s="17" t="s">
+      <c r="B1413" s="9" t="s">
         <v>3149</v>
       </c>
-      <c r="C1413" s="19" t="s">
+      <c r="C1413" s="15" t="s">
         <v>3150</v>
       </c>
       <c r="D1413" s="10" t="s">
@@ -31785,10 +31784,10 @@
       <c r="A1414" s="7" t="s">
         <v>3152</v>
       </c>
-      <c r="B1414" s="17" t="s">
+      <c r="B1414" s="9" t="s">
         <v>3153</v>
       </c>
-      <c r="C1414" s="19" t="s">
+      <c r="C1414" s="15" t="s">
         <v>3154</v>
       </c>
       <c r="D1414" s="10" t="s">
@@ -31799,10 +31798,10 @@
       <c r="A1415" s="7" t="s">
         <v>3156</v>
       </c>
-      <c r="B1415" s="19" t="s">
+      <c r="B1415" s="15" t="s">
         <v>3157</v>
       </c>
-      <c r="C1415" s="19" t="s">
+      <c r="C1415" s="15" t="s">
         <v>3158</v>
       </c>
       <c r="D1415" s="10" t="s">
@@ -31813,10 +31812,10 @@
       <c r="A1416" s="7" t="s">
         <v>3160</v>
       </c>
-      <c r="B1416" s="17" t="s">
+      <c r="B1416" s="9" t="s">
         <v>3161</v>
       </c>
-      <c r="C1416" s="19" t="s">
+      <c r="C1416" s="15" t="s">
         <v>3162</v>
       </c>
       <c r="D1416" s="10" t="s">
@@ -31827,10 +31826,10 @@
       <c r="A1417" s="7" t="s">
         <v>3164</v>
       </c>
-      <c r="B1417" s="17" t="s">
+      <c r="B1417" s="9" t="s">
         <v>3165</v>
       </c>
-      <c r="C1417" s="19" t="s">
+      <c r="C1417" s="15" t="s">
         <v>3166</v>
       </c>
       <c r="D1417" s="10" t="s">
@@ -31841,10 +31840,10 @@
       <c r="A1418" s="7" t="s">
         <v>3168</v>
       </c>
-      <c r="B1418" s="17" t="s">
+      <c r="B1418" s="9" t="s">
         <v>3169</v>
       </c>
-      <c r="C1418" s="19" t="s">
+      <c r="C1418" s="15" t="s">
         <v>3170</v>
       </c>
       <c r="D1418" s="10" t="s">
@@ -31855,10 +31854,10 @@
       <c r="A1419" s="7" t="s">
         <v>3172</v>
       </c>
-      <c r="B1419" s="17" t="s">
+      <c r="B1419" s="9" t="s">
         <v>3173</v>
       </c>
-      <c r="C1419" s="19" t="s">
+      <c r="C1419" s="15" t="s">
         <v>3174</v>
       </c>
       <c r="D1419" s="10" t="s">
@@ -31869,10 +31868,10 @@
       <c r="A1420" s="7" t="s">
         <v>3176</v>
       </c>
-      <c r="B1420" s="17" t="s">
+      <c r="B1420" s="9" t="s">
         <v>3177</v>
       </c>
-      <c r="C1420" s="19" t="s">
+      <c r="C1420" s="15" t="s">
         <v>3178</v>
       </c>
       <c r="D1420" s="10" t="s">
@@ -31883,10 +31882,10 @@
       <c r="A1421" s="7" t="s">
         <v>3180</v>
       </c>
-      <c r="B1421" s="17" t="s">
+      <c r="B1421" s="9" t="s">
         <v>3181</v>
       </c>
-      <c r="C1421" s="19" t="s">
+      <c r="C1421" s="15" t="s">
         <v>3182</v>
       </c>
       <c r="D1421" s="10" t="s">
@@ -31897,10 +31896,10 @@
       <c r="A1422" s="7" t="s">
         <v>3184</v>
       </c>
-      <c r="B1422" s="17" t="s">
+      <c r="B1422" s="9" t="s">
         <v>3185</v>
       </c>
-      <c r="C1422" s="19" t="s">
+      <c r="C1422" s="15" t="s">
         <v>3186</v>
       </c>
       <c r="D1422" s="10" t="s">
@@ -31911,10 +31910,10 @@
       <c r="A1423" s="7" t="s">
         <v>3188</v>
       </c>
-      <c r="B1423" s="17" t="s">
+      <c r="B1423" s="9" t="s">
         <v>3189</v>
       </c>
-      <c r="C1423" s="19" t="s">
+      <c r="C1423" s="15" t="s">
         <v>3190</v>
       </c>
       <c r="D1423" s="10" t="s">
@@ -31925,10 +31924,10 @@
       <c r="A1424" s="7" t="s">
         <v>3192</v>
       </c>
-      <c r="B1424" s="17" t="s">
+      <c r="B1424" s="9" t="s">
         <v>3193</v>
       </c>
-      <c r="C1424" s="31" t="s">
+      <c r="C1424" s="34" t="s">
         <v>3270</v>
       </c>
       <c r="D1424" s="10" t="s">
@@ -31939,10 +31938,10 @@
       <c r="A1425" s="5" t="s">
         <v>3194</v>
       </c>
-      <c r="B1425" s="30" t="s">
+      <c r="B1425" s="11" t="s">
         <v>3195</v>
       </c>
-      <c r="C1425" s="32" t="s">
+      <c r="C1425" s="35" t="s">
         <v>3272</v>
       </c>
       <c r="D1425" s="10" t="s">
@@ -31953,10 +31952,10 @@
       <c r="A1426" s="5" t="s">
         <v>3196</v>
       </c>
-      <c r="B1426" s="30" t="s">
+      <c r="B1426" s="11" t="s">
         <v>3197</v>
       </c>
-      <c r="C1426" s="32" t="s">
+      <c r="C1426" s="35" t="s">
         <v>3274</v>
       </c>
       <c r="D1426" s="10" t="s">
@@ -31967,10 +31966,10 @@
       <c r="A1427" s="5" t="s">
         <v>3198</v>
       </c>
-      <c r="B1427" s="30" t="s">
+      <c r="B1427" s="11" t="s">
         <v>3199</v>
       </c>
-      <c r="C1427" s="32" t="s">
+      <c r="C1427" s="35" t="s">
         <v>3276</v>
       </c>
       <c r="D1427" s="10" t="s">
@@ -31981,10 +31980,10 @@
       <c r="A1428" s="5" t="s">
         <v>3200</v>
       </c>
-      <c r="B1428" s="30" t="s">
+      <c r="B1428" s="11" t="s">
         <v>3201</v>
       </c>
-      <c r="C1428" s="32" t="s">
+      <c r="C1428" s="35" t="s">
         <v>3278</v>
       </c>
       <c r="D1428" s="10" t="s">
@@ -31995,10 +31994,10 @@
       <c r="A1429" s="5" t="s">
         <v>3202</v>
       </c>
-      <c r="B1429" s="30" t="s">
+      <c r="B1429" s="11" t="s">
         <v>3203</v>
       </c>
-      <c r="C1429" s="32" t="s">
+      <c r="C1429" s="35" t="s">
         <v>3280</v>
       </c>
       <c r="D1429" s="10" t="s">
@@ -32009,10 +32008,10 @@
       <c r="A1430" s="5" t="s">
         <v>3204</v>
       </c>
-      <c r="B1430" s="30" t="s">
+      <c r="B1430" s="11" t="s">
         <v>3205</v>
       </c>
-      <c r="C1430" s="32" t="s">
+      <c r="C1430" s="35" t="s">
         <v>3282</v>
       </c>
       <c r="D1430" s="10" t="s">
@@ -32023,10 +32022,10 @@
       <c r="A1431" s="5" t="s">
         <v>3206</v>
       </c>
-      <c r="B1431" s="30" t="s">
+      <c r="B1431" s="11" t="s">
         <v>3207</v>
       </c>
-      <c r="C1431" s="32" t="s">
+      <c r="C1431" s="35" t="s">
         <v>3284</v>
       </c>
       <c r="D1431" s="10" t="s">
@@ -32037,10 +32036,10 @@
       <c r="A1432" s="5" t="s">
         <v>3208</v>
       </c>
-      <c r="B1432" s="30" t="s">
+      <c r="B1432" s="11" t="s">
         <v>3209</v>
       </c>
-      <c r="C1432" s="32" t="s">
+      <c r="C1432" s="35" t="s">
         <v>3286</v>
       </c>
       <c r="D1432" s="10" t="s">
@@ -32051,10 +32050,10 @@
       <c r="A1433" s="5" t="s">
         <v>3210</v>
       </c>
-      <c r="B1433" s="30" t="s">
+      <c r="B1433" s="11" t="s">
         <v>3211</v>
       </c>
-      <c r="C1433" s="32" t="s">
+      <c r="C1433" s="35" t="s">
         <v>3288</v>
       </c>
       <c r="D1433" s="10" t="s">
@@ -32065,10 +32064,10 @@
       <c r="A1434" s="5" t="s">
         <v>3212</v>
       </c>
-      <c r="B1434" s="30" t="s">
+      <c r="B1434" s="11" t="s">
         <v>3213</v>
       </c>
-      <c r="C1434" s="32" t="s">
+      <c r="C1434" s="35" t="s">
         <v>3290</v>
       </c>
       <c r="D1434" s="10" t="s">
@@ -32079,10 +32078,10 @@
       <c r="A1435" s="5" t="s">
         <v>3214</v>
       </c>
-      <c r="B1435" s="30" t="s">
+      <c r="B1435" s="11" t="s">
         <v>3215</v>
       </c>
-      <c r="C1435" s="32" t="s">
+      <c r="C1435" s="35" t="s">
         <v>3292</v>
       </c>
       <c r="D1435" s="10" t="s">
@@ -32093,10 +32092,10 @@
       <c r="A1436" s="5" t="s">
         <v>3216</v>
       </c>
-      <c r="B1436" s="30" t="s">
+      <c r="B1436" s="11" t="s">
         <v>3217</v>
       </c>
-      <c r="C1436" s="32" t="s">
+      <c r="C1436" s="35" t="s">
         <v>3294</v>
       </c>
       <c r="D1436" s="10" t="s">
@@ -32107,10 +32106,10 @@
       <c r="A1437" s="5" t="s">
         <v>3218</v>
       </c>
-      <c r="B1437" s="30" t="s">
+      <c r="B1437" s="11" t="s">
         <v>3219</v>
       </c>
-      <c r="C1437" s="32" t="s">
+      <c r="C1437" s="35" t="s">
         <v>3296</v>
       </c>
       <c r="D1437" s="10" t="s">
@@ -32121,10 +32120,10 @@
       <c r="A1438" s="5" t="s">
         <v>3220</v>
       </c>
-      <c r="B1438" s="30" t="s">
+      <c r="B1438" s="11" t="s">
         <v>3221</v>
       </c>
-      <c r="C1438" s="32" t="s">
+      <c r="C1438" s="35" t="s">
         <v>3298</v>
       </c>
       <c r="D1438" s="10" t="s">
@@ -32135,10 +32134,10 @@
       <c r="A1439" s="5" t="s">
         <v>3222</v>
       </c>
-      <c r="B1439" s="30" t="s">
+      <c r="B1439" s="11" t="s">
         <v>3223</v>
       </c>
-      <c r="C1439" s="32" t="s">
+      <c r="C1439" s="35" t="s">
         <v>3300</v>
       </c>
       <c r="D1439" s="10" t="s">
@@ -32149,10 +32148,10 @@
       <c r="A1440" s="5" t="s">
         <v>3224</v>
       </c>
-      <c r="B1440" s="30" t="s">
+      <c r="B1440" s="11" t="s">
         <v>3225</v>
       </c>
-      <c r="C1440" s="32" t="s">
+      <c r="C1440" s="35" t="s">
         <v>3302</v>
       </c>
       <c r="D1440" s="10" t="s">
@@ -32163,10 +32162,10 @@
       <c r="A1441" s="2" t="s">
         <v>3226</v>
       </c>
-      <c r="B1441" s="30" t="s">
+      <c r="B1441" s="11" t="s">
         <v>3227</v>
       </c>
-      <c r="C1441" s="33" t="s">
+      <c r="C1441" s="27" t="s">
         <v>3304</v>
       </c>
       <c r="D1441" s="10" t="s">
@@ -32177,10 +32176,10 @@
       <c r="A1442" s="2" t="s">
         <v>3228</v>
       </c>
-      <c r="B1442" s="30" t="s">
+      <c r="B1442" s="11" t="s">
         <v>3229</v>
       </c>
-      <c r="C1442" s="33" t="s">
+      <c r="C1442" s="27" t="s">
         <v>3306</v>
       </c>
       <c r="D1442" s="10" t="s">
@@ -32191,10 +32190,10 @@
       <c r="A1443" s="2" t="s">
         <v>3230</v>
       </c>
-      <c r="B1443" s="30" t="s">
+      <c r="B1443" s="11" t="s">
         <v>3231</v>
       </c>
-      <c r="C1443" s="33" t="s">
+      <c r="C1443" s="27" t="s">
         <v>3308</v>
       </c>
       <c r="D1443" s="10" t="s">
@@ -32205,10 +32204,10 @@
       <c r="A1444" s="2" t="s">
         <v>3232</v>
       </c>
-      <c r="B1444" s="30" t="s">
+      <c r="B1444" s="11" t="s">
         <v>3233</v>
       </c>
-      <c r="C1444" s="33" t="s">
+      <c r="C1444" s="27" t="s">
         <v>3310</v>
       </c>
       <c r="D1444" s="10" t="s">
@@ -32219,10 +32218,10 @@
       <c r="A1445" s="2" t="s">
         <v>3234</v>
       </c>
-      <c r="B1445" s="30" t="s">
+      <c r="B1445" s="11" t="s">
         <v>3235</v>
       </c>
-      <c r="C1445" s="33" t="s">
+      <c r="C1445" s="27" t="s">
         <v>3312</v>
       </c>
       <c r="D1445" s="10" t="s">
@@ -32233,10 +32232,10 @@
       <c r="A1446" s="2" t="s">
         <v>3236</v>
       </c>
-      <c r="B1446" s="30" t="s">
+      <c r="B1446" s="11" t="s">
         <v>3237</v>
       </c>
-      <c r="C1446" s="33" t="s">
+      <c r="C1446" s="27" t="s">
         <v>3314</v>
       </c>
       <c r="D1446" s="10" t="s">
@@ -32247,10 +32246,10 @@
       <c r="A1447" s="5" t="s">
         <v>3238</v>
       </c>
-      <c r="B1447" s="30" t="s">
+      <c r="B1447" s="11" t="s">
         <v>3239</v>
       </c>
-      <c r="C1447" s="32" t="s">
+      <c r="C1447" s="35" t="s">
         <v>3316</v>
       </c>
       <c r="D1447" s="10" t="s">
@@ -32261,10 +32260,10 @@
       <c r="A1448" s="5" t="s">
         <v>3240</v>
       </c>
-      <c r="B1448" s="30" t="s">
+      <c r="B1448" s="11" t="s">
         <v>3241</v>
       </c>
-      <c r="C1448" s="32" t="s">
+      <c r="C1448" s="35" t="s">
         <v>3318</v>
       </c>
       <c r="D1448" s="10" t="s">
@@ -32275,10 +32274,10 @@
       <c r="A1449" s="5" t="s">
         <v>3242</v>
       </c>
-      <c r="B1449" s="30" t="s">
+      <c r="B1449" s="11" t="s">
         <v>3243</v>
       </c>
-      <c r="C1449" s="32" t="s">
+      <c r="C1449" s="35" t="s">
         <v>3320</v>
       </c>
       <c r="D1449" s="10" t="s">
@@ -32289,10 +32288,10 @@
       <c r="A1450" s="5" t="s">
         <v>3244</v>
       </c>
-      <c r="B1450" s="30" t="s">
+      <c r="B1450" s="11" t="s">
         <v>3245</v>
       </c>
-      <c r="C1450" s="32" t="s">
+      <c r="C1450" s="35" t="s">
         <v>3322</v>
       </c>
       <c r="D1450" s="10" t="s">
@@ -32303,10 +32302,10 @@
       <c r="A1451" s="2" t="s">
         <v>3246</v>
       </c>
-      <c r="B1451" s="30" t="s">
+      <c r="B1451" s="11" t="s">
         <v>3247</v>
       </c>
-      <c r="C1451" s="33" t="s">
+      <c r="C1451" s="27" t="s">
         <v>3324</v>
       </c>
       <c r="D1451" s="10" t="s">
@@ -32317,10 +32316,10 @@
       <c r="A1452" s="5" t="s">
         <v>3248</v>
       </c>
-      <c r="B1452" s="30" t="s">
+      <c r="B1452" s="11" t="s">
         <v>3249</v>
       </c>
-      <c r="C1452" s="32" t="s">
+      <c r="C1452" s="35" t="s">
         <v>3326</v>
       </c>
       <c r="D1452" s="10" t="s">
@@ -32331,10 +32330,10 @@
       <c r="A1453" s="5" t="s">
         <v>3250</v>
       </c>
-      <c r="B1453" s="30" t="s">
+      <c r="B1453" s="11" t="s">
         <v>3251</v>
       </c>
-      <c r="C1453" s="32" t="s">
+      <c r="C1453" s="35" t="s">
         <v>3328</v>
       </c>
       <c r="D1453" s="10" t="s">
@@ -32345,10 +32344,10 @@
       <c r="A1454" s="5" t="s">
         <v>3252</v>
       </c>
-      <c r="B1454" s="30" t="s">
+      <c r="B1454" s="11" t="s">
         <v>3253</v>
       </c>
-      <c r="C1454" s="32" t="s">
+      <c r="C1454" s="35" t="s">
         <v>3330</v>
       </c>
       <c r="D1454" s="10" t="s">
@@ -32359,10 +32358,10 @@
       <c r="A1455" s="5" t="s">
         <v>3254</v>
       </c>
-      <c r="B1455" s="30" t="s">
+      <c r="B1455" s="11" t="s">
         <v>3255</v>
       </c>
-      <c r="C1455" s="32" t="s">
+      <c r="C1455" s="35" t="s">
         <v>3332</v>
       </c>
       <c r="D1455" s="10" t="s">
@@ -32373,10 +32372,10 @@
       <c r="A1456" s="5" t="s">
         <v>3256</v>
       </c>
-      <c r="B1456" s="30" t="s">
+      <c r="B1456" s="11" t="s">
         <v>3257</v>
       </c>
-      <c r="C1456" s="32" t="s">
+      <c r="C1456" s="35" t="s">
         <v>3334</v>
       </c>
       <c r="D1456" s="10" t="s">
@@ -32387,10 +32386,10 @@
       <c r="A1457" s="5" t="s">
         <v>3258</v>
       </c>
-      <c r="B1457" s="30" t="s">
+      <c r="B1457" s="11" t="s">
         <v>3259</v>
       </c>
-      <c r="C1457" s="32" t="s">
+      <c r="C1457" s="35" t="s">
         <v>3336</v>
       </c>
       <c r="D1457" s="10" t="s">
@@ -32401,10 +32400,10 @@
       <c r="A1458" s="5" t="s">
         <v>3260</v>
       </c>
-      <c r="B1458" s="30" t="s">
+      <c r="B1458" s="11" t="s">
         <v>3261</v>
       </c>
-      <c r="C1458" s="32" t="s">
+      <c r="C1458" s="35" t="s">
         <v>3338</v>
       </c>
       <c r="D1458" s="10" t="s">
@@ -32415,10 +32414,10 @@
       <c r="A1459" s="5" t="s">
         <v>3262</v>
       </c>
-      <c r="B1459" s="30" t="s">
+      <c r="B1459" s="11" t="s">
         <v>3263</v>
       </c>
-      <c r="C1459" s="32" t="s">
+      <c r="C1459" s="35" t="s">
         <v>3340</v>
       </c>
       <c r="D1459" s="10" t="s">
@@ -32429,10 +32428,10 @@
       <c r="A1460" s="2" t="s">
         <v>3264</v>
       </c>
-      <c r="B1460" s="35" t="s">
+      <c r="B1460" s="36" t="s">
         <v>3265</v>
       </c>
-      <c r="C1460" s="33" t="s">
+      <c r="C1460" s="27" t="s">
         <v>3342</v>
       </c>
       <c r="D1460" s="10" t="s">
@@ -32443,10 +32442,10 @@
       <c r="A1461" s="2" t="s">
         <v>3266</v>
       </c>
-      <c r="B1461" s="35" t="s">
+      <c r="B1461" s="36" t="s">
         <v>3267</v>
       </c>
-      <c r="C1461" s="33" t="s">
+      <c r="C1461" s="27" t="s">
         <v>3344</v>
       </c>
       <c r="D1461" s="10" t="s">
@@ -32454,13 +32453,13 @@
       </c>
     </row>
     <row r="1462" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1462" s="34" t="s">
+      <c r="A1462" s="23" t="s">
         <v>3268</v>
       </c>
-      <c r="B1462" s="35" t="s">
+      <c r="B1462" s="36" t="s">
         <v>3269</v>
       </c>
-      <c r="C1462" s="36" t="s">
+      <c r="C1462" s="37" t="s">
         <v>3346</v>
       </c>
       <c r="D1462" s="10" t="s">
@@ -32471,10 +32470,10 @@
       <c r="A1463" s="1" t="s">
         <v>3348</v>
       </c>
-      <c r="B1463" s="17" t="s">
+      <c r="B1463" s="9" t="s">
         <v>3349</v>
       </c>
-      <c r="C1463" s="17" t="s">
+      <c r="C1463" s="9" t="s">
         <v>3350</v>
       </c>
       <c r="D1463" s="10" t="s">
@@ -32485,10 +32484,10 @@
       <c r="A1464" s="7" t="s">
         <v>3352</v>
       </c>
-      <c r="B1464" s="17" t="s">
+      <c r="B1464" s="9" t="s">
         <v>3353</v>
       </c>
-      <c r="C1464" s="31" t="s">
+      <c r="C1464" s="34" t="s">
         <v>3384</v>
       </c>
       <c r="D1464" s="10" t="s">
@@ -32499,10 +32498,10 @@
       <c r="A1465" s="5" t="s">
         <v>3354</v>
       </c>
-      <c r="B1465" s="30" t="s">
+      <c r="B1465" s="11" t="s">
         <v>3355</v>
       </c>
-      <c r="C1465" s="32" t="s">
+      <c r="C1465" s="35" t="s">
         <v>3386</v>
       </c>
       <c r="D1465" s="10" t="s">
@@ -32513,10 +32512,10 @@
       <c r="A1466" s="5" t="s">
         <v>3356</v>
       </c>
-      <c r="B1466" s="30" t="s">
+      <c r="B1466" s="11" t="s">
         <v>3357</v>
       </c>
-      <c r="C1466" s="32" t="s">
+      <c r="C1466" s="35" t="s">
         <v>3388</v>
       </c>
       <c r="D1466" s="10" t="s">
@@ -32527,10 +32526,10 @@
       <c r="A1467" s="5" t="s">
         <v>3358</v>
       </c>
-      <c r="B1467" s="30" t="s">
+      <c r="B1467" s="11" t="s">
         <v>3359</v>
       </c>
-      <c r="C1467" s="32" t="s">
+      <c r="C1467" s="35" t="s">
         <v>3390</v>
       </c>
       <c r="D1467" s="10" t="s">
@@ -32541,10 +32540,10 @@
       <c r="A1468" s="5" t="s">
         <v>3360</v>
       </c>
-      <c r="B1468" s="30" t="s">
+      <c r="B1468" s="11" t="s">
         <v>3361</v>
       </c>
-      <c r="C1468" s="32" t="s">
+      <c r="C1468" s="35" t="s">
         <v>3392</v>
       </c>
       <c r="D1468" s="10" t="s">
@@ -32555,10 +32554,10 @@
       <c r="A1469" s="2" t="s">
         <v>3362</v>
       </c>
-      <c r="B1469" s="30" t="s">
+      <c r="B1469" s="11" t="s">
         <v>3363</v>
       </c>
-      <c r="C1469" s="33" t="s">
+      <c r="C1469" s="27" t="s">
         <v>3394</v>
       </c>
       <c r="D1469" s="10" t="s">
@@ -32569,10 +32568,10 @@
       <c r="A1470" s="2" t="s">
         <v>3364</v>
       </c>
-      <c r="B1470" s="30" t="s">
+      <c r="B1470" s="11" t="s">
         <v>3365</v>
       </c>
-      <c r="C1470" s="33" t="s">
+      <c r="C1470" s="27" t="s">
         <v>3396</v>
       </c>
       <c r="D1470" s="10" t="s">
@@ -32583,10 +32582,10 @@
       <c r="A1471" s="5" t="s">
         <v>3366</v>
       </c>
-      <c r="B1471" s="30" t="s">
+      <c r="B1471" s="11" t="s">
         <v>3367</v>
       </c>
-      <c r="C1471" s="32" t="s">
+      <c r="C1471" s="35" t="s">
         <v>3398</v>
       </c>
       <c r="D1471" s="10" t="s">
@@ -32597,10 +32596,10 @@
       <c r="A1472" s="5" t="s">
         <v>3368</v>
       </c>
-      <c r="B1472" s="30" t="s">
+      <c r="B1472" s="11" t="s">
         <v>3369</v>
       </c>
-      <c r="C1472" s="32" t="s">
+      <c r="C1472" s="35" t="s">
         <v>3400</v>
       </c>
       <c r="D1472" s="10" t="s">
@@ -32611,10 +32610,10 @@
       <c r="A1473" s="5" t="s">
         <v>3370</v>
       </c>
-      <c r="B1473" s="30" t="s">
+      <c r="B1473" s="11" t="s">
         <v>3371</v>
       </c>
-      <c r="C1473" s="32" t="s">
+      <c r="C1473" s="35" t="s">
         <v>3402</v>
       </c>
       <c r="D1473" s="10" t="s">
@@ -32625,10 +32624,10 @@
       <c r="A1474" s="5" t="s">
         <v>3372</v>
       </c>
-      <c r="B1474" s="30" t="s">
+      <c r="B1474" s="11" t="s">
         <v>3373</v>
       </c>
-      <c r="C1474" s="32" t="s">
+      <c r="C1474" s="35" t="s">
         <v>3404</v>
       </c>
       <c r="D1474" s="10" t="s">
@@ -32639,10 +32638,10 @@
       <c r="A1475" s="5" t="s">
         <v>3374</v>
       </c>
-      <c r="B1475" s="30" t="s">
+      <c r="B1475" s="11" t="s">
         <v>3375</v>
       </c>
-      <c r="C1475" s="32" t="s">
+      <c r="C1475" s="35" t="s">
         <v>3406</v>
       </c>
       <c r="D1475" s="10" t="s">
@@ -32653,10 +32652,10 @@
       <c r="A1476" s="5" t="s">
         <v>3376</v>
       </c>
-      <c r="B1476" s="30" t="s">
+      <c r="B1476" s="11" t="s">
         <v>3377</v>
       </c>
-      <c r="C1476" s="32" t="s">
+      <c r="C1476" s="35" t="s">
         <v>3408</v>
       </c>
       <c r="D1476" s="10" t="s">
@@ -32667,10 +32666,10 @@
       <c r="A1477" s="5" t="s">
         <v>3378</v>
       </c>
-      <c r="B1477" s="30" t="s">
+      <c r="B1477" s="11" t="s">
         <v>3379</v>
       </c>
-      <c r="C1477" s="32" t="s">
+      <c r="C1477" s="35" t="s">
         <v>3410</v>
       </c>
       <c r="D1477" s="10" t="s">
@@ -32681,10 +32680,10 @@
       <c r="A1478" s="5" t="s">
         <v>3380</v>
       </c>
-      <c r="B1478" s="37" t="s">
+      <c r="B1478" s="13" t="s">
         <v>3381</v>
       </c>
-      <c r="C1478" s="32" t="s">
+      <c r="C1478" s="35" t="s">
         <v>3412</v>
       </c>
       <c r="D1478" s="10" t="s">
@@ -32692,13 +32691,13 @@
       </c>
     </row>
     <row r="1479" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1479" s="38" t="s">
+      <c r="A1479" s="24" t="s">
         <v>3382</v>
       </c>
-      <c r="B1479" s="39" t="s">
+      <c r="B1479" s="38" t="s">
         <v>3383</v>
       </c>
-      <c r="C1479" s="40" t="s">
+      <c r="C1479" s="29" t="s">
         <v>3414</v>
       </c>
       <c r="D1479" s="10" t="s">
@@ -32706,13 +32705,13 @@
       </c>
     </row>
     <row r="1480" spans="1:4" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1480" s="41" t="s">
+      <c r="A1480" s="25" t="s">
         <v>3416</v>
       </c>
-      <c r="B1480" s="25" t="s">
+      <c r="B1480" s="19" t="s">
         <v>3417</v>
       </c>
-      <c r="C1480" s="25" t="s">
+      <c r="C1480" s="19" t="s">
         <v>3418</v>
       </c>
       <c r="D1480" s="10" t="s">
@@ -32720,13 +32719,13 @@
       </c>
     </row>
     <row r="1481" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1481" s="42" t="s">
+      <c r="A1481" s="26" t="s">
         <v>3420</v>
       </c>
-      <c r="B1481" s="25" t="s">
+      <c r="B1481" s="19" t="s">
         <v>3421</v>
       </c>
-      <c r="C1481" s="25" t="s">
+      <c r="C1481" s="19" t="s">
         <v>3422</v>
       </c>
       <c r="D1481" s="10" t="s">
@@ -32734,13 +32733,13 @@
       </c>
     </row>
     <row r="1482" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1482" s="42" t="s">
+      <c r="A1482" s="26" t="s">
         <v>3424</v>
       </c>
-      <c r="B1482" s="25" t="s">
+      <c r="B1482" s="19" t="s">
         <v>3425</v>
       </c>
-      <c r="C1482" s="25" t="s">
+      <c r="C1482" s="19" t="s">
         <v>3426</v>
       </c>
       <c r="D1482" s="10" t="s">
@@ -32748,13 +32747,13 @@
       </c>
     </row>
     <row r="1483" spans="1:4" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1483" s="42" t="s">
+      <c r="A1483" s="26" t="s">
         <v>3428</v>
       </c>
-      <c r="B1483" s="25" t="s">
+      <c r="B1483" s="19" t="s">
         <v>3429</v>
       </c>
-      <c r="C1483" s="25" t="s">
+      <c r="C1483" s="19" t="s">
         <v>3430</v>
       </c>
       <c r="D1483" s="10" t="s">
@@ -32762,13 +32761,13 @@
       </c>
     </row>
     <row r="1484" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1484" s="42" t="s">
+      <c r="A1484" s="26" t="s">
         <v>3432</v>
       </c>
-      <c r="B1484" s="25" t="s">
+      <c r="B1484" s="19" t="s">
         <v>3433</v>
       </c>
-      <c r="C1484" s="25" t="s">
+      <c r="C1484" s="19" t="s">
         <v>3434</v>
       </c>
       <c r="D1484" s="10" t="s">
@@ -32776,13 +32775,13 @@
       </c>
     </row>
     <row r="1485" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1485" s="42" t="s">
+      <c r="A1485" s="26" t="s">
         <v>3436</v>
       </c>
-      <c r="B1485" s="25" t="s">
+      <c r="B1485" s="19" t="s">
         <v>3437</v>
       </c>
-      <c r="C1485" s="25" t="s">
+      <c r="C1485" s="19" t="s">
         <v>3438</v>
       </c>
       <c r="D1485" s="10" t="s">
@@ -32790,13 +32789,13 @@
       </c>
     </row>
     <row r="1486" spans="1:4" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1486" s="42" t="s">
+      <c r="A1486" s="26" t="s">
         <v>3440</v>
       </c>
-      <c r="B1486" s="25" t="s">
+      <c r="B1486" s="19" t="s">
         <v>3441</v>
       </c>
-      <c r="C1486" s="25" t="s">
+      <c r="C1486" s="19" t="s">
         <v>3442</v>
       </c>
       <c r="D1486" s="10" t="s">
@@ -32804,13 +32803,13 @@
       </c>
     </row>
     <row r="1487" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1487" s="42" t="s">
+      <c r="A1487" s="26" t="s">
         <v>3444</v>
       </c>
-      <c r="B1487" s="25" t="s">
+      <c r="B1487" s="19" t="s">
         <v>3445</v>
       </c>
-      <c r="C1487" s="25" t="s">
+      <c r="C1487" s="19" t="s">
         <v>3446</v>
       </c>
       <c r="D1487" s="10" t="s">
@@ -32818,13 +32817,13 @@
       </c>
     </row>
     <row r="1488" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1488" s="42" t="s">
+      <c r="A1488" s="26" t="s">
         <v>3448</v>
       </c>
-      <c r="B1488" s="25" t="s">
+      <c r="B1488" s="19" t="s">
         <v>3449</v>
       </c>
-      <c r="C1488" s="25" t="s">
+      <c r="C1488" s="19" t="s">
         <v>3450</v>
       </c>
       <c r="D1488" s="10" t="s">
@@ -32832,13 +32831,13 @@
       </c>
     </row>
     <row r="1489" spans="1:4" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1489" s="42" t="s">
+      <c r="A1489" s="26" t="s">
         <v>3452</v>
       </c>
-      <c r="B1489" s="25" t="s">
+      <c r="B1489" s="19" t="s">
         <v>3453</v>
       </c>
-      <c r="C1489" s="25" t="s">
+      <c r="C1489" s="19" t="s">
         <v>3454</v>
       </c>
       <c r="D1489" s="10" t="s">
@@ -32846,13 +32845,13 @@
       </c>
     </row>
     <row r="1490" spans="1:4" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1490" s="42" t="s">
+      <c r="A1490" s="26" t="s">
         <v>3456</v>
       </c>
-      <c r="B1490" s="25" t="s">
+      <c r="B1490" s="19" t="s">
         <v>3457</v>
       </c>
-      <c r="C1490" s="25" t="s">
+      <c r="C1490" s="19" t="s">
         <v>3458</v>
       </c>
       <c r="D1490" s="10" t="s">
@@ -32860,13 +32859,13 @@
       </c>
     </row>
     <row r="1491" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1491" s="42" t="s">
+      <c r="A1491" s="26" t="s">
         <v>3460</v>
       </c>
-      <c r="B1491" s="25" t="s">
+      <c r="B1491" s="19" t="s">
         <v>3461</v>
       </c>
-      <c r="C1491" s="25" t="s">
+      <c r="C1491" s="19" t="s">
         <v>3462</v>
       </c>
       <c r="D1491" s="10" t="s">
@@ -32874,13 +32873,13 @@
       </c>
     </row>
     <row r="1492" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1492" s="42" t="s">
+      <c r="A1492" s="26" t="s">
         <v>3464</v>
       </c>
-      <c r="B1492" s="25" t="s">
+      <c r="B1492" s="19" t="s">
         <v>3465</v>
       </c>
-      <c r="C1492" s="25" t="s">
+      <c r="C1492" s="19" t="s">
         <v>3466</v>
       </c>
       <c r="D1492" s="10" t="s">
@@ -32888,13 +32887,13 @@
       </c>
     </row>
     <row r="1493" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1493" s="42" t="s">
+      <c r="A1493" s="26" t="s">
         <v>3468</v>
       </c>
-      <c r="B1493" s="25" t="s">
+      <c r="B1493" s="19" t="s">
         <v>3469</v>
       </c>
-      <c r="C1493" s="25" t="s">
+      <c r="C1493" s="19" t="s">
         <v>3470</v>
       </c>
       <c r="D1493" s="10" t="s">
@@ -32902,13 +32901,13 @@
       </c>
     </row>
     <row r="1494" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1494" s="42" t="s">
+      <c r="A1494" s="26" t="s">
         <v>3472</v>
       </c>
-      <c r="B1494" s="25" t="s">
+      <c r="B1494" s="19" t="s">
         <v>3473</v>
       </c>
-      <c r="C1494" s="25" t="s">
+      <c r="C1494" s="19" t="s">
         <v>3474</v>
       </c>
       <c r="D1494" s="10" t="s">
@@ -32916,13 +32915,13 @@
       </c>
     </row>
     <row r="1495" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1495" s="42" t="s">
+      <c r="A1495" s="26" t="s">
         <v>3476</v>
       </c>
-      <c r="B1495" s="25" t="s">
+      <c r="B1495" s="19" t="s">
         <v>3477</v>
       </c>
-      <c r="C1495" s="25" t="s">
+      <c r="C1495" s="19" t="s">
         <v>3478</v>
       </c>
       <c r="D1495" s="10" t="s">
@@ -32930,13 +32929,13 @@
       </c>
     </row>
     <row r="1496" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1496" s="42" t="s">
+      <c r="A1496" s="26" t="s">
         <v>3480</v>
       </c>
-      <c r="B1496" s="25" t="s">
+      <c r="B1496" s="19" t="s">
         <v>3481</v>
       </c>
-      <c r="C1496" s="25" t="s">
+      <c r="C1496" s="19" t="s">
         <v>3482</v>
       </c>
       <c r="D1496" s="10" t="s">
@@ -32944,13 +32943,13 @@
       </c>
     </row>
     <row r="1497" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1497" s="42" t="s">
+      <c r="A1497" s="26" t="s">
         <v>3484</v>
       </c>
-      <c r="B1497" s="25" t="s">
+      <c r="B1497" s="19" t="s">
         <v>3485</v>
       </c>
-      <c r="C1497" s="25" t="s">
+      <c r="C1497" s="19" t="s">
         <v>3486</v>
       </c>
       <c r="D1497" s="10" t="s">
@@ -32958,13 +32957,13 @@
       </c>
     </row>
     <row r="1498" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1498" s="42" t="s">
+      <c r="A1498" s="26" t="s">
         <v>3488</v>
       </c>
-      <c r="B1498" s="25" t="s">
+      <c r="B1498" s="19" t="s">
         <v>3489</v>
       </c>
-      <c r="C1498" s="25" t="s">
+      <c r="C1498" s="19" t="s">
         <v>3490</v>
       </c>
       <c r="D1498" s="10" t="s">
@@ -32972,13 +32971,13 @@
       </c>
     </row>
     <row r="1499" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1499" s="42" t="s">
+      <c r="A1499" s="26" t="s">
         <v>3492</v>
       </c>
-      <c r="B1499" s="25" t="s">
+      <c r="B1499" s="19" t="s">
         <v>3493</v>
       </c>
-      <c r="C1499" s="25" t="s">
+      <c r="C1499" s="19" t="s">
         <v>3494</v>
       </c>
       <c r="D1499" s="10" t="s">
@@ -32986,13 +32985,13 @@
       </c>
     </row>
     <row r="1500" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1500" s="42" t="s">
+      <c r="A1500" s="26" t="s">
         <v>3496</v>
       </c>
-      <c r="B1500" s="25" t="s">
+      <c r="B1500" s="19" t="s">
         <v>3497</v>
       </c>
-      <c r="C1500" s="25" t="s">
+      <c r="C1500" s="19" t="s">
         <v>3498</v>
       </c>
       <c r="D1500" s="10" t="s">
@@ -33000,13 +32999,13 @@
       </c>
     </row>
     <row r="1501" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1501" s="42" t="s">
+      <c r="A1501" s="26" t="s">
         <v>3500</v>
       </c>
-      <c r="B1501" s="25" t="s">
+      <c r="B1501" s="19" t="s">
         <v>3501</v>
       </c>
-      <c r="C1501" s="25" t="s">
+      <c r="C1501" s="19" t="s">
         <v>3502</v>
       </c>
       <c r="D1501" s="10" t="s">
@@ -33014,13 +33013,13 @@
       </c>
     </row>
     <row r="1502" spans="1:4" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1502" s="42" t="s">
+      <c r="A1502" s="26" t="s">
         <v>3504</v>
       </c>
-      <c r="B1502" s="25" t="s">
+      <c r="B1502" s="19" t="s">
         <v>3505</v>
       </c>
-      <c r="C1502" s="25" t="s">
+      <c r="C1502" s="19" t="s">
         <v>3506</v>
       </c>
       <c r="D1502" s="10" t="s">
@@ -33028,13 +33027,13 @@
       </c>
     </row>
     <row r="1503" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1503" s="42" t="s">
+      <c r="A1503" s="26" t="s">
         <v>3508</v>
       </c>
-      <c r="B1503" s="25" t="s">
+      <c r="B1503" s="19" t="s">
         <v>3509</v>
       </c>
-      <c r="C1503" s="25" t="s">
+      <c r="C1503" s="19" t="s">
         <v>3510</v>
       </c>
       <c r="D1503" s="10" t="s">
@@ -33042,13 +33041,13 @@
       </c>
     </row>
     <row r="1504" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1504" s="42" t="s">
+      <c r="A1504" s="26" t="s">
         <v>3512</v>
       </c>
-      <c r="B1504" s="25" t="s">
+      <c r="B1504" s="19" t="s">
         <v>3513</v>
       </c>
-      <c r="C1504" s="25" t="s">
+      <c r="C1504" s="19" t="s">
         <v>3514</v>
       </c>
       <c r="D1504" s="10" t="s">
@@ -33056,13 +33055,13 @@
       </c>
     </row>
     <row r="1505" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1505" s="42" t="s">
+      <c r="A1505" s="26" t="s">
         <v>3516</v>
       </c>
-      <c r="B1505" s="25" t="s">
+      <c r="B1505" s="19" t="s">
         <v>3517</v>
       </c>
-      <c r="C1505" s="25" t="s">
+      <c r="C1505" s="19" t="s">
         <v>3518</v>
       </c>
       <c r="D1505" s="10" t="s">
@@ -33070,13 +33069,13 @@
       </c>
     </row>
     <row r="1506" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1506" s="42" t="s">
+      <c r="A1506" s="26" t="s">
         <v>3520</v>
       </c>
-      <c r="B1506" s="25" t="s">
+      <c r="B1506" s="19" t="s">
         <v>3521</v>
       </c>
-      <c r="C1506" s="25" t="s">
+      <c r="C1506" s="19" t="s">
         <v>3522</v>
       </c>
       <c r="D1506" s="10" t="s">
@@ -33087,10 +33086,10 @@
       <c r="A1507" s="7" t="s">
         <v>3524</v>
       </c>
-      <c r="B1507" s="43" t="s">
+      <c r="B1507" s="39" t="s">
         <v>3525</v>
       </c>
-      <c r="C1507" s="25" t="s">
+      <c r="C1507" s="19" t="s">
         <v>3526</v>
       </c>
       <c r="D1507" s="10" t="s">
@@ -33101,10 +33100,10 @@
       <c r="A1508" s="7" t="s">
         <v>3528</v>
       </c>
-      <c r="B1508" s="17" t="s">
+      <c r="B1508" s="9" t="s">
         <v>3529</v>
       </c>
-      <c r="C1508" s="31" t="s">
+      <c r="C1508" s="34" t="s">
         <v>3540</v>
       </c>
       <c r="D1508" s="10" t="s">
@@ -33115,10 +33114,10 @@
       <c r="A1509" s="5" t="s">
         <v>3530</v>
       </c>
-      <c r="B1509" s="30" t="s">
+      <c r="B1509" s="11" t="s">
         <v>3531</v>
       </c>
-      <c r="C1509" s="32" t="s">
+      <c r="C1509" s="35" t="s">
         <v>3542</v>
       </c>
       <c r="D1509" s="10" t="s">
@@ -33129,10 +33128,10 @@
       <c r="A1510" s="5" t="s">
         <v>3532</v>
       </c>
-      <c r="B1510" s="30" t="s">
+      <c r="B1510" s="11" t="s">
         <v>3533</v>
       </c>
-      <c r="C1510" s="32" t="s">
+      <c r="C1510" s="35" t="s">
         <v>3544</v>
       </c>
       <c r="D1510" s="10" t="s">
@@ -33143,10 +33142,10 @@
       <c r="A1511" s="5" t="s">
         <v>3534</v>
       </c>
-      <c r="B1511" s="30" t="s">
+      <c r="B1511" s="11" t="s">
         <v>3535</v>
       </c>
-      <c r="C1511" s="32" t="s">
+      <c r="C1511" s="35" t="s">
         <v>3546</v>
       </c>
       <c r="D1511" s="10" t="s">
@@ -33157,10 +33156,10 @@
       <c r="A1512" s="5" t="s">
         <v>3536</v>
       </c>
-      <c r="B1512" s="30" t="s">
+      <c r="B1512" s="11" t="s">
         <v>3537</v>
       </c>
-      <c r="C1512" s="32" t="s">
+      <c r="C1512" s="35" t="s">
         <v>3548</v>
       </c>
       <c r="D1512" s="10" t="s">
@@ -33171,10 +33170,10 @@
       <c r="A1513" s="2" t="s">
         <v>3538</v>
       </c>
-      <c r="B1513" s="30" t="s">
+      <c r="B1513" s="11" t="s">
         <v>3539</v>
       </c>
-      <c r="C1513" s="33" t="s">
+      <c r="C1513" s="27" t="s">
         <v>3550</v>
       </c>
       <c r="D1513" s="10" t="s">
@@ -33185,10 +33184,10 @@
       <c r="A1514" s="7" t="s">
         <v>3552</v>
       </c>
-      <c r="B1514" s="17" t="s">
+      <c r="B1514" s="9" t="s">
         <v>3553</v>
       </c>
-      <c r="C1514" s="31" t="s">
+      <c r="C1514" s="34" t="s">
         <v>3566</v>
       </c>
       <c r="D1514" s="10" t="s">
@@ -33199,10 +33198,10 @@
       <c r="A1515" s="5" t="s">
         <v>3554</v>
       </c>
-      <c r="B1515" s="30" t="s">
+      <c r="B1515" s="11" t="s">
         <v>3555</v>
       </c>
-      <c r="C1515" s="32" t="s">
+      <c r="C1515" s="35" t="s">
         <v>3568</v>
       </c>
       <c r="D1515" s="10" t="s">
@@ -33213,10 +33212,10 @@
       <c r="A1516" s="5" t="s">
         <v>3556</v>
       </c>
-      <c r="B1516" s="30" t="s">
+      <c r="B1516" s="11" t="s">
         <v>3557</v>
       </c>
-      <c r="C1516" s="32" t="s">
+      <c r="C1516" s="35" t="s">
         <v>3570</v>
       </c>
       <c r="D1516" s="10" t="s">
@@ -33227,10 +33226,10 @@
       <c r="A1517" s="5" t="s">
         <v>3558</v>
       </c>
-      <c r="B1517" s="30" t="s">
+      <c r="B1517" s="11" t="s">
         <v>3559</v>
       </c>
-      <c r="C1517" s="32" t="s">
+      <c r="C1517" s="35" t="s">
         <v>3572</v>
       </c>
       <c r="D1517" s="10" t="s">
@@ -33241,10 +33240,10 @@
       <c r="A1518" s="5" t="s">
         <v>3560</v>
       </c>
-      <c r="B1518" s="30" t="s">
+      <c r="B1518" s="11" t="s">
         <v>3561</v>
       </c>
-      <c r="C1518" s="32" t="s">
+      <c r="C1518" s="35" t="s">
         <v>3574</v>
       </c>
       <c r="D1518" s="10" t="s">
@@ -33255,10 +33254,10 @@
       <c r="A1519" s="5" t="s">
         <v>3562</v>
       </c>
-      <c r="B1519" s="30" t="s">
+      <c r="B1519" s="11" t="s">
         <v>3563</v>
       </c>
-      <c r="C1519" s="32" t="s">
+      <c r="C1519" s="35" t="s">
         <v>3576</v>
       </c>
       <c r="D1519" s="10" t="s">
@@ -33269,10 +33268,10 @@
       <c r="A1520" s="5" t="s">
         <v>3564</v>
       </c>
-      <c r="B1520" s="30" t="s">
+      <c r="B1520" s="11" t="s">
         <v>3565</v>
       </c>
-      <c r="C1520" s="32" t="s">
+      <c r="C1520" s="35" t="s">
         <v>3578</v>
       </c>
       <c r="D1520" s="10" t="s">
@@ -33283,10 +33282,10 @@
       <c r="A1521" s="7" t="s">
         <v>3580</v>
       </c>
-      <c r="B1521" s="17" t="s">
+      <c r="B1521" s="9" t="s">
         <v>3581</v>
       </c>
-      <c r="C1521" s="31" t="s">
+      <c r="C1521" s="34" t="s">
         <v>3597</v>
       </c>
       <c r="D1521" s="10" t="s">
@@ -33297,10 +33296,10 @@
       <c r="A1522" s="2" t="s">
         <v>3582</v>
       </c>
-      <c r="B1522" s="30" t="s">
+      <c r="B1522" s="11" t="s">
         <v>3583</v>
       </c>
-      <c r="C1522" s="33" t="s">
+      <c r="C1522" s="27" t="s">
         <v>3611</v>
       </c>
       <c r="D1522" s="10" t="s">
@@ -33311,10 +33310,10 @@
       <c r="A1523" s="2" t="s">
         <v>3584</v>
       </c>
-      <c r="B1523" s="30" t="s">
+      <c r="B1523" s="11" t="s">
         <v>3585</v>
       </c>
-      <c r="C1523" s="33" t="s">
+      <c r="C1523" s="27" t="s">
         <v>3599</v>
       </c>
       <c r="D1523" s="10" t="s">
@@ -33325,10 +33324,10 @@
       <c r="A1524" s="2" t="s">
         <v>3586</v>
       </c>
-      <c r="B1524" s="30" t="s">
+      <c r="B1524" s="11" t="s">
         <v>3587</v>
       </c>
-      <c r="C1524" s="33" t="s">
+      <c r="C1524" s="27" t="s">
         <v>3601</v>
       </c>
       <c r="D1524" s="10" t="s">
@@ -33339,10 +33338,10 @@
       <c r="A1525" s="2" t="s">
         <v>3588</v>
       </c>
-      <c r="B1525" s="30" t="s">
+      <c r="B1525" s="11" t="s">
         <v>3589</v>
       </c>
-      <c r="C1525" s="33" t="s">
+      <c r="C1525" s="27" t="s">
         <v>3603</v>
       </c>
       <c r="D1525" s="10" t="s">
@@ -33353,10 +33352,10 @@
       <c r="A1526" s="2" t="s">
         <v>3590</v>
       </c>
-      <c r="B1526" s="30" t="s">
+      <c r="B1526" s="11" t="s">
         <v>3591</v>
       </c>
-      <c r="C1526" s="33" t="s">
+      <c r="C1526" s="27" t="s">
         <v>3605</v>
       </c>
       <c r="D1526" s="10" t="s">
@@ -33370,7 +33369,7 @@
       <c r="B1527" s="11" t="s">
         <v>3592</v>
       </c>
-      <c r="C1527" s="44" t="s">
+      <c r="C1527" s="27" t="s">
         <v>3613</v>
       </c>
       <c r="D1527" s="10" t="s">
@@ -33381,10 +33380,10 @@
       <c r="A1528" s="2" t="s">
         <v>3593</v>
       </c>
-      <c r="B1528" s="30" t="s">
+      <c r="B1528" s="11" t="s">
         <v>3594</v>
       </c>
-      <c r="C1528" s="33" t="s">
+      <c r="C1528" s="27" t="s">
         <v>3607</v>
       </c>
       <c r="D1528" s="10" t="s">
@@ -33395,10 +33394,10 @@
       <c r="A1529" s="2" t="s">
         <v>3595</v>
       </c>
-      <c r="B1529" s="30" t="s">
+      <c r="B1529" s="11" t="s">
         <v>3596</v>
       </c>
-      <c r="C1529" s="33" t="s">
+      <c r="C1529" s="27" t="s">
         <v>3609</v>
       </c>
       <c r="D1529" s="10" t="s">
@@ -33409,10 +33408,10 @@
       <c r="A1530" s="8" t="s">
         <v>3616</v>
       </c>
-      <c r="B1530" s="18" t="s">
+      <c r="B1530" s="16" t="s">
         <v>3617</v>
       </c>
-      <c r="C1530" s="31" t="s">
+      <c r="C1530" s="34" t="s">
         <v>3634</v>
       </c>
       <c r="D1530" s="10" t="s">
@@ -33420,13 +33419,13 @@
       </c>
     </row>
     <row r="1531" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1531" s="34" t="s">
+      <c r="A1531" s="23" t="s">
         <v>3618</v>
       </c>
-      <c r="B1531" s="35" t="s">
+      <c r="B1531" s="36" t="s">
         <v>3619</v>
       </c>
-      <c r="C1531" s="32" t="s">
+      <c r="C1531" s="35" t="s">
         <v>3636</v>
       </c>
       <c r="D1531" s="10" t="s">
@@ -33434,13 +33433,13 @@
       </c>
     </row>
     <row r="1532" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1532" s="34" t="s">
+      <c r="A1532" s="23" t="s">
         <v>3620</v>
       </c>
-      <c r="B1532" s="35" t="s">
+      <c r="B1532" s="36" t="s">
         <v>3621</v>
       </c>
-      <c r="C1532" s="32" t="s">
+      <c r="C1532" s="35" t="s">
         <v>3638</v>
       </c>
       <c r="D1532" s="10" t="s">
@@ -33448,13 +33447,13 @@
       </c>
     </row>
     <row r="1533" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1533" s="34" t="s">
+      <c r="A1533" s="23" t="s">
         <v>3622</v>
       </c>
-      <c r="B1533" s="35" t="s">
+      <c r="B1533" s="36" t="s">
         <v>3623</v>
       </c>
-      <c r="C1533" s="32" t="s">
+      <c r="C1533" s="35" t="s">
         <v>3640</v>
       </c>
       <c r="D1533" s="10" t="s">
@@ -33462,13 +33461,13 @@
       </c>
     </row>
     <row r="1534" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1534" s="34" t="s">
+      <c r="A1534" s="23" t="s">
         <v>3624</v>
       </c>
-      <c r="B1534" s="35" t="s">
+      <c r="B1534" s="36" t="s">
         <v>3625</v>
       </c>
-      <c r="C1534" s="32" t="s">
+      <c r="C1534" s="35" t="s">
         <v>3642</v>
       </c>
       <c r="D1534" s="10" t="s">
@@ -33476,13 +33475,13 @@
       </c>
     </row>
     <row r="1535" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1535" s="34" t="s">
+      <c r="A1535" s="23" t="s">
         <v>3626</v>
       </c>
-      <c r="B1535" s="35" t="s">
+      <c r="B1535" s="36" t="s">
         <v>3627</v>
       </c>
-      <c r="C1535" s="32" t="s">
+      <c r="C1535" s="35" t="s">
         <v>3644</v>
       </c>
       <c r="D1535" s="10" t="s">
@@ -33490,13 +33489,13 @@
       </c>
     </row>
     <row r="1536" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1536" s="34" t="s">
+      <c r="A1536" s="23" t="s">
         <v>3628</v>
       </c>
-      <c r="B1536" s="35" t="s">
+      <c r="B1536" s="36" t="s">
         <v>3629</v>
       </c>
-      <c r="C1536" s="32" t="s">
+      <c r="C1536" s="35" t="s">
         <v>3646</v>
       </c>
       <c r="D1536" s="10" t="s">
@@ -33504,13 +33503,13 @@
       </c>
     </row>
     <row r="1537" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1537" s="34" t="s">
+      <c r="A1537" s="23" t="s">
         <v>3630</v>
       </c>
-      <c r="B1537" s="35" t="s">
+      <c r="B1537" s="36" t="s">
         <v>3631</v>
       </c>
-      <c r="C1537" s="32" t="s">
+      <c r="C1537" s="35" t="s">
         <v>3648</v>
       </c>
       <c r="D1537" s="10" t="s">
@@ -33518,13 +33517,13 @@
       </c>
     </row>
     <row r="1538" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1538" s="34" t="s">
+      <c r="A1538" s="23" t="s">
         <v>3632</v>
       </c>
-      <c r="B1538" s="35" t="s">
+      <c r="B1538" s="36" t="s">
         <v>3633</v>
       </c>
-      <c r="C1538" s="32" t="s">
+      <c r="C1538" s="35" t="s">
         <v>3650</v>
       </c>
       <c r="D1538" s="10" t="s">
@@ -33535,10 +33534,10 @@
       <c r="A1539" s="7" t="s">
         <v>3652</v>
       </c>
-      <c r="B1539" s="18" t="s">
+      <c r="B1539" s="16" t="s">
         <v>3653</v>
       </c>
-      <c r="C1539" s="31" t="s">
+      <c r="C1539" s="34" t="s">
         <v>3656</v>
       </c>
       <c r="D1539" s="10" t="s">
@@ -33549,10 +33548,10 @@
       <c r="A1540" s="5" t="s">
         <v>3654</v>
       </c>
-      <c r="B1540" s="35" t="s">
+      <c r="B1540" s="36" t="s">
         <v>3655</v>
       </c>
-      <c r="C1540" s="32" t="s">
+      <c r="C1540" s="35" t="s">
         <v>3658</v>
       </c>
       <c r="D1540" s="10" t="s">
@@ -33563,10 +33562,10 @@
       <c r="A1541" s="7" t="s">
         <v>3660</v>
       </c>
-      <c r="B1541" s="17" t="s">
+      <c r="B1541" s="9" t="s">
         <v>3661</v>
       </c>
-      <c r="C1541" s="31" t="s">
+      <c r="C1541" s="34" t="s">
         <v>3666</v>
       </c>
       <c r="D1541" s="10" t="s">
@@ -33577,10 +33576,10 @@
       <c r="A1542" s="2" t="s">
         <v>3662</v>
       </c>
-      <c r="B1542" s="30" t="s">
+      <c r="B1542" s="11" t="s">
         <v>3663</v>
       </c>
-      <c r="C1542" s="32" t="s">
+      <c r="C1542" s="35" t="s">
         <v>3668</v>
       </c>
       <c r="D1542" s="10" t="s">
@@ -33591,10 +33590,10 @@
       <c r="A1543" s="5" t="s">
         <v>3664</v>
       </c>
-      <c r="B1543" s="30" t="s">
+      <c r="B1543" s="11" t="s">
         <v>3665</v>
       </c>
-      <c r="C1543" s="32" t="s">
+      <c r="C1543" s="35" t="s">
         <v>3670</v>
       </c>
       <c r="D1543" s="10" t="s">
@@ -33605,10 +33604,10 @@
       <c r="A1544" s="7" t="s">
         <v>3672</v>
       </c>
-      <c r="B1544" s="19" t="s">
+      <c r="B1544" s="15" t="s">
         <v>3673</v>
       </c>
-      <c r="C1544" s="31" t="s">
+      <c r="C1544" s="34" t="s">
         <v>3676</v>
       </c>
       <c r="D1544" s="10" t="s">
@@ -33619,10 +33618,10 @@
       <c r="A1545" s="5" t="s">
         <v>3674</v>
       </c>
-      <c r="B1545" s="37" t="s">
+      <c r="B1545" s="13" t="s">
         <v>3675</v>
       </c>
-      <c r="C1545" s="32" t="s">
+      <c r="C1545" s="35" t="s">
         <v>3678</v>
       </c>
       <c r="D1545" s="10" t="s">
@@ -33633,10 +33632,10 @@
       <c r="A1546" s="7" t="s">
         <v>3680</v>
       </c>
-      <c r="B1546" s="19" t="s">
+      <c r="B1546" s="15" t="s">
         <v>3681</v>
       </c>
-      <c r="C1546" s="31" t="s">
+      <c r="C1546" s="34" t="s">
         <v>3684</v>
       </c>
       <c r="D1546" s="10" t="s">
@@ -33647,10 +33646,10 @@
       <c r="A1547" s="5" t="s">
         <v>3682</v>
       </c>
-      <c r="B1547" s="37" t="s">
+      <c r="B1547" s="13" t="s">
         <v>3683</v>
       </c>
-      <c r="C1547" s="32" t="s">
+      <c r="C1547" s="35" t="s">
         <v>3686</v>
       </c>
       <c r="D1547" s="10" t="s">
@@ -33661,10 +33660,10 @@
       <c r="A1548" s="7" t="s">
         <v>3688</v>
       </c>
-      <c r="B1548" s="17" t="s">
+      <c r="B1548" s="9" t="s">
         <v>3689</v>
       </c>
-      <c r="C1548" s="31" t="s">
+      <c r="C1548" s="34" t="s">
         <v>3700</v>
       </c>
       <c r="D1548" s="10" t="s">
@@ -33675,10 +33674,10 @@
       <c r="A1549" s="5" t="s">
         <v>3690</v>
       </c>
-      <c r="B1549" s="30" t="s">
+      <c r="B1549" s="11" t="s">
         <v>3691</v>
       </c>
-      <c r="C1549" s="32" t="s">
+      <c r="C1549" s="35" t="s">
         <v>3702</v>
       </c>
       <c r="D1549" s="10" t="s">
@@ -33689,10 +33688,10 @@
       <c r="A1550" s="5" t="s">
         <v>3692</v>
       </c>
-      <c r="B1550" s="30" t="s">
+      <c r="B1550" s="11" t="s">
         <v>3693</v>
       </c>
-      <c r="C1550" s="32" t="s">
+      <c r="C1550" s="35" t="s">
         <v>3704</v>
       </c>
       <c r="D1550" s="10" t="s">
@@ -33703,10 +33702,10 @@
       <c r="A1551" s="5" t="s">
         <v>3694</v>
       </c>
-      <c r="B1551" s="30" t="s">
+      <c r="B1551" s="11" t="s">
         <v>3695</v>
       </c>
-      <c r="C1551" s="32" t="s">
+      <c r="C1551" s="35" t="s">
         <v>3706</v>
       </c>
       <c r="D1551" s="10" t="s">
@@ -33717,10 +33716,10 @@
       <c r="A1552" s="5" t="s">
         <v>3696</v>
       </c>
-      <c r="B1552" s="30" t="s">
+      <c r="B1552" s="11" t="s">
         <v>3697</v>
       </c>
-      <c r="C1552" s="32" t="s">
+      <c r="C1552" s="35" t="s">
         <v>3708</v>
       </c>
       <c r="D1552" s="10" t="s">
@@ -33731,10 +33730,10 @@
       <c r="A1553" s="5" t="s">
         <v>3698</v>
       </c>
-      <c r="B1553" s="30" t="s">
+      <c r="B1553" s="11" t="s">
         <v>3699</v>
       </c>
-      <c r="C1553" s="32" t="s">
+      <c r="C1553" s="35" t="s">
         <v>3710</v>
       </c>
       <c r="D1553" s="10" t="s">
@@ -33745,10 +33744,10 @@
       <c r="A1554" s="7" t="s">
         <v>3712</v>
       </c>
-      <c r="B1554" s="17" t="s">
+      <c r="B1554" s="9" t="s">
         <v>3713</v>
       </c>
-      <c r="C1554" s="31" t="s">
+      <c r="C1554" s="34" t="s">
         <v>3730</v>
       </c>
       <c r="D1554" s="10" t="s">
@@ -33759,10 +33758,10 @@
       <c r="A1555" s="5" t="s">
         <v>3714</v>
       </c>
-      <c r="B1555" s="30" t="s">
+      <c r="B1555" s="11" t="s">
         <v>3715</v>
       </c>
-      <c r="C1555" s="32" t="s">
+      <c r="C1555" s="35" t="s">
         <v>3732</v>
       </c>
       <c r="D1555" s="10" t="s">
@@ -33773,10 +33772,10 @@
       <c r="A1556" s="5" t="s">
         <v>3716</v>
       </c>
-      <c r="B1556" s="30" t="s">
+      <c r="B1556" s="11" t="s">
         <v>3717</v>
       </c>
-      <c r="C1556" s="32" t="s">
+      <c r="C1556" s="35" t="s">
         <v>3734</v>
       </c>
       <c r="D1556" s="10" t="s">
@@ -33787,10 +33786,10 @@
       <c r="A1557" s="5" t="s">
         <v>3718</v>
       </c>
-      <c r="B1557" s="30" t="s">
+      <c r="B1557" s="11" t="s">
         <v>3719</v>
       </c>
-      <c r="C1557" s="32" t="s">
+      <c r="C1557" s="35" t="s">
         <v>3736</v>
       </c>
       <c r="D1557" s="10" t="s">
@@ -33801,10 +33800,10 @@
       <c r="A1558" s="5" t="s">
         <v>3720</v>
       </c>
-      <c r="B1558" s="30" t="s">
+      <c r="B1558" s="11" t="s">
         <v>3721</v>
       </c>
-      <c r="C1558" s="32" t="s">
+      <c r="C1558" s="35" t="s">
         <v>3738</v>
       </c>
       <c r="D1558" s="10" t="s">
@@ -33815,10 +33814,10 @@
       <c r="A1559" s="5" t="s">
         <v>3722</v>
       </c>
-      <c r="B1559" s="30" t="s">
+      <c r="B1559" s="11" t="s">
         <v>3723</v>
       </c>
-      <c r="C1559" s="32" t="s">
+      <c r="C1559" s="35" t="s">
         <v>3740</v>
       </c>
       <c r="D1559" s="10" t="s">
@@ -33829,10 +33828,10 @@
       <c r="A1560" s="5" t="s">
         <v>3724</v>
       </c>
-      <c r="B1560" s="30" t="s">
+      <c r="B1560" s="11" t="s">
         <v>3725</v>
       </c>
-      <c r="C1560" s="32" t="s">
+      <c r="C1560" s="35" t="s">
         <v>3742</v>
       </c>
       <c r="D1560" s="10" t="s">
@@ -33843,10 +33842,10 @@
       <c r="A1561" s="5" t="s">
         <v>3726</v>
       </c>
-      <c r="B1561" s="30" t="s">
+      <c r="B1561" s="11" t="s">
         <v>3727</v>
       </c>
-      <c r="C1561" s="32" t="s">
+      <c r="C1561" s="35" t="s">
         <v>3744</v>
       </c>
       <c r="D1561" s="10" t="s">
@@ -33857,14 +33856,28 @@
       <c r="A1562" s="5" t="s">
         <v>3728</v>
       </c>
-      <c r="B1562" s="30" t="s">
+      <c r="B1562" s="11" t="s">
         <v>3729</v>
       </c>
-      <c r="C1562" s="32" t="s">
+      <c r="C1562" s="29" t="s">
         <v>3746</v>
       </c>
       <c r="D1562" s="10" t="s">
         <v>3747</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1563" s="7" t="s">
+        <v>3748</v>
+      </c>
+      <c r="B1563" s="39" t="s">
+        <v>3749</v>
+      </c>
+      <c r="C1563" s="28" t="s">
+        <v>3750</v>
+      </c>
+      <c r="D1563" s="10" t="s">
+        <v>3751</v>
       </c>
     </row>
   </sheetData>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{451DB57C-BE7A-4296-82B4-B2191FC748EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B85443-4F8B-43B6-A8E5-AB9DB232A896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2610" yWindow="1395" windowWidth="17130" windowHeight="13995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3754" uniqueCount="3752">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3766" uniqueCount="3764">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -11307,6 +11307,42 @@
   </si>
   <si>
     <t>69.604969</t>
+  </si>
+  <si>
+    <t>Namangan sh., Qoʻqon ko'chasi, 168 uy: г. Наманган, улица Кукон, 168 дом</t>
+  </si>
+  <si>
+    <t>FrНАМ-30</t>
+  </si>
+  <si>
+    <t>40.972782</t>
+  </si>
+  <si>
+    <t>71.657521</t>
+  </si>
+  <si>
+    <t>Yakkabog' sh., Yakkabog' tumani, Aygʻirko‘l ko'chasi, 105 uy: г. Яккабаг, Яккабагский район, улица Айгиркол, дом 105</t>
+  </si>
+  <si>
+    <t>FrЯКК-7</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Olmazor tumani, Farobiy ko'chasi, 310 uy: г. Ташкент, Алмазарский район, улица Фараби, дом 310</t>
+  </si>
+  <si>
+    <t>FrТАШ-406</t>
+  </si>
+  <si>
+    <t>38.969349</t>
+  </si>
+  <si>
+    <t>66.713059</t>
+  </si>
+  <si>
+    <t>41.341989</t>
+  </si>
+  <si>
+    <t>69.212437</t>
   </si>
 </sst>
 </file>
@@ -11589,7 +11625,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -11707,6 +11743,21 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -11988,7 +12039,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1563"/>
+  <dimension ref="A1:D1566"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -12292,7 +12343,7 @@
         <v>71.809231999999994</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>42</v>
       </c>
@@ -14294,7 +14345,7 @@
         <v>69.343695999999994</v>
       </c>
     </row>
-    <row r="165" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="5" t="s">
         <v>328</v>
       </c>
@@ -15190,7 +15241,7 @@
         <v>72.999573999999996</v>
       </c>
     </row>
-    <row r="229" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="5" t="s">
         <v>456</v>
       </c>
@@ -15358,7 +15409,7 @@
         <v>64.434209999999993</v>
       </c>
     </row>
-    <row r="241" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="5" t="s">
         <v>480</v>
       </c>
@@ -16086,7 +16137,7 @@
         <v>70.059414000000004</v>
       </c>
     </row>
-    <row r="293" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="5" t="s">
         <v>584</v>
       </c>
@@ -18690,7 +18741,7 @@
         <v>69.23648</v>
       </c>
     </row>
-    <row r="479" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A479" s="5" t="s">
         <v>956</v>
       </c>
@@ -21056,7 +21107,7 @@
         <v>59.462802000000003</v>
       </c>
     </row>
-    <row r="648" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A648" s="5" t="s">
         <v>1294</v>
       </c>
@@ -21378,7 +21429,7 @@
         <v>69.202941999999993</v>
       </c>
     </row>
-    <row r="671" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A671" s="5" t="s">
         <v>1340</v>
       </c>
@@ -21770,7 +21821,7 @@
         <v>72.069658000000004</v>
       </c>
     </row>
-    <row r="699" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A699" s="5" t="s">
         <v>1396</v>
       </c>
@@ -22106,7 +22157,7 @@
         <v>72.754859999999994</v>
       </c>
     </row>
-    <row r="723" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A723" s="5" t="s">
         <v>1444</v>
       </c>
@@ -22792,7 +22843,7 @@
         <v>69.341136000000006</v>
       </c>
     </row>
-    <row r="772" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A772" s="5" t="s">
         <v>1542</v>
       </c>
@@ -23114,7 +23165,7 @@
         <v>72.094283000000004</v>
       </c>
     </row>
-    <row r="795" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A795" s="5" t="s">
         <v>1588</v>
       </c>
@@ -23590,7 +23641,7 @@
         <v>60.602592999999999</v>
       </c>
     </row>
-    <row r="829" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A829" s="5" t="s">
         <v>1656</v>
       </c>
@@ -25046,7 +25097,7 @@
         <v>69.221705</v>
       </c>
     </row>
-    <row r="933" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="933" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A933" s="5" t="s">
         <v>1864</v>
       </c>
@@ -25494,7 +25545,7 @@
         <v>69.371487000000002</v>
       </c>
     </row>
-    <row r="965" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="965" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A965" s="5" t="s">
         <v>1928</v>
       </c>
@@ -25956,7 +26007,7 @@
         <v>72.833483000000001</v>
       </c>
     </row>
-    <row r="998" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="998" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A998" s="5" t="s">
         <v>1994</v>
       </c>
@@ -33878,6 +33929,48 @@
       </c>
       <c r="D1563" s="10" t="s">
         <v>3751</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1564" s="8" t="s">
+        <v>3752</v>
+      </c>
+      <c r="B1564" s="40" t="s">
+        <v>3753</v>
+      </c>
+      <c r="C1564" s="28" t="s">
+        <v>3754</v>
+      </c>
+      <c r="D1564" s="10" t="s">
+        <v>3755</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1565" s="7" t="s">
+        <v>3756</v>
+      </c>
+      <c r="B1565" s="41" t="s">
+        <v>3757</v>
+      </c>
+      <c r="C1565" s="43" t="s">
+        <v>3760</v>
+      </c>
+      <c r="D1565" s="10" t="s">
+        <v>3761</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1566" s="5" t="s">
+        <v>3758</v>
+      </c>
+      <c r="B1566" s="42" t="s">
+        <v>3759</v>
+      </c>
+      <c r="C1566" s="44" t="s">
+        <v>3762</v>
+      </c>
+      <c r="D1566" s="10" t="s">
+        <v>3763</v>
       </c>
     </row>
   </sheetData>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B85443-4F8B-43B6-A8E5-AB9DB232A896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD938B9-879A-4C2F-958C-21567682042D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3766" uniqueCount="3764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3806" uniqueCount="3804">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -11343,6 +11343,126 @@
   </si>
   <si>
     <t>69.212437</t>
+  </si>
+  <si>
+    <t>Chekchuvaldoq sh., Soy boʼyi ko‘chasi, 28 uy: г. Чекчувалдак, улица Сой Бойи, дом 28</t>
+  </si>
+  <si>
+    <t>FrЧКЧ-1</t>
+  </si>
+  <si>
+    <t>Beshariq sh., Oltin Vodiy ko‘chasi, 209 uy: г. Бешарык, улица Олтин Водий, дом 209</t>
+  </si>
+  <si>
+    <t>FrБШК-2</t>
+  </si>
+  <si>
+    <t>Zarafshon sh., Abay ko'chasi, 3 g uy: г. Зарафшан, улица Абай, дом 3г</t>
+  </si>
+  <si>
+    <t>FrЗАР-6</t>
+  </si>
+  <si>
+    <t>G'ujbag' sh., Baxt ko'chasi, 25а uy: г. Гуджбаг, улица Бахт, дом 25а</t>
+  </si>
+  <si>
+    <t>FrГУЖ-1</t>
+  </si>
+  <si>
+    <t>г. Почван, улица Почван, дом 49: Pochvon sh., Pochvon ko'chasi, 49 uy</t>
+  </si>
+  <si>
+    <t>FrПЧВ-1</t>
+  </si>
+  <si>
+    <t>Sultonobod sh., Qo‘rg‘ontepa tumani, Jannat bog ko'chasi, 321 uy: г. Султанабад, Кургантепинский район, улица Жаннат бог, дом 321</t>
+  </si>
+  <si>
+    <t>FrСЛТ-1</t>
+  </si>
+  <si>
+    <t>Denov sh., Madaniyat ko'chasi, 152a uy: г. Денау, улица Маданият, дом 152а</t>
+  </si>
+  <si>
+    <t>FrДЕН-8</t>
+  </si>
+  <si>
+    <t>To'rtko'l sh., Beruniy ko'chasi, 270a uy : г. Турткуль, улица Бируни, дом 270а</t>
+  </si>
+  <si>
+    <t>FrТРТ-7</t>
+  </si>
+  <si>
+    <t>Yangijoy sh., Buyuk Turon, 79a uy: г. Янгижой, улица Буюк Турон, дом 79а</t>
+  </si>
+  <si>
+    <t>FrЯГЖ-1</t>
+  </si>
+  <si>
+    <t>Yilkichi sh., M. Tashev ko'chasi, 57a uy: г. Йилкичи, улица М. Ташев, дом 57а</t>
+  </si>
+  <si>
+    <t>FrЛКЧ-1</t>
+  </si>
+  <si>
+    <t>40.531908</t>
+  </si>
+  <si>
+    <t>70.814569</t>
+  </si>
+  <si>
+    <t>40.437002</t>
+  </si>
+  <si>
+    <t>70.611627</t>
+  </si>
+  <si>
+    <t>41.568418</t>
+  </si>
+  <si>
+    <t>64.171320</t>
+  </si>
+  <si>
+    <t>40.206524</t>
+  </si>
+  <si>
+    <t>65.359948</t>
+  </si>
+  <si>
+    <t>39.469275</t>
+  </si>
+  <si>
+    <t>67.278055</t>
+  </si>
+  <si>
+    <t>40.770223</t>
+  </si>
+  <si>
+    <t>72.973007</t>
+  </si>
+  <si>
+    <t>38.281273</t>
+  </si>
+  <si>
+    <t>67.904541</t>
+  </si>
+  <si>
+    <t>41.558000</t>
+  </si>
+  <si>
+    <t>60.992931</t>
+  </si>
+  <si>
+    <t>39.587970</t>
+  </si>
+  <si>
+    <t>66.942004</t>
+  </si>
+  <si>
+    <t>41.042747</t>
+  </si>
+  <si>
+    <t>69.134031</t>
   </si>
 </sst>
 </file>
@@ -11625,7 +11745,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -11757,6 +11877,12 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -12039,7 +12165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1566"/>
+  <dimension ref="A1:D1576"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -33973,6 +34099,146 @@
         <v>3763</v>
       </c>
     </row>
+    <row r="1567" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1567" s="8" t="s">
+        <v>3764</v>
+      </c>
+      <c r="B1567" s="45" t="s">
+        <v>3765</v>
+      </c>
+      <c r="C1567" s="43" t="s">
+        <v>3784</v>
+      </c>
+      <c r="D1567" s="10" t="s">
+        <v>3785</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1568" s="23" t="s">
+        <v>3766</v>
+      </c>
+      <c r="B1568" s="46" t="s">
+        <v>3767</v>
+      </c>
+      <c r="C1568" s="44" t="s">
+        <v>3786</v>
+      </c>
+      <c r="D1568" s="10" t="s">
+        <v>3787</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1569" s="23" t="s">
+        <v>3768</v>
+      </c>
+      <c r="B1569" s="46" t="s">
+        <v>3769</v>
+      </c>
+      <c r="C1569" s="44" t="s">
+        <v>3788</v>
+      </c>
+      <c r="D1569" s="10" t="s">
+        <v>3789</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1570" s="23" t="s">
+        <v>3770</v>
+      </c>
+      <c r="B1570" s="46" t="s">
+        <v>3771</v>
+      </c>
+      <c r="C1570" s="44" t="s">
+        <v>3790</v>
+      </c>
+      <c r="D1570" s="10" t="s">
+        <v>3791</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1571" s="23" t="s">
+        <v>3772</v>
+      </c>
+      <c r="B1571" s="46" t="s">
+        <v>3773</v>
+      </c>
+      <c r="C1571" s="44" t="s">
+        <v>3792</v>
+      </c>
+      <c r="D1571" s="10" t="s">
+        <v>3793</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1572" s="23" t="s">
+        <v>3774</v>
+      </c>
+      <c r="B1572" s="46" t="s">
+        <v>3775</v>
+      </c>
+      <c r="C1572" s="44" t="s">
+        <v>3794</v>
+      </c>
+      <c r="D1572" s="10" t="s">
+        <v>3795</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1573" s="23" t="s">
+        <v>3776</v>
+      </c>
+      <c r="B1573" s="46" t="s">
+        <v>3777</v>
+      </c>
+      <c r="C1573" s="44" t="s">
+        <v>3796</v>
+      </c>
+      <c r="D1573" s="10" t="s">
+        <v>3797</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1574" s="23" t="s">
+        <v>3778</v>
+      </c>
+      <c r="B1574" s="46" t="s">
+        <v>3779</v>
+      </c>
+      <c r="C1574" s="44" t="s">
+        <v>3798</v>
+      </c>
+      <c r="D1574" s="10" t="s">
+        <v>3799</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1575" s="23" t="s">
+        <v>3780</v>
+      </c>
+      <c r="B1575" s="46" t="s">
+        <v>3781</v>
+      </c>
+      <c r="C1575" s="44" t="s">
+        <v>3800</v>
+      </c>
+      <c r="D1575" s="10" t="s">
+        <v>3801</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1576" s="23" t="s">
+        <v>3782</v>
+      </c>
+      <c r="B1576" s="46" t="s">
+        <v>3783</v>
+      </c>
+      <c r="C1576" s="44" t="s">
+        <v>3802</v>
+      </c>
+      <c r="D1576" s="10" t="s">
+        <v>3803</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD938B9-879A-4C2F-958C-21567682042D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{132C3A16-4A1D-40AF-8C29-26C5F9ABDD5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3806" uniqueCount="3804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3814" uniqueCount="3812">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -11463,6 +11463,30 @@
   </si>
   <si>
     <t>69.134031</t>
+  </si>
+  <si>
+    <t>Urganch sh., Mirzo Ulug'bek ko'chasi, 1 uy: г. Ургенч, улица Мирзо Улугбека, дом 1</t>
+  </si>
+  <si>
+    <t>FrУРГ-28</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Yakkasaroy tumani, Abdulla Qahhor ko'chasi, 18a uy: г. Ташкент, Яккасарайский район, улица Абдуллы Каххара, дом 18а</t>
+  </si>
+  <si>
+    <t>FrТАШ-403</t>
+  </si>
+  <si>
+    <t>41.549722</t>
+  </si>
+  <si>
+    <t>60.606405</t>
+  </si>
+  <si>
+    <t>41.285324</t>
+  </si>
+  <si>
+    <t>69.257705</t>
   </si>
 </sst>
 </file>
@@ -12165,7 +12189,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1576"/>
+  <dimension ref="A1:D1578"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -34239,6 +34263,34 @@
         <v>3803</v>
       </c>
     </row>
+    <row r="1577" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1577" s="7" t="s">
+        <v>3804</v>
+      </c>
+      <c r="B1577" s="41" t="s">
+        <v>3805</v>
+      </c>
+      <c r="C1577" s="43" t="s">
+        <v>3808</v>
+      </c>
+      <c r="D1577" s="10" t="s">
+        <v>3809</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1578" s="5" t="s">
+        <v>3806</v>
+      </c>
+      <c r="B1578" s="42" t="s">
+        <v>3807</v>
+      </c>
+      <c r="C1578" s="44" t="s">
+        <v>3810</v>
+      </c>
+      <c r="D1578" s="10" t="s">
+        <v>3811</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{132C3A16-4A1D-40AF-8C29-26C5F9ABDD5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{198F8C13-95F5-468D-A046-268E2F5FC317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3814" uniqueCount="3812">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3878" uniqueCount="3875">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -11487,6 +11487,195 @@
   </si>
   <si>
     <t>69.257705</t>
+  </si>
+  <si>
+    <t>Kattaqo‘rg‘on sh., Alisher Navoiy ko‘chasi, 186 A uy: г. Каттакурган, улица Алишера Навои, дом 186 A</t>
+  </si>
+  <si>
+    <t>FrКТГ-10</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Yashnobod tumani, Izzat ko'chasi, 30 uy: г. Ташкент, Яшнабадский район, улица Иззат, дом 30</t>
+  </si>
+  <si>
+    <t>FrТАШ-405</t>
+  </si>
+  <si>
+    <t>Yangi Nishon sh., O‘zbekiston ko'chasi, 67 А uy: г. Янги Нишан, улица Узбекистан, дом 67 А</t>
+  </si>
+  <si>
+    <t>FrЯНШ-2</t>
+  </si>
+  <si>
+    <t>Uchqo'rg'on sh., Doʻstlik ko'chasi, 3 uy: г. Учкурган, улица Дустлик, дом 3</t>
+  </si>
+  <si>
+    <t>FrУЧН-5</t>
+  </si>
+  <si>
+    <t>Yangi Marg'ilon sh., Yangi Farg'ona ko'chasi, 130 Б uy: г. Янги Маргилан, улица Янги Фергана, дом 130 Б</t>
+  </si>
+  <si>
+    <t>FrЯМГ-2</t>
+  </si>
+  <si>
+    <t>Shavat sh., Turkiston ko'chasi, 9 uy.: г. Шават, улица Туркистон, дом 9</t>
+  </si>
+  <si>
+    <t>FrШВТ-3</t>
+  </si>
+  <si>
+    <t>Mundiyan sh., Kattaqo'rg'on tumani, Mundiyon ko'chasi, 628 uy.: г. Мундиян, Каттакурганский район, улица Мундиён, дом 628</t>
+  </si>
+  <si>
+    <t>FrМУН-1</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Yashnobod tumani, Botkina ko'chasi, 6-uy: г. Ташкент , Яшнабадский район, ул. Боткина, дом 6</t>
+  </si>
+  <si>
+    <t>FrТАШ-413</t>
+  </si>
+  <si>
+    <t>Dashnabod sh., Toshkent ko'chasi, 31 uy.: г. Дашнабад, улица Ташкент, дом 31</t>
+  </si>
+  <si>
+    <t>FrДШН-1</t>
+  </si>
+  <si>
+    <t>Dehqonobod sh., Urgut tumani, Dehqonobod ko'chasi, 5 uy.: г. Дехконобод, Ургутский район, улица Дехконобод, дом 5</t>
+  </si>
+  <si>
+    <t>FrДЕХ-1</t>
+  </si>
+  <si>
+    <t>Konigil sh., Azizon ko'chasi, 100 uy.: г. Конигиль, улица Азизон, дом 100</t>
+  </si>
+  <si>
+    <t>FrКОН-1</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Chilonzor tumani, Al-Xorazmiy-2, 14 uy: г. Ташкент, Чиланзарский район, массив Аль-Хорезми-2, дом 14</t>
+  </si>
+  <si>
+    <t>FrТАШ-409</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Chilonzor tumani, , Dombrobod ko'chasi, 1 uy: г. Ташкент, Чиланзарский район, улица Домбробод, дом 1</t>
+  </si>
+  <si>
+    <t>FrТАШ-411</t>
+  </si>
+  <si>
+    <t>Ibrat sh., Buvayda tumani, Alisher Navoiy ko'chasi, 10 uy.: г. Ибрат, Бувайдинский район, улица Алишера Навои, дом 10</t>
+  </si>
+  <si>
+    <t>FrИБР-1</t>
+  </si>
+  <si>
+    <t>Namangan sh., Mamarasulov ko'chasi, 81 uy: г. Наманган, улица Мамарасулова, 81 дом</t>
+  </si>
+  <si>
+    <t>FrНАМ-34</t>
+  </si>
+  <si>
+    <t>FrКГН-2</t>
+  </si>
+  <si>
+    <t>39.892489</t>
+  </si>
+  <si>
+    <t>66.257840</t>
+  </si>
+  <si>
+    <t>41.278250</t>
+  </si>
+  <si>
+    <t>69.341242</t>
+  </si>
+  <si>
+    <t>38.641752</t>
+  </si>
+  <si>
+    <t>65.695508</t>
+  </si>
+  <si>
+    <t>41.115651</t>
+  </si>
+  <si>
+    <t>72.082565</t>
+  </si>
+  <si>
+    <t>40.423576</t>
+  </si>
+  <si>
+    <t>71.722005</t>
+  </si>
+  <si>
+    <t>41.691814</t>
+  </si>
+  <si>
+    <t>60.282402</t>
+  </si>
+  <si>
+    <t>39.998660</t>
+  </si>
+  <si>
+    <t>66.207149</t>
+  </si>
+  <si>
+    <t>41.301399</t>
+  </si>
+  <si>
+    <t>69.305521</t>
+  </si>
+  <si>
+    <t>38.518517</t>
+  </si>
+  <si>
+    <t>68.042520</t>
+  </si>
+  <si>
+    <t>39.453717</t>
+  </si>
+  <si>
+    <t>67.089227</t>
+  </si>
+  <si>
+    <t>39.670225</t>
+  </si>
+  <si>
+    <t>67.020107</t>
+  </si>
+  <si>
+    <t>41.264242</t>
+  </si>
+  <si>
+    <t>69.158264</t>
+  </si>
+  <si>
+    <t>41.268605</t>
+  </si>
+  <si>
+    <t>69.210705</t>
+  </si>
+  <si>
+    <t>40.556220</t>
+  </si>
+  <si>
+    <t>71.144063</t>
+  </si>
+  <si>
+    <t>41.011307</t>
+  </si>
+  <si>
+    <t>71.677116</t>
+  </si>
+  <si>
+    <t>40.853136</t>
+  </si>
+  <si>
+    <t>72.321296</t>
   </si>
 </sst>
 </file>
@@ -11769,7 +11958,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -11907,6 +12096,9 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -12189,7 +12381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1578"/>
+  <dimension ref="A1:D1594"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -34291,6 +34483,230 @@
         <v>3811</v>
       </c>
     </row>
+    <row r="1579" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1579" s="7" t="s">
+        <v>3812</v>
+      </c>
+      <c r="B1579" s="41" t="s">
+        <v>3813</v>
+      </c>
+      <c r="C1579" s="43" t="s">
+        <v>3843</v>
+      </c>
+      <c r="D1579" s="10" t="s">
+        <v>3844</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1580" s="2" t="s">
+        <v>3814</v>
+      </c>
+      <c r="B1580" s="42" t="s">
+        <v>3815</v>
+      </c>
+      <c r="C1580" s="47" t="s">
+        <v>3845</v>
+      </c>
+      <c r="D1580" s="10" t="s">
+        <v>3846</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1581" s="5" t="s">
+        <v>3816</v>
+      </c>
+      <c r="B1581" s="42" t="s">
+        <v>3817</v>
+      </c>
+      <c r="C1581" s="44" t="s">
+        <v>3847</v>
+      </c>
+      <c r="D1581" s="10" t="s">
+        <v>3848</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1582" s="5" t="s">
+        <v>3818</v>
+      </c>
+      <c r="B1582" s="42" t="s">
+        <v>3819</v>
+      </c>
+      <c r="C1582" s="44" t="s">
+        <v>3849</v>
+      </c>
+      <c r="D1582" s="10" t="s">
+        <v>3850</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1583" s="5" t="s">
+        <v>3820</v>
+      </c>
+      <c r="B1583" s="42" t="s">
+        <v>3821</v>
+      </c>
+      <c r="C1583" s="44" t="s">
+        <v>3851</v>
+      </c>
+      <c r="D1583" s="10" t="s">
+        <v>3852</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1584" s="5" t="s">
+        <v>3822</v>
+      </c>
+      <c r="B1584" s="42" t="s">
+        <v>3823</v>
+      </c>
+      <c r="C1584" s="44" t="s">
+        <v>3853</v>
+      </c>
+      <c r="D1584" s="10" t="s">
+        <v>3854</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1585" s="5" t="s">
+        <v>3824</v>
+      </c>
+      <c r="B1585" s="42" t="s">
+        <v>3825</v>
+      </c>
+      <c r="C1585" s="44" t="s">
+        <v>3855</v>
+      </c>
+      <c r="D1585" s="10" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1586" s="5" t="s">
+        <v>3826</v>
+      </c>
+      <c r="B1586" s="42" t="s">
+        <v>3827</v>
+      </c>
+      <c r="C1586" s="44" t="s">
+        <v>3857</v>
+      </c>
+      <c r="D1586" s="10" t="s">
+        <v>3858</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1587" s="5" t="s">
+        <v>3828</v>
+      </c>
+      <c r="B1587" s="42" t="s">
+        <v>3829</v>
+      </c>
+      <c r="C1587" s="44" t="s">
+        <v>3859</v>
+      </c>
+      <c r="D1587" s="10" t="s">
+        <v>3860</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1588" s="5" t="s">
+        <v>3830</v>
+      </c>
+      <c r="B1588" s="42" t="s">
+        <v>3831</v>
+      </c>
+      <c r="C1588" s="44" t="s">
+        <v>3861</v>
+      </c>
+      <c r="D1588" s="10" t="s">
+        <v>3862</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1589" s="5" t="s">
+        <v>3832</v>
+      </c>
+      <c r="B1589" s="42" t="s">
+        <v>3833</v>
+      </c>
+      <c r="C1589" s="44" t="s">
+        <v>3863</v>
+      </c>
+      <c r="D1589" s="10" t="s">
+        <v>3864</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1590" s="5" t="s">
+        <v>3834</v>
+      </c>
+      <c r="B1590" s="42" t="s">
+        <v>3835</v>
+      </c>
+      <c r="C1590" s="44" t="s">
+        <v>3865</v>
+      </c>
+      <c r="D1590" s="10" t="s">
+        <v>3866</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1591" s="5" t="s">
+        <v>3836</v>
+      </c>
+      <c r="B1591" s="42" t="s">
+        <v>3837</v>
+      </c>
+      <c r="C1591" s="44" t="s">
+        <v>3867</v>
+      </c>
+      <c r="D1591" s="10" t="s">
+        <v>3868</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1592" s="5" t="s">
+        <v>3838</v>
+      </c>
+      <c r="B1592" s="42" t="s">
+        <v>3839</v>
+      </c>
+      <c r="C1592" s="44" t="s">
+        <v>3869</v>
+      </c>
+      <c r="D1592" s="10" t="s">
+        <v>3870</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1593" s="5" t="s">
+        <v>3840</v>
+      </c>
+      <c r="B1593" s="42" t="s">
+        <v>3841</v>
+      </c>
+      <c r="C1593" s="44" t="s">
+        <v>3871</v>
+      </c>
+      <c r="D1593" s="10" t="s">
+        <v>3872</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1594" s="5" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B1594" s="42" t="s">
+        <v>3842</v>
+      </c>
+      <c r="C1594" s="44" t="s">
+        <v>3873</v>
+      </c>
+      <c r="D1594" s="10" t="s">
+        <v>3874</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
